--- a/data/OVTech Master Curriculum.xlsx
+++ b/data/OVTech Master Curriculum.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8400"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Master Curriculum" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2325" uniqueCount="772">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2326" uniqueCount="772">
   <si>
     <t>Global Order</t>
   </si>
@@ -431,15 +431,6 @@
     <t>Word Document</t>
   </si>
   <si>
-    <t>EX018</t>
-  </si>
-  <si>
-    <t>Excel Practical Teaching With Example</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=cKWal1lewQI</t>
-  </si>
-  <si>
     <t>EX019</t>
   </si>
   <si>
@@ -530,7 +521,7 @@
     <t>EX028</t>
   </si>
   <si>
-    <t>Mini-Project 1 Pt.1b</t>
+    <t>Mini-Project 1 Pt 2</t>
   </si>
   <si>
     <t>https://youtu.be/kRjhOCkhB20</t>
@@ -2223,6 +2214,15 @@
   </si>
   <si>
     <t>https://youtu.be/LZWTeYXzAO8</t>
+  </si>
+  <si>
+    <t>Capstone Project</t>
+  </si>
+  <si>
+    <t>PY021</t>
+  </si>
+  <si>
+    <t>2026-09-16</t>
   </si>
   <si>
     <t>OVTech LMS Curriculum Fix Summary</t>
@@ -3272,7 +3272,7 @@
     <tableColumn id="8" name="YouTube Link"/>
     <tableColumn id="9" name="Downloadable Resource"/>
     <tableColumn id="10" name="Unlock Day"/>
-    <tableColumn id="11" name="Notes"/>
+    <tableColumn id="11" name="Week"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4952,7 +4952,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" ht="27.6" spans="1:14">
+    <row r="35" spans="1:14">
       <c r="A35" s="5">
         <v>34</v>
       </c>
@@ -4977,20 +4977,24 @@
       <c r="H35" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="I35" s="5"/>
+      <c r="I35" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="J35" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K35" s="5">
         <v>2</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="N35" s="6"/>
+        <v>68</v>
+      </c>
+      <c r="N35" s="6" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="5">
@@ -5003,7 +5007,7 @@
         <v>129</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E36" s="5">
         <v>19</v>
@@ -5012,10 +5016,10 @@
         <v>24</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I36" s="5" t="s">
         <v>18</v>
@@ -5027,7 +5031,7 @@
         <v>2</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="M36" s="6" t="s">
         <v>68</v>
@@ -5071,7 +5075,7 @@
         <v>2</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>68</v>
@@ -5115,7 +5119,7 @@
         <v>2</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="M38" s="6" t="s">
         <v>68</v>
@@ -5159,7 +5163,7 @@
         <v>2</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="M39" s="6" t="s">
         <v>68</v>
@@ -5197,16 +5201,16 @@
         <v>18</v>
       </c>
       <c r="J40" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K40" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="N40" s="6" t="s">
         <v>18</v>
@@ -5223,7 +5227,7 @@
         <v>129</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E41" s="5">
         <v>24</v>
@@ -5232,10 +5236,10 @@
         <v>24</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I41" s="5" t="s">
         <v>18</v>
@@ -5247,7 +5251,7 @@
         <v>3</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="M41" s="6" t="s">
         <v>84</v>
@@ -5291,7 +5295,7 @@
         <v>3</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="M42" s="6" t="s">
         <v>84</v>
@@ -5335,7 +5339,7 @@
         <v>3</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="M43" s="6" t="s">
         <v>84</v>
@@ -5373,16 +5377,16 @@
         <v>18</v>
       </c>
       <c r="J44" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K44" s="5">
         <v>3</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="N44" s="6" t="s">
         <v>18</v>
@@ -5399,7 +5403,7 @@
         <v>129</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E45" s="5">
         <v>28</v>
@@ -5408,10 +5412,10 @@
         <v>24</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I45" s="5" t="s">
         <v>18</v>
@@ -5423,7 +5427,7 @@
         <v>3</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="M45" s="6" t="s">
         <v>21</v>
@@ -5440,25 +5444,25 @@
         <v>75</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>129</v>
+        <v>169</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E46" s="5">
         <v>29</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>171</v>
+        <v>18</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>18</v>
+        <v>172</v>
       </c>
       <c r="J46" s="5">
         <v>11</v>
@@ -5467,13 +5471,13 @@
         <v>3</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="M46" s="6" t="s">
         <v>21</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="47" spans="1:14">
@@ -5484,7 +5488,7 @@
         <v>75</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>173</v>
@@ -5502,7 +5506,7 @@
         <v>18</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>175</v>
+        <v>132</v>
       </c>
       <c r="J47" s="5">
         <v>11</v>
@@ -5511,7 +5515,7 @@
         <v>3</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="M47" s="6" t="s">
         <v>21</v>
@@ -5528,25 +5532,25 @@
         <v>75</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E48" s="5">
         <v>31</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G48" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="H48" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="H48" s="5" t="s">
-        <v>18</v>
-      </c>
       <c r="I48" s="5" t="s">
-        <v>132</v>
+        <v>18</v>
       </c>
       <c r="J48" s="5">
         <v>11</v>
@@ -5555,13 +5559,13 @@
         <v>3</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="M48" s="6" t="s">
         <v>21</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="49" spans="1:14">
@@ -5572,7 +5576,7 @@
         <v>75</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>178</v>
@@ -5589,7 +5593,7 @@
       <c r="H49" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="I49" s="5" t="s">
+      <c r="I49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="J49" s="5">
@@ -5599,7 +5603,7 @@
         <v>3</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="M49" s="6" t="s">
         <v>21</v>
@@ -5616,7 +5620,7 @@
         <v>75</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>181</v>
@@ -5637,22 +5641,22 @@
         <v>18</v>
       </c>
       <c r="J50" s="5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K50" s="5">
         <v>3</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="M50" s="6" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="N50" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="51" spans="1:14">
+    <row r="51" ht="14.4" spans="1:14">
       <c r="A51" s="5">
         <v>50</v>
       </c>
@@ -5660,10 +5664,10 @@
         <v>75</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E51" s="5">
         <v>34</v>
@@ -5672,10 +5676,10 @@
         <v>24</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="H51" s="5" t="s">
         <v>186</v>
+      </c>
+      <c r="H51" s="7" t="s">
+        <v>187</v>
       </c>
       <c r="I51" s="6" t="s">
         <v>18</v>
@@ -5687,7 +5691,7 @@
         <v>3</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="M51" s="6" t="s">
         <v>40</v>
@@ -5696,7 +5700,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="52" ht="14.4" spans="1:14">
+    <row r="52" spans="1:14">
       <c r="A52" s="5">
         <v>51</v>
       </c>
@@ -5704,7 +5708,7 @@
         <v>75</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>188</v>
@@ -5718,7 +5722,7 @@
       <c r="G52" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="H52" s="7" t="s">
+      <c r="H52" s="5" t="s">
         <v>190</v>
       </c>
       <c r="I52" s="6" t="s">
@@ -5731,7 +5735,7 @@
         <v>3</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="M52" s="6" t="s">
         <v>40</v>
@@ -5748,7 +5752,7 @@
         <v>75</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>191</v>
@@ -5765,7 +5769,7 @@
       <c r="H53" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="I53" s="6" t="s">
+      <c r="I53" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J53" s="5">
@@ -5775,7 +5779,7 @@
         <v>3</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="M53" s="6" t="s">
         <v>40</v>
@@ -5792,7 +5796,7 @@
         <v>75</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>194</v>
@@ -5813,22 +5817,22 @@
         <v>18</v>
       </c>
       <c r="J54" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K54" s="5">
         <v>3</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="M54" s="6" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="N54" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="55" spans="1:14">
+    <row r="55" ht="14.4" spans="1:14">
       <c r="A55" s="5">
         <v>54</v>
       </c>
@@ -5836,10 +5840,10 @@
         <v>75</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E55" s="5">
         <v>38</v>
@@ -5848,10 +5852,10 @@
         <v>24</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="H55" s="5" t="s">
         <v>199</v>
+      </c>
+      <c r="H55" s="8" t="s">
+        <v>200</v>
       </c>
       <c r="I55" s="5" t="s">
         <v>18</v>
@@ -5863,7 +5867,7 @@
         <v>3</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="M55" s="6" t="s">
         <v>54</v>
@@ -5872,7 +5876,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="56" ht="14.4" spans="1:14">
+    <row r="56" spans="1:14">
       <c r="A56" s="5">
         <v>55</v>
       </c>
@@ -5880,7 +5884,7 @@
         <v>75</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D56" s="5" t="s">
         <v>201</v>
@@ -5894,7 +5898,7 @@
       <c r="G56" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="H56" s="8" t="s">
+      <c r="H56" s="5" t="s">
         <v>203</v>
       </c>
       <c r="I56" s="5" t="s">
@@ -5907,7 +5911,7 @@
         <v>3</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="M56" s="6" t="s">
         <v>54</v>
@@ -5924,7 +5928,7 @@
         <v>75</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>204</v>
@@ -5951,7 +5955,7 @@
         <v>3</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="M57" s="6" t="s">
         <v>54</v>
@@ -5968,7 +5972,7 @@
         <v>75</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D58" s="5" t="s">
         <v>207</v>
@@ -5989,22 +5993,22 @@
         <v>18</v>
       </c>
       <c r="J58" s="5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K58" s="5">
         <v>3</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="M58" s="6" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="N58" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:14">
+    <row r="59" ht="27.6" spans="1:14">
       <c r="A59" s="5">
         <v>58</v>
       </c>
@@ -6012,25 +6016,25 @@
         <v>75</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>172</v>
+        <v>211</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E59" s="5">
         <v>42</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>212</v>
+        <v>18</v>
       </c>
       <c r="I59" s="5" t="s">
-        <v>18</v>
+        <v>132</v>
       </c>
       <c r="J59" s="5">
         <v>14</v>
@@ -6039,13 +6043,13 @@
         <v>3</v>
       </c>
       <c r="L59" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="M59" s="6" t="s">
         <v>68</v>
       </c>
       <c r="N59" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="60" ht="27.6" spans="1:14">
@@ -6056,25 +6060,25 @@
         <v>75</v>
       </c>
       <c r="C60" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="D60" s="5" t="s">
         <v>214</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>215</v>
       </c>
       <c r="E60" s="5">
         <v>43</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G60" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="H60" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="H60" s="5" t="s">
-        <v>18</v>
-      </c>
       <c r="I60" s="5" t="s">
-        <v>132</v>
+        <v>18</v>
       </c>
       <c r="J60" s="5">
         <v>14</v>
@@ -6083,13 +6087,13 @@
         <v>3</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="M60" s="6" t="s">
         <v>68</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="61" ht="27.6" spans="1:14">
@@ -6100,7 +6104,7 @@
         <v>75</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>217</v>
@@ -6127,7 +6131,7 @@
         <v>3</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="M61" s="6" t="s">
         <v>68</v>
@@ -6144,7 +6148,7 @@
         <v>75</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>220</v>
@@ -6171,7 +6175,7 @@
         <v>3</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="M62" s="6" t="s">
         <v>68</v>
@@ -6188,7 +6192,7 @@
         <v>75</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>223</v>
@@ -6209,16 +6213,16 @@
         <v>18</v>
       </c>
       <c r="J63" s="5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K63" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="M63" s="6" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="N63" s="6" t="s">
         <v>18</v>
@@ -6232,10 +6236,10 @@
         <v>75</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E64" s="5">
         <v>47</v>
@@ -6244,10 +6248,10 @@
         <v>24</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I64" s="5" t="s">
         <v>18</v>
@@ -6259,7 +6263,7 @@
         <v>4</v>
       </c>
       <c r="L64" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="M64" s="6" t="s">
         <v>84</v>
@@ -6276,7 +6280,7 @@
         <v>75</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D65" s="5" t="s">
         <v>230</v>
@@ -6303,7 +6307,7 @@
         <v>4</v>
       </c>
       <c r="L65" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="M65" s="6" t="s">
         <v>84</v>
@@ -6320,7 +6324,7 @@
         <v>75</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D66" s="5" t="s">
         <v>233</v>
@@ -6347,7 +6351,7 @@
         <v>4</v>
       </c>
       <c r="L66" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="M66" s="6" t="s">
         <v>84</v>
@@ -6364,7 +6368,7 @@
         <v>75</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D67" s="5" t="s">
         <v>236</v>
@@ -6385,16 +6389,16 @@
         <v>18</v>
       </c>
       <c r="J67" s="5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K67" s="5">
         <v>4</v>
       </c>
       <c r="L67" s="6" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="M67" s="6" t="s">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="N67" s="6" t="s">
         <v>18</v>
@@ -6408,10 +6412,10 @@
         <v>75</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E68" s="5">
         <v>51</v>
@@ -6420,10 +6424,10 @@
         <v>24</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I68" s="5" t="s">
         <v>18</v>
@@ -6435,7 +6439,7 @@
         <v>4</v>
       </c>
       <c r="L68" s="6" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="M68" s="6" t="s">
         <v>21</v>
@@ -6452,7 +6456,7 @@
         <v>75</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D69" s="5" t="s">
         <v>243</v>
@@ -6479,7 +6483,7 @@
         <v>4</v>
       </c>
       <c r="L69" s="6" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="M69" s="6" t="s">
         <v>21</v>
@@ -6496,7 +6500,7 @@
         <v>75</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D70" s="5" t="s">
         <v>246</v>
@@ -6523,7 +6527,7 @@
         <v>4</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="M70" s="6" t="s">
         <v>21</v>
@@ -6540,7 +6544,7 @@
         <v>75</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D71" s="5" t="s">
         <v>249</v>
@@ -6561,16 +6565,16 @@
         <v>18</v>
       </c>
       <c r="J71" s="5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K71" s="5">
         <v>4</v>
       </c>
       <c r="L71" s="6" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="M71" s="6" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="N71" s="6" t="s">
         <v>18</v>
@@ -6584,10 +6588,10 @@
         <v>75</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E72" s="5">
         <v>55</v>
@@ -6596,10 +6600,10 @@
         <v>24</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I72" s="5" t="s">
         <v>18</v>
@@ -6611,7 +6615,7 @@
         <v>4</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="M72" s="6" t="s">
         <v>40</v>
@@ -6628,7 +6632,7 @@
         <v>75</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D73" s="5" t="s">
         <v>256</v>
@@ -6655,7 +6659,7 @@
         <v>4</v>
       </c>
       <c r="L73" s="6" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="M73" s="6" t="s">
         <v>40</v>
@@ -6672,7 +6676,7 @@
         <v>75</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D74" s="5" t="s">
         <v>259</v>
@@ -6699,7 +6703,7 @@
         <v>4</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="M74" s="6" t="s">
         <v>40</v>
@@ -6716,7 +6720,7 @@
         <v>75</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D75" s="5" t="s">
         <v>262</v>
@@ -6737,16 +6741,16 @@
         <v>18</v>
       </c>
       <c r="J75" s="5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K75" s="5">
         <v>4</v>
       </c>
       <c r="L75" s="6" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="M75" s="6" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="N75" s="6" t="s">
         <v>18</v>
@@ -6760,10 +6764,10 @@
         <v>75</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E76" s="5">
         <v>59</v>
@@ -6772,10 +6776,10 @@
         <v>24</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>266</v>
+        <v>205</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>267</v>
+        <v>206</v>
       </c>
       <c r="I76" s="5" t="s">
         <v>18</v>
@@ -6787,7 +6791,7 @@
         <v>4</v>
       </c>
       <c r="L76" s="6" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="M76" s="6" t="s">
         <v>54</v>
@@ -6804,10 +6808,10 @@
         <v>75</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E77" s="5">
         <v>60</v>
@@ -6831,7 +6835,7 @@
         <v>4</v>
       </c>
       <c r="L77" s="6" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="M77" s="6" t="s">
         <v>54</v>
@@ -6848,10 +6852,10 @@
         <v>75</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E78" s="5">
         <v>61</v>
@@ -6860,10 +6864,10 @@
         <v>24</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>211</v>
+        <v>269</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>212</v>
+        <v>270</v>
       </c>
       <c r="I78" s="5" t="s">
         <v>18</v>
@@ -6875,7 +6879,7 @@
         <v>4</v>
       </c>
       <c r="L78" s="6" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="M78" s="6" t="s">
         <v>54</v>
@@ -6884,7 +6888,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="79" ht="27.6" spans="1:14">
+    <row r="79" spans="1:14">
       <c r="A79" s="5">
         <v>78</v>
       </c>
@@ -6892,10 +6896,10 @@
         <v>75</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>214</v>
+        <v>271</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E79" s="5">
         <v>62</v>
@@ -6904,25 +6908,25 @@
         <v>24</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H79" s="5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I79" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J79" s="5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K79" s="5">
         <v>4</v>
       </c>
       <c r="L79" s="6" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="M79" s="6" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="N79" s="6" t="s">
         <v>18</v>
@@ -6936,10 +6940,10 @@
         <v>75</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E80" s="5">
         <v>63</v>
@@ -6948,10 +6952,10 @@
         <v>24</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I80" s="5" t="s">
         <v>18</v>
@@ -6963,7 +6967,7 @@
         <v>4</v>
       </c>
       <c r="L80" s="6" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="M80" s="6" t="s">
         <v>68</v>
@@ -6980,7 +6984,7 @@
         <v>75</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D81" s="5" t="s">
         <v>279</v>
@@ -7007,7 +7011,7 @@
         <v>4</v>
       </c>
       <c r="L81" s="6" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="M81" s="6" t="s">
         <v>68</v>
@@ -7024,7 +7028,7 @@
         <v>75</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D82" s="5" t="s">
         <v>282</v>
@@ -7051,7 +7055,7 @@
         <v>4</v>
       </c>
       <c r="L82" s="6" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="M82" s="6" t="s">
         <v>68</v>
@@ -7068,40 +7072,40 @@
         <v>75</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E83" s="5">
         <v>66</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H83" s="5" t="s">
-        <v>287</v>
+        <v>18</v>
       </c>
       <c r="I83" s="5" t="s">
-        <v>18</v>
+        <v>172</v>
       </c>
       <c r="J83" s="5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K83" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L83" s="6" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="M83" s="6" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="N83" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="84" spans="1:14">
@@ -7112,7 +7116,7 @@
         <v>75</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D84" s="5" t="s">
         <v>289</v>
@@ -7130,7 +7134,7 @@
         <v>18</v>
       </c>
       <c r="I84" s="5" t="s">
-        <v>175</v>
+        <v>132</v>
       </c>
       <c r="J84" s="5">
         <v>20</v>
@@ -7139,7 +7143,7 @@
         <v>5</v>
       </c>
       <c r="L84" s="6" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="M84" s="6" t="s">
         <v>84</v>
@@ -7156,25 +7160,25 @@
         <v>75</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E85" s="5">
         <v>68</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G85" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="H85" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="H85" s="5" t="s">
-        <v>18</v>
-      </c>
       <c r="I85" s="5" t="s">
-        <v>132</v>
+        <v>18</v>
       </c>
       <c r="J85" s="5">
         <v>20</v>
@@ -7183,13 +7187,13 @@
         <v>5</v>
       </c>
       <c r="L85" s="6" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="M85" s="6" t="s">
         <v>84</v>
       </c>
       <c r="N85" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="86" spans="1:14">
@@ -7200,7 +7204,7 @@
         <v>75</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D86" s="5" t="s">
         <v>294</v>
@@ -7227,7 +7231,7 @@
         <v>5</v>
       </c>
       <c r="L86" s="6" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="M86" s="6" t="s">
         <v>84</v>
@@ -7244,7 +7248,7 @@
         <v>75</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D87" s="5" t="s">
         <v>297</v>
@@ -7271,7 +7275,7 @@
         <v>5</v>
       </c>
       <c r="L87" s="6" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="M87" s="6" t="s">
         <v>84</v>
@@ -7288,7 +7292,7 @@
         <v>75</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D88" s="5" t="s">
         <v>300</v>
@@ -7303,7 +7307,7 @@
         <v>301</v>
       </c>
       <c r="H88" s="5" t="s">
-        <v>302</v>
+        <v>196</v>
       </c>
       <c r="I88" s="5" t="s">
         <v>18</v>
@@ -7315,7 +7319,7 @@
         <v>5</v>
       </c>
       <c r="L88" s="6" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="M88" s="6" t="s">
         <v>84</v>
@@ -7332,10 +7336,10 @@
         <v>75</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E89" s="5">
         <v>72</v>
@@ -7344,25 +7348,25 @@
         <v>24</v>
       </c>
       <c r="G89" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="H89" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="H89" s="5" t="s">
-        <v>199</v>
-      </c>
       <c r="I89" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J89" s="5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K89" s="5">
         <v>5</v>
       </c>
       <c r="L89" s="6" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="M89" s="6" t="s">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="N89" s="6" t="s">
         <v>18</v>
@@ -7376,10 +7380,10 @@
         <v>75</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E90" s="5">
         <v>73</v>
@@ -7388,10 +7392,10 @@
         <v>24</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H90" s="5" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I90" s="5" t="s">
         <v>18</v>
@@ -7403,7 +7407,7 @@
         <v>5</v>
       </c>
       <c r="L90" s="6" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="M90" s="6" t="s">
         <v>21</v>
@@ -7420,7 +7424,7 @@
         <v>75</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D91" s="5" t="s">
         <v>309</v>
@@ -7447,7 +7451,7 @@
         <v>5</v>
       </c>
       <c r="L91" s="6" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="M91" s="6" t="s">
         <v>21</v>
@@ -7464,7 +7468,7 @@
         <v>75</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D92" s="5" t="s">
         <v>312</v>
@@ -7479,7 +7483,7 @@
         <v>313</v>
       </c>
       <c r="H92" s="5" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="I92" s="5" t="s">
         <v>18</v>
@@ -7491,7 +7495,7 @@
         <v>5</v>
       </c>
       <c r="L92" s="6" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="M92" s="6" t="s">
         <v>21</v>
@@ -7508,7 +7512,7 @@
         <v>75</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>288</v>
+        <v>314</v>
       </c>
       <c r="D93" s="5" t="s">
         <v>315</v>
@@ -7517,31 +7521,31 @@
         <v>76</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G93" s="5" t="s">
         <v>316</v>
       </c>
       <c r="H93" s="5" t="s">
-        <v>311</v>
+        <v>18</v>
       </c>
       <c r="I93" s="5" t="s">
-        <v>18</v>
+        <v>172</v>
       </c>
       <c r="J93" s="5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K93" s="5">
         <v>5</v>
       </c>
       <c r="L93" s="6" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="M93" s="6" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="N93" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="94" spans="1:14">
@@ -7552,7 +7556,7 @@
         <v>75</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D94" s="5" t="s">
         <v>318</v>
@@ -7561,16 +7565,16 @@
         <v>77</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G94" s="5" t="s">
         <v>319</v>
       </c>
       <c r="H94" s="5" t="s">
-        <v>18</v>
+        <v>320</v>
       </c>
       <c r="I94" s="5" t="s">
-        <v>175</v>
+        <v>18</v>
       </c>
       <c r="J94" s="5">
         <v>22</v>
@@ -7579,13 +7583,13 @@
         <v>5</v>
       </c>
       <c r="L94" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="M94" s="6" t="s">
         <v>40</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="95" spans="1:14">
@@ -7596,7 +7600,7 @@
         <v>75</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D95" s="5" t="s">
         <v>321</v>
@@ -7623,7 +7627,7 @@
         <v>5</v>
       </c>
       <c r="L95" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="M95" s="6" t="s">
         <v>40</v>
@@ -7640,7 +7644,7 @@
         <v>75</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D96" s="5" t="s">
         <v>324</v>
@@ -7667,7 +7671,7 @@
         <v>5</v>
       </c>
       <c r="L96" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="M96" s="6" t="s">
         <v>40</v>
@@ -7684,7 +7688,7 @@
         <v>75</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D97" s="5" t="s">
         <v>327</v>
@@ -7711,7 +7715,7 @@
         <v>5</v>
       </c>
       <c r="L97" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="M97" s="6" t="s">
         <v>40</v>
@@ -7728,10 +7732,10 @@
         <v>75</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E98" s="5">
         <v>81</v>
@@ -7740,7 +7744,7 @@
         <v>24</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H98" s="5" t="s">
         <v>332</v>
@@ -7749,16 +7753,16 @@
         <v>18</v>
       </c>
       <c r="J98" s="5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K98" s="5">
         <v>5</v>
       </c>
       <c r="L98" s="6" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
       <c r="M98" s="6" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="N98" s="6" t="s">
         <v>18</v>
@@ -7772,7 +7776,7 @@
         <v>75</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D99" s="5" t="s">
         <v>334</v>
@@ -7784,10 +7788,10 @@
         <v>24</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H99" s="5" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="I99" s="5" t="s">
         <v>18</v>
@@ -7799,7 +7803,7 @@
         <v>5</v>
       </c>
       <c r="L99" s="6" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="M99" s="6" t="s">
         <v>54</v>
@@ -7816,7 +7820,7 @@
         <v>75</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D100" s="5" t="s">
         <v>337</v>
@@ -7843,7 +7847,7 @@
         <v>5</v>
       </c>
       <c r="L100" s="6" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="M100" s="6" t="s">
         <v>54</v>
@@ -7860,7 +7864,7 @@
         <v>75</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D101" s="5" t="s">
         <v>340</v>
@@ -7887,7 +7891,7 @@
         <v>5</v>
       </c>
       <c r="L101" s="6" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="M101" s="6" t="s">
         <v>54</v>
@@ -7904,7 +7908,7 @@
         <v>75</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D102" s="5" t="s">
         <v>343</v>
@@ -7925,16 +7929,16 @@
         <v>18</v>
       </c>
       <c r="J102" s="5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K102" s="5">
         <v>5</v>
       </c>
       <c r="L102" s="6" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="M102" s="6" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="N102" s="6" t="s">
         <v>18</v>
@@ -7948,10 +7952,10 @@
         <v>75</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E103" s="5">
         <v>86</v>
@@ -7960,10 +7964,10 @@
         <v>24</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H103" s="5" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="I103" s="5" t="s">
         <v>18</v>
@@ -7975,7 +7979,7 @@
         <v>5</v>
       </c>
       <c r="L103" s="6" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="M103" s="6" t="s">
         <v>68</v>
@@ -7989,43 +7993,43 @@
         <v>103</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>75</v>
+        <v>350</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>333</v>
+        <v>350</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E104" s="5">
-        <v>87</v>
+        <v>1</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H104" s="5" t="s">
-        <v>352</v>
+        <v>18</v>
       </c>
       <c r="I104" s="5" t="s">
-        <v>18</v>
+        <v>172</v>
       </c>
       <c r="J104" s="5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K104" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L104" s="6" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="M104" s="6" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="105" spans="1:14">
@@ -8033,16 +8037,16 @@
         <v>104</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D105" s="5" t="s">
         <v>354</v>
       </c>
       <c r="E105" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F105" s="5" t="s">
         <v>16</v>
@@ -8054,7 +8058,7 @@
         <v>18</v>
       </c>
       <c r="I105" s="5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="J105" s="5">
         <v>25</v>
@@ -8063,7 +8067,7 @@
         <v>6</v>
       </c>
       <c r="L105" s="6" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="M105" s="6" t="s">
         <v>84</v>
@@ -8077,28 +8081,28 @@
         <v>105</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D106" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="E106" s="5">
+        <v>3</v>
+      </c>
+      <c r="F106" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G106" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="E106" s="5">
-        <v>2</v>
-      </c>
-      <c r="F106" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G106" s="5" t="s">
+      <c r="H106" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="H106" s="5" t="s">
-        <v>18</v>
-      </c>
       <c r="I106" s="5" t="s">
-        <v>175</v>
+        <v>18</v>
       </c>
       <c r="J106" s="5">
         <v>25</v>
@@ -8107,13 +8111,13 @@
         <v>6</v>
       </c>
       <c r="L106" s="6" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="M106" s="6" t="s">
         <v>84</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="107" spans="1:14">
@@ -8121,16 +8125,16 @@
         <v>106</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D107" s="5" t="s">
         <v>359</v>
       </c>
       <c r="E107" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F107" s="5" t="s">
         <v>24</v>
@@ -8151,7 +8155,7 @@
         <v>6</v>
       </c>
       <c r="L107" s="6" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="M107" s="6" t="s">
         <v>84</v>
@@ -8165,16 +8169,16 @@
         <v>107</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D108" s="5" t="s">
         <v>362</v>
       </c>
       <c r="E108" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F108" s="5" t="s">
         <v>24</v>
@@ -8195,7 +8199,7 @@
         <v>6</v>
       </c>
       <c r="L108" s="6" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="M108" s="6" t="s">
         <v>84</v>
@@ -8209,16 +8213,16 @@
         <v>108</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D109" s="5" t="s">
         <v>365</v>
       </c>
       <c r="E109" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F109" s="5" t="s">
         <v>24</v>
@@ -8239,7 +8243,7 @@
         <v>6</v>
       </c>
       <c r="L109" s="6" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="M109" s="6" t="s">
         <v>84</v>
@@ -8253,16 +8257,16 @@
         <v>109</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D110" s="5" t="s">
         <v>368</v>
       </c>
       <c r="E110" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F110" s="5" t="s">
         <v>24</v>
@@ -8277,16 +8281,16 @@
         <v>18</v>
       </c>
       <c r="J110" s="5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K110" s="5">
         <v>6</v>
       </c>
       <c r="L110" s="6" t="s">
-        <v>356</v>
+        <v>371</v>
       </c>
       <c r="M110" s="6" t="s">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="N110" s="6" t="s">
         <v>18</v>
@@ -8297,25 +8301,25 @@
         <v>110</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E111" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F111" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G111" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H111" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="I111" s="5" t="s">
         <v>18</v>
@@ -8327,7 +8331,7 @@
         <v>6</v>
       </c>
       <c r="L111" s="6" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="M111" s="6" t="s">
         <v>21</v>
@@ -8341,16 +8345,16 @@
         <v>111</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D112" s="5" t="s">
         <v>375</v>
       </c>
       <c r="E112" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F112" s="5" t="s">
         <v>24</v>
@@ -8371,7 +8375,7 @@
         <v>6</v>
       </c>
       <c r="L112" s="6" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="M112" s="6" t="s">
         <v>21</v>
@@ -8385,16 +8389,16 @@
         <v>112</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D113" s="5" t="s">
         <v>378</v>
       </c>
       <c r="E113" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F113" s="5" t="s">
         <v>24</v>
@@ -8415,7 +8419,7 @@
         <v>6</v>
       </c>
       <c r="L113" s="6" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="M113" s="6" t="s">
         <v>21</v>
@@ -8429,16 +8433,16 @@
         <v>113</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D114" s="5" t="s">
         <v>381</v>
       </c>
       <c r="E114" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F114" s="5" t="s">
         <v>24</v>
@@ -8453,16 +8457,16 @@
         <v>18</v>
       </c>
       <c r="J114" s="5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K114" s="5">
         <v>6</v>
       </c>
       <c r="L114" s="6" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="M114" s="6" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="N114" s="6" t="s">
         <v>18</v>
@@ -8473,25 +8477,25 @@
         <v>114</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E115" s="5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F115" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G115" s="5" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H115" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="I115" s="5" t="s">
         <v>18</v>
@@ -8503,7 +8507,7 @@
         <v>6</v>
       </c>
       <c r="L115" s="6" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="M115" s="6" t="s">
         <v>40</v>
@@ -8517,16 +8521,16 @@
         <v>115</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D116" s="5" t="s">
         <v>388</v>
       </c>
       <c r="E116" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F116" s="5" t="s">
         <v>24</v>
@@ -8547,7 +8551,7 @@
         <v>6</v>
       </c>
       <c r="L116" s="6" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="M116" s="6" t="s">
         <v>40</v>
@@ -8561,16 +8565,16 @@
         <v>116</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D117" s="5" t="s">
         <v>391</v>
       </c>
       <c r="E117" s="5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F117" s="5" t="s">
         <v>24</v>
@@ -8591,7 +8595,7 @@
         <v>6</v>
       </c>
       <c r="L117" s="6" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="M117" s="6" t="s">
         <v>40</v>
@@ -8605,43 +8609,43 @@
         <v>117</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>353</v>
+        <v>75</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>353</v>
+        <v>394</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E118" s="5">
-        <v>14</v>
+        <v>88</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G118" s="5" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H118" s="5" t="s">
-        <v>396</v>
+        <v>18</v>
       </c>
       <c r="I118" s="5" t="s">
-        <v>18</v>
+        <v>172</v>
       </c>
       <c r="J118" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K118" s="5">
         <v>6</v>
       </c>
       <c r="L118" s="6" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="M118" s="6" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="119" spans="1:14">
@@ -8652,25 +8656,25 @@
         <v>75</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="D119" s="5" t="s">
         <v>398</v>
       </c>
       <c r="E119" s="5">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F119" s="5" t="s">
         <v>16</v>
       </c>
       <c r="G119" s="5" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="H119" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I119" s="5" t="s">
-        <v>175</v>
+        <v>132</v>
       </c>
       <c r="J119" s="5">
         <v>28</v>
@@ -8679,7 +8683,7 @@
         <v>6</v>
       </c>
       <c r="L119" s="6" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="M119" s="6" t="s">
         <v>54</v>
@@ -8696,25 +8700,25 @@
         <v>75</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="D120" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="E120" s="5">
+        <v>90</v>
+      </c>
+      <c r="F120" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G120" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="H120" s="5" t="s">
         <v>401</v>
       </c>
-      <c r="E120" s="5">
-        <v>89</v>
-      </c>
-      <c r="F120" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G120" s="5" t="s">
-        <v>397</v>
-      </c>
-      <c r="H120" s="5" t="s">
-        <v>18</v>
-      </c>
       <c r="I120" s="5" t="s">
-        <v>132</v>
+        <v>18</v>
       </c>
       <c r="J120" s="5">
         <v>28</v>
@@ -8723,13 +8727,13 @@
         <v>6</v>
       </c>
       <c r="L120" s="6" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="M120" s="6" t="s">
         <v>54</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="121" spans="1:14">
@@ -8740,22 +8744,22 @@
         <v>75</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="D121" s="5" t="s">
         <v>402</v>
       </c>
       <c r="E121" s="5">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F121" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G121" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="H121" s="5" t="s">
         <v>403</v>
-      </c>
-      <c r="H121" s="5" t="s">
-        <v>404</v>
       </c>
       <c r="I121" s="5" t="s">
         <v>18</v>
@@ -8767,7 +8771,7 @@
         <v>6</v>
       </c>
       <c r="L121" s="6" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="M121" s="6" t="s">
         <v>54</v>
@@ -8784,19 +8788,19 @@
         <v>75</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="D122" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="E122" s="5">
+        <v>92</v>
+      </c>
+      <c r="F122" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G122" s="5" t="s">
         <v>405</v>
-      </c>
-      <c r="E122" s="5">
-        <v>91</v>
-      </c>
-      <c r="F122" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G122" s="5" t="s">
-        <v>403</v>
       </c>
       <c r="H122" s="5" t="s">
         <v>406</v>
@@ -8811,7 +8815,7 @@
         <v>6</v>
       </c>
       <c r="L122" s="6" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="M122" s="6" t="s">
         <v>54</v>
@@ -8828,13 +8832,13 @@
         <v>75</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="D123" s="5" t="s">
         <v>407</v>
       </c>
       <c r="E123" s="5">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F123" s="5" t="s">
         <v>24</v>
@@ -8855,7 +8859,7 @@
         <v>6</v>
       </c>
       <c r="L123" s="6" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="M123" s="6" t="s">
         <v>54</v>
@@ -8872,13 +8876,13 @@
         <v>75</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="D124" s="5" t="s">
         <v>410</v>
       </c>
       <c r="E124" s="5">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F124" s="5" t="s">
         <v>24</v>
@@ -8893,16 +8897,16 @@
         <v>18</v>
       </c>
       <c r="J124" s="5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K124" s="5">
         <v>6</v>
       </c>
       <c r="L124" s="6" t="s">
-        <v>400</v>
+        <v>413</v>
       </c>
       <c r="M124" s="6" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="N124" s="6" t="s">
         <v>18</v>
@@ -8916,22 +8920,22 @@
         <v>75</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E125" s="5">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F125" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G125" s="5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H125" s="5" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="I125" s="5" t="s">
         <v>18</v>
@@ -8943,7 +8947,7 @@
         <v>6</v>
       </c>
       <c r="L125" s="6" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="M125" s="6" t="s">
         <v>68</v>
@@ -8960,13 +8964,13 @@
         <v>75</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="D126" s="5" t="s">
         <v>417</v>
       </c>
       <c r="E126" s="5">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F126" s="5" t="s">
         <v>24</v>
@@ -8987,7 +8991,7 @@
         <v>6</v>
       </c>
       <c r="L126" s="6" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="M126" s="6" t="s">
         <v>68</v>
@@ -9004,13 +9008,13 @@
         <v>75</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="D127" s="5" t="s">
         <v>420</v>
       </c>
       <c r="E127" s="5">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F127" s="5" t="s">
         <v>24</v>
@@ -9031,7 +9035,7 @@
         <v>6</v>
       </c>
       <c r="L127" s="6" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="M127" s="6" t="s">
         <v>68</v>
@@ -9045,40 +9049,40 @@
         <v>127</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>75</v>
+        <v>423</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>397</v>
+        <v>424</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E128" s="5">
-        <v>97</v>
+        <v>1</v>
       </c>
       <c r="F128" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G128" s="5" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="H128" s="5" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="I128" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J128" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K128" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L128" s="6" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="M128" s="6" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="N128" s="6" t="s">
         <v>18</v>
@@ -9089,25 +9093,25 @@
         <v>128</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E129" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F129" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G129" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H129" s="5" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="I129" s="5" t="s">
         <v>18</v>
@@ -9119,7 +9123,7 @@
         <v>7</v>
       </c>
       <c r="L129" s="6" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="M129" s="6" t="s">
         <v>84</v>
@@ -9133,16 +9137,16 @@
         <v>129</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="D130" s="5" t="s">
         <v>432</v>
       </c>
       <c r="E130" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F130" s="5" t="s">
         <v>24</v>
@@ -9163,7 +9167,7 @@
         <v>7</v>
       </c>
       <c r="L130" s="6" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="M130" s="6" t="s">
         <v>84</v>
@@ -9177,16 +9181,16 @@
         <v>130</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="D131" s="5" t="s">
         <v>435</v>
       </c>
       <c r="E131" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F131" s="5" t="s">
         <v>24</v>
@@ -9207,7 +9211,7 @@
         <v>7</v>
       </c>
       <c r="L131" s="6" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="M131" s="6" t="s">
         <v>84</v>
@@ -9221,16 +9225,16 @@
         <v>131</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="D132" s="5" t="s">
         <v>438</v>
       </c>
       <c r="E132" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F132" s="5" t="s">
         <v>24</v>
@@ -9245,16 +9249,16 @@
         <v>18</v>
       </c>
       <c r="J132" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K132" s="5">
         <v>7</v>
       </c>
       <c r="L132" s="6" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="M132" s="6" t="s">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="N132" s="6" t="s">
         <v>18</v>
@@ -9265,25 +9269,25 @@
         <v>132</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E133" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F133" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G133" s="5" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H133" s="5" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="I133" s="5" t="s">
         <v>18</v>
@@ -9295,7 +9299,7 @@
         <v>7</v>
       </c>
       <c r="L133" s="6" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="M133" s="6" t="s">
         <v>21</v>
@@ -9309,16 +9313,16 @@
         <v>133</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="D134" s="5" t="s">
         <v>445</v>
       </c>
       <c r="E134" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F134" s="5" t="s">
         <v>24</v>
@@ -9339,7 +9343,7 @@
         <v>7</v>
       </c>
       <c r="L134" s="6" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="M134" s="6" t="s">
         <v>21</v>
@@ -9353,16 +9357,16 @@
         <v>134</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="D135" s="5" t="s">
         <v>448</v>
       </c>
       <c r="E135" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F135" s="5" t="s">
         <v>24</v>
@@ -9383,7 +9387,7 @@
         <v>7</v>
       </c>
       <c r="L135" s="6" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="M135" s="6" t="s">
         <v>21</v>
@@ -9397,16 +9401,16 @@
         <v>135</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="D136" s="5" t="s">
         <v>451</v>
       </c>
       <c r="E136" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F136" s="5" t="s">
         <v>24</v>
@@ -9427,10 +9431,10 @@
         <v>7</v>
       </c>
       <c r="L136" s="6" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="M136" s="6" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="N136" s="6" t="s">
         <v>18</v>
@@ -9441,25 +9445,25 @@
         <v>136</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E137" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F137" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G137" s="5" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H137" s="5" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="I137" s="5" t="s">
         <v>18</v>
@@ -9471,7 +9475,7 @@
         <v>7</v>
       </c>
       <c r="L137" s="6" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="M137" s="6" t="s">
         <v>40</v>
@@ -9485,37 +9489,37 @@
         <v>137</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>427</v>
+        <v>458</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E138" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F138" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G138" s="5" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H138" s="5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="I138" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J138" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K138" s="5">
         <v>7</v>
       </c>
       <c r="L138" s="6" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="M138" s="6" t="s">
         <v>40</v>
@@ -9529,16 +9533,16 @@
         <v>138</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="D139" s="5" t="s">
         <v>462</v>
       </c>
       <c r="E139" s="5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F139" s="5" t="s">
         <v>24</v>
@@ -9559,7 +9563,7 @@
         <v>7</v>
       </c>
       <c r="L139" s="6" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="M139" s="6" t="s">
         <v>40</v>
@@ -9573,16 +9577,16 @@
         <v>139</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="D140" s="5" t="s">
         <v>465</v>
       </c>
       <c r="E140" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F140" s="5" t="s">
         <v>24</v>
@@ -9603,10 +9607,10 @@
         <v>7</v>
       </c>
       <c r="L140" s="6" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="M140" s="6" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="N140" s="6" t="s">
         <v>18</v>
@@ -9617,25 +9621,25 @@
         <v>140</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E141" s="5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F141" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G141" s="5" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H141" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="I141" s="5" t="s">
         <v>18</v>
@@ -9647,7 +9651,7 @@
         <v>7</v>
       </c>
       <c r="L141" s="6" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="M141" s="6" t="s">
         <v>54</v>
@@ -9661,16 +9665,16 @@
         <v>141</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="D142" s="5" t="s">
         <v>472</v>
       </c>
       <c r="E142" s="5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F142" s="5" t="s">
         <v>24</v>
@@ -9685,13 +9689,13 @@
         <v>18</v>
       </c>
       <c r="J142" s="5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K142" s="5">
         <v>7</v>
       </c>
       <c r="L142" s="6" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="M142" s="6" t="s">
         <v>54</v>
@@ -9705,16 +9709,16 @@
         <v>142</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="D143" s="5" t="s">
         <v>475</v>
       </c>
       <c r="E143" s="5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F143" s="5" t="s">
         <v>24</v>
@@ -9735,7 +9739,7 @@
         <v>7</v>
       </c>
       <c r="L143" s="6" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="M143" s="6" t="s">
         <v>54</v>
@@ -9749,16 +9753,16 @@
         <v>143</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="D144" s="5" t="s">
         <v>478</v>
       </c>
       <c r="E144" s="5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F144" s="5" t="s">
         <v>24</v>
@@ -9779,10 +9783,10 @@
         <v>7</v>
       </c>
       <c r="L144" s="6" t="s">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="M144" s="6" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="N144" s="6" t="s">
         <v>18</v>
@@ -9793,25 +9797,25 @@
         <v>144</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E145" s="5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F145" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G145" s="5" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H145" s="5" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="I145" s="5" t="s">
         <v>18</v>
@@ -9823,7 +9827,7 @@
         <v>7</v>
       </c>
       <c r="L145" s="6" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="M145" s="6" t="s">
         <v>68</v>
@@ -9837,16 +9841,16 @@
         <v>145</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="D146" s="5" t="s">
         <v>485</v>
       </c>
       <c r="E146" s="5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F146" s="5" t="s">
         <v>24</v>
@@ -9861,13 +9865,13 @@
         <v>18</v>
       </c>
       <c r="J146" s="5">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K146" s="5">
         <v>7</v>
       </c>
       <c r="L146" s="6" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="M146" s="6" t="s">
         <v>68</v>
@@ -9881,16 +9885,16 @@
         <v>146</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="D147" s="5" t="s">
         <v>488</v>
       </c>
       <c r="E147" s="5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F147" s="5" t="s">
         <v>24</v>
@@ -9911,7 +9915,7 @@
         <v>7</v>
       </c>
       <c r="L147" s="6" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="M147" s="6" t="s">
         <v>68</v>
@@ -9920,45 +9924,45 @@
         <v>18</v>
       </c>
     </row>
-    <row r="148" spans="1:14">
+    <row r="148" ht="27.6" spans="1:14">
       <c r="A148" s="5">
         <v>147</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>461</v>
+        <v>491</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E148" s="5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F148" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G148" s="5" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H148" s="5" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="I148" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J148" s="5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K148" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L148" s="6" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="M148" s="6" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="N148" s="6" t="s">
         <v>18</v>
@@ -9969,25 +9973,25 @@
         <v>148</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E149" s="5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F149" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G149" s="5" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H149" s="5" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="I149" s="5" t="s">
         <v>18</v>
@@ -9999,7 +10003,7 @@
         <v>8</v>
       </c>
       <c r="L149" s="6" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="M149" s="6" t="s">
         <v>84</v>
@@ -10013,16 +10017,16 @@
         <v>149</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="D150" s="5" t="s">
         <v>499</v>
       </c>
       <c r="E150" s="5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F150" s="5" t="s">
         <v>24</v>
@@ -10043,7 +10047,7 @@
         <v>8</v>
       </c>
       <c r="L150" s="6" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="M150" s="6" t="s">
         <v>84</v>
@@ -10057,16 +10061,16 @@
         <v>150</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="D151" s="5" t="s">
         <v>502</v>
       </c>
       <c r="E151" s="5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F151" s="5" t="s">
         <v>24</v>
@@ -10087,7 +10091,7 @@
         <v>8</v>
       </c>
       <c r="L151" s="6" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="M151" s="6" t="s">
         <v>84</v>
@@ -10101,16 +10105,16 @@
         <v>151</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="D152" s="5" t="s">
         <v>505</v>
       </c>
       <c r="E152" s="5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F152" s="5" t="s">
         <v>24</v>
@@ -10125,16 +10129,16 @@
         <v>18</v>
       </c>
       <c r="J152" s="5">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K152" s="5">
         <v>8</v>
       </c>
       <c r="L152" s="6" t="s">
-        <v>498</v>
+        <v>508</v>
       </c>
       <c r="M152" s="6" t="s">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="N152" s="6" t="s">
         <v>18</v>
@@ -10145,37 +10149,37 @@
         <v>152</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E153" s="5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F153" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G153" s="5" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H153" s="5" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="I153" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J153" s="5">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K153" s="5">
         <v>8</v>
       </c>
       <c r="L153" s="6" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="M153" s="6" t="s">
         <v>21</v>
@@ -10189,16 +10193,16 @@
         <v>153</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="D154" s="5" t="s">
         <v>512</v>
       </c>
       <c r="E154" s="5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F154" s="5" t="s">
         <v>24</v>
@@ -10213,13 +10217,13 @@
         <v>18</v>
       </c>
       <c r="J154" s="5">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K154" s="5">
         <v>8</v>
       </c>
       <c r="L154" s="6" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="M154" s="6" t="s">
         <v>21</v>
@@ -10233,16 +10237,16 @@
         <v>154</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="D155" s="5" t="s">
         <v>515</v>
       </c>
       <c r="E155" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F155" s="5" t="s">
         <v>24</v>
@@ -10263,7 +10267,7 @@
         <v>8</v>
       </c>
       <c r="L155" s="6" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="M155" s="6" t="s">
         <v>21</v>
@@ -10277,16 +10281,16 @@
         <v>155</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="D156" s="5" t="s">
         <v>518</v>
       </c>
       <c r="E156" s="5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F156" s="5" t="s">
         <v>24</v>
@@ -10307,7 +10311,7 @@
         <v>8</v>
       </c>
       <c r="L156" s="6" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="M156" s="6" t="s">
         <v>21</v>
@@ -10321,43 +10325,43 @@
         <v>156</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>494</v>
+        <v>521</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E157" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F157" s="5" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G157" s="5" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H157" s="5" t="s">
-        <v>523</v>
+        <v>18</v>
       </c>
       <c r="I157" s="5" t="s">
-        <v>18</v>
+        <v>172</v>
       </c>
       <c r="J157" s="5">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K157" s="5">
         <v>8</v>
       </c>
       <c r="L157" s="6" t="s">
-        <v>511</v>
+        <v>524</v>
       </c>
       <c r="M157" s="6" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="N157" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="158" ht="27.6" spans="1:14">
@@ -10365,16 +10369,16 @@
         <v>157</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D158" s="5" t="s">
         <v>525</v>
       </c>
       <c r="E158" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F158" s="5" t="s">
         <v>16</v>
@@ -10386,7 +10390,7 @@
         <v>18</v>
       </c>
       <c r="I158" s="5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="J158" s="5">
         <v>37</v>
@@ -10395,7 +10399,7 @@
         <v>8</v>
       </c>
       <c r="L158" s="6" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="M158" s="6" t="s">
         <v>40</v>
@@ -10409,28 +10413,28 @@
         <v>158</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E159" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F159" s="5" t="s">
         <v>16</v>
       </c>
       <c r="G159" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H159" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I159" s="5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="J159" s="5">
         <v>37</v>
@@ -10439,7 +10443,7 @@
         <v>8</v>
       </c>
       <c r="L159" s="6" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="M159" s="6" t="s">
         <v>40</v>
@@ -10453,28 +10457,28 @@
         <v>159</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D160" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="E160" s="5">
+        <v>33</v>
+      </c>
+      <c r="F160" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G160" s="5" t="s">
         <v>530</v>
       </c>
-      <c r="E160" s="5">
-        <v>32</v>
-      </c>
-      <c r="F160" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G160" s="5" t="s">
+      <c r="H160" s="5" t="s">
         <v>531</v>
       </c>
-      <c r="H160" s="5" t="s">
-        <v>18</v>
-      </c>
       <c r="I160" s="5" t="s">
-        <v>175</v>
+        <v>18</v>
       </c>
       <c r="J160" s="5">
         <v>37</v>
@@ -10483,13 +10487,13 @@
         <v>8</v>
       </c>
       <c r="L160" s="6" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="M160" s="6" t="s">
         <v>40</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="161" ht="27.6" spans="1:14">
@@ -10497,16 +10501,16 @@
         <v>160</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D161" s="5" t="s">
         <v>532</v>
       </c>
       <c r="E161" s="5">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F161" s="5" t="s">
         <v>24</v>
@@ -10527,7 +10531,7 @@
         <v>8</v>
       </c>
       <c r="L161" s="6" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="M161" s="6" t="s">
         <v>40</v>
@@ -10541,16 +10545,16 @@
         <v>161</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D162" s="5" t="s">
         <v>535</v>
       </c>
       <c r="E162" s="5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F162" s="5" t="s">
         <v>24</v>
@@ -10571,7 +10575,7 @@
         <v>8</v>
       </c>
       <c r="L162" s="6" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="M162" s="6" t="s">
         <v>40</v>
@@ -10585,16 +10589,16 @@
         <v>162</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D163" s="5" t="s">
         <v>538</v>
       </c>
       <c r="E163" s="5">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F163" s="5" t="s">
         <v>24</v>
@@ -10615,7 +10619,7 @@
         <v>8</v>
       </c>
       <c r="L163" s="6" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="M163" s="6" t="s">
         <v>40</v>
@@ -10629,16 +10633,16 @@
         <v>163</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D164" s="5" t="s">
         <v>541</v>
       </c>
       <c r="E164" s="5">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F164" s="5" t="s">
         <v>24</v>
@@ -10653,16 +10657,16 @@
         <v>18</v>
       </c>
       <c r="J164" s="5">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K164" s="5">
         <v>8</v>
       </c>
       <c r="L164" s="6" t="s">
-        <v>527</v>
+        <v>544</v>
       </c>
       <c r="M164" s="6" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="N164" s="6" t="s">
         <v>18</v>
@@ -10673,25 +10677,25 @@
         <v>164</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E165" s="5">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F165" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G165" s="5" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H165" s="5" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="I165" s="5" t="s">
         <v>18</v>
@@ -10703,7 +10707,7 @@
         <v>8</v>
       </c>
       <c r="L165" s="6" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="M165" s="6" t="s">
         <v>54</v>
@@ -10717,16 +10721,16 @@
         <v>165</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D166" s="5" t="s">
         <v>548</v>
       </c>
       <c r="E166" s="5">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F166" s="5" t="s">
         <v>24</v>
@@ -10747,7 +10751,7 @@
         <v>8</v>
       </c>
       <c r="L166" s="6" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="M166" s="6" t="s">
         <v>54</v>
@@ -10761,16 +10765,16 @@
         <v>166</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D167" s="5" t="s">
         <v>551</v>
       </c>
       <c r="E167" s="5">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F167" s="5" t="s">
         <v>24</v>
@@ -10791,7 +10795,7 @@
         <v>8</v>
       </c>
       <c r="L167" s="6" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="M167" s="6" t="s">
         <v>54</v>
@@ -10805,16 +10809,16 @@
         <v>167</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D168" s="5" t="s">
         <v>554</v>
       </c>
       <c r="E168" s="5">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F168" s="5" t="s">
         <v>24</v>
@@ -10835,7 +10839,7 @@
         <v>8</v>
       </c>
       <c r="L168" s="6" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="M168" s="6" t="s">
         <v>54</v>
@@ -10849,16 +10853,16 @@
         <v>168</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D169" s="5" t="s">
         <v>557</v>
       </c>
       <c r="E169" s="5">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F169" s="5" t="s">
         <v>24</v>
@@ -10873,16 +10877,16 @@
         <v>18</v>
       </c>
       <c r="J169" s="5">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K169" s="5">
         <v>8</v>
       </c>
       <c r="L169" s="6" t="s">
-        <v>547</v>
+        <v>560</v>
       </c>
       <c r="M169" s="6" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="N169" s="6" t="s">
         <v>18</v>
@@ -10893,25 +10897,25 @@
         <v>169</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D170" s="5" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E170" s="5">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F170" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G170" s="5" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H170" s="5" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="I170" s="5" t="s">
         <v>18</v>
@@ -10923,7 +10927,7 @@
         <v>8</v>
       </c>
       <c r="L170" s="6" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="M170" s="6" t="s">
         <v>68</v>
@@ -10937,16 +10941,16 @@
         <v>170</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D171" s="5" t="s">
         <v>564</v>
       </c>
       <c r="E171" s="5">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F171" s="5" t="s">
         <v>24</v>
@@ -10955,7 +10959,7 @@
         <v>565</v>
       </c>
       <c r="H171" s="5" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="I171" s="5" t="s">
         <v>18</v>
@@ -10967,7 +10971,7 @@
         <v>8</v>
       </c>
       <c r="L171" s="6" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="M171" s="6" t="s">
         <v>68</v>
@@ -10981,25 +10985,25 @@
         <v>171</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D172" s="5" t="s">
+        <v>566</v>
+      </c>
+      <c r="E172" s="5">
+        <v>45</v>
+      </c>
+      <c r="F172" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G172" s="5" t="s">
         <v>567</v>
       </c>
-      <c r="E172" s="5">
-        <v>44</v>
-      </c>
-      <c r="F172" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G172" s="5" t="s">
+      <c r="H172" s="5" t="s">
         <v>568</v>
-      </c>
-      <c r="H172" s="5" t="s">
-        <v>566</v>
       </c>
       <c r="I172" s="5" t="s">
         <v>18</v>
@@ -11011,7 +11015,7 @@
         <v>8</v>
       </c>
       <c r="L172" s="6" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="M172" s="6" t="s">
         <v>68</v>
@@ -11020,48 +11024,48 @@
         <v>18</v>
       </c>
     </row>
-    <row r="173" ht="27.6" spans="1:14">
+    <row r="173" spans="1:14">
       <c r="A173" s="5">
         <v>172</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>426</v>
+        <v>569</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>524</v>
+        <v>570</v>
       </c>
       <c r="D173" s="5" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E173" s="5">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="F173" s="5" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G173" s="5" t="s">
-        <v>570</v>
+        <v>352</v>
       </c>
       <c r="H173" s="5" t="s">
-        <v>571</v>
+        <v>18</v>
       </c>
       <c r="I173" s="5" t="s">
-        <v>18</v>
+        <v>172</v>
       </c>
       <c r="J173" s="5">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K173" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L173" s="6" t="s">
-        <v>563</v>
+        <v>572</v>
       </c>
       <c r="M173" s="6" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="N173" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="174" spans="1:14">
@@ -11069,16 +11073,16 @@
         <v>173</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C174" s="5" t="s">
+        <v>570</v>
+      </c>
+      <c r="D174" s="5" t="s">
         <v>573</v>
       </c>
-      <c r="D174" s="5" t="s">
-        <v>574</v>
-      </c>
       <c r="E174" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F174" s="5" t="s">
         <v>16</v>
@@ -11090,7 +11094,7 @@
         <v>18</v>
       </c>
       <c r="I174" s="5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="J174" s="5">
         <v>40</v>
@@ -11099,7 +11103,7 @@
         <v>9</v>
       </c>
       <c r="L174" s="6" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="M174" s="6" t="s">
         <v>84</v>
@@ -11113,28 +11117,28 @@
         <v>174</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D175" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E175" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F175" s="5" t="s">
         <v>16</v>
       </c>
       <c r="G175" s="5" t="s">
-        <v>358</v>
+        <v>13</v>
       </c>
       <c r="H175" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I175" s="5" t="s">
-        <v>175</v>
+        <v>132</v>
       </c>
       <c r="J175" s="5">
         <v>40</v>
@@ -11143,7 +11147,7 @@
         <v>9</v>
       </c>
       <c r="L175" s="6" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="M175" s="6" t="s">
         <v>84</v>
@@ -11157,28 +11161,28 @@
         <v>175</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D176" s="5" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E176" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F176" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G176" s="5" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H176" s="5" t="s">
-        <v>18</v>
+        <v>576</v>
       </c>
       <c r="I176" s="5" t="s">
-        <v>132</v>
+        <v>18</v>
       </c>
       <c r="J176" s="5">
         <v>40</v>
@@ -11187,13 +11191,13 @@
         <v>9</v>
       </c>
       <c r="L176" s="6" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="M176" s="6" t="s">
         <v>84</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="177" spans="1:14">
@@ -11201,22 +11205,22 @@
         <v>176</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D177" s="5" t="s">
+        <v>577</v>
+      </c>
+      <c r="E177" s="5">
+        <v>5</v>
+      </c>
+      <c r="F177" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G177" s="5" t="s">
         <v>578</v>
-      </c>
-      <c r="E177" s="5">
-        <v>4</v>
-      </c>
-      <c r="F177" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G177" s="5" t="s">
-        <v>25</v>
       </c>
       <c r="H177" s="5" t="s">
         <v>579</v>
@@ -11231,7 +11235,7 @@
         <v>9</v>
       </c>
       <c r="L177" s="6" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="M177" s="6" t="s">
         <v>84</v>
@@ -11240,21 +11244,21 @@
         <v>18</v>
       </c>
     </row>
-    <row r="178" spans="1:14">
+    <row r="178" ht="27.6" spans="1:14">
       <c r="A178" s="5">
         <v>177</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D178" s="5" t="s">
         <v>580</v>
       </c>
       <c r="E178" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F178" s="5" t="s">
         <v>24</v>
@@ -11275,7 +11279,7 @@
         <v>9</v>
       </c>
       <c r="L178" s="6" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="M178" s="6" t="s">
         <v>84</v>
@@ -11284,21 +11288,21 @@
         <v>18</v>
       </c>
     </row>
-    <row r="179" ht="27.6" spans="1:14">
+    <row r="179" spans="1:14">
       <c r="A179" s="5">
         <v>178</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D179" s="5" t="s">
         <v>583</v>
       </c>
       <c r="E179" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F179" s="5" t="s">
         <v>24</v>
@@ -11319,7 +11323,7 @@
         <v>9</v>
       </c>
       <c r="L179" s="6" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="M179" s="6" t="s">
         <v>84</v>
@@ -11333,16 +11337,16 @@
         <v>179</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D180" s="5" t="s">
         <v>586</v>
       </c>
       <c r="E180" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F180" s="5" t="s">
         <v>24</v>
@@ -11357,16 +11361,16 @@
         <v>18</v>
       </c>
       <c r="J180" s="5">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K180" s="5">
         <v>9</v>
       </c>
       <c r="L180" s="6" t="s">
-        <v>575</v>
+        <v>589</v>
       </c>
       <c r="M180" s="6" t="s">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="N180" s="6" t="s">
         <v>18</v>
@@ -11377,25 +11381,25 @@
         <v>180</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D181" s="5" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E181" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F181" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G181" s="5" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H181" s="5" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="I181" s="5" t="s">
         <v>18</v>
@@ -11407,7 +11411,7 @@
         <v>9</v>
       </c>
       <c r="L181" s="6" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="M181" s="6" t="s">
         <v>21</v>
@@ -11421,16 +11425,16 @@
         <v>181</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D182" s="5" t="s">
         <v>593</v>
       </c>
       <c r="E182" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F182" s="5" t="s">
         <v>24</v>
@@ -11451,7 +11455,7 @@
         <v>9</v>
       </c>
       <c r="L182" s="6" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="M182" s="6" t="s">
         <v>21</v>
@@ -11465,16 +11469,16 @@
         <v>182</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D183" s="5" t="s">
         <v>596</v>
       </c>
       <c r="E183" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F183" s="5" t="s">
         <v>24</v>
@@ -11495,7 +11499,7 @@
         <v>9</v>
       </c>
       <c r="L183" s="6" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="M183" s="6" t="s">
         <v>21</v>
@@ -11509,16 +11513,16 @@
         <v>183</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D184" s="5" t="s">
         <v>599</v>
       </c>
       <c r="E184" s="5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F184" s="5" t="s">
         <v>24</v>
@@ -11533,16 +11537,16 @@
         <v>18</v>
       </c>
       <c r="J184" s="5">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K184" s="5">
         <v>9</v>
       </c>
       <c r="L184" s="6" t="s">
-        <v>592</v>
+        <v>602</v>
       </c>
       <c r="M184" s="6" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="N184" s="6" t="s">
         <v>18</v>
@@ -11553,25 +11557,25 @@
         <v>184</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D185" s="5" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E185" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F185" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G185" s="5" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H185" s="5" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="I185" s="5" t="s">
         <v>18</v>
@@ -11583,7 +11587,7 @@
         <v>9</v>
       </c>
       <c r="L185" s="6" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="M185" s="6" t="s">
         <v>40</v>
@@ -11597,16 +11601,16 @@
         <v>185</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D186" s="5" t="s">
         <v>606</v>
       </c>
       <c r="E186" s="5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F186" s="5" t="s">
         <v>24</v>
@@ -11627,7 +11631,7 @@
         <v>9</v>
       </c>
       <c r="L186" s="6" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="M186" s="6" t="s">
         <v>40</v>
@@ -11641,16 +11645,16 @@
         <v>186</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D187" s="5" t="s">
         <v>609</v>
       </c>
       <c r="E187" s="5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F187" s="5" t="s">
         <v>24</v>
@@ -11671,7 +11675,7 @@
         <v>9</v>
       </c>
       <c r="L187" s="6" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="M187" s="6" t="s">
         <v>40</v>
@@ -11685,16 +11689,16 @@
         <v>187</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D188" s="5" t="s">
         <v>612</v>
       </c>
       <c r="E188" s="5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F188" s="5" t="s">
         <v>24</v>
@@ -11709,16 +11713,16 @@
         <v>18</v>
       </c>
       <c r="J188" s="5">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K188" s="5">
         <v>9</v>
       </c>
       <c r="L188" s="6" t="s">
-        <v>605</v>
+        <v>615</v>
       </c>
       <c r="M188" s="6" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="N188" s="6" t="s">
         <v>18</v>
@@ -11729,25 +11733,25 @@
         <v>188</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D189" s="5" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E189" s="5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F189" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G189" s="5" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H189" s="5" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="I189" s="5" t="s">
         <v>18</v>
@@ -11759,7 +11763,7 @@
         <v>9</v>
       </c>
       <c r="L189" s="6" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="M189" s="6" t="s">
         <v>54</v>
@@ -11773,16 +11777,16 @@
         <v>189</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D190" s="5" t="s">
         <v>619</v>
       </c>
       <c r="E190" s="5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F190" s="5" t="s">
         <v>24</v>
@@ -11803,7 +11807,7 @@
         <v>9</v>
       </c>
       <c r="L190" s="6" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="M190" s="6" t="s">
         <v>54</v>
@@ -11817,16 +11821,16 @@
         <v>190</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D191" s="5" t="s">
         <v>622</v>
       </c>
       <c r="E191" s="5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F191" s="5" t="s">
         <v>24</v>
@@ -11847,7 +11851,7 @@
         <v>9</v>
       </c>
       <c r="L191" s="6" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="M191" s="6" t="s">
         <v>54</v>
@@ -11861,16 +11865,16 @@
         <v>191</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D192" s="5" t="s">
         <v>625</v>
       </c>
       <c r="E192" s="5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F192" s="5" t="s">
         <v>24</v>
@@ -11885,16 +11889,16 @@
         <v>18</v>
       </c>
       <c r="J192" s="5">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K192" s="5">
         <v>9</v>
       </c>
       <c r="L192" s="6" t="s">
-        <v>618</v>
+        <v>628</v>
       </c>
       <c r="M192" s="6" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="N192" s="6" t="s">
         <v>18</v>
@@ -11905,25 +11909,25 @@
         <v>192</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D193" s="5" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E193" s="5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F193" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G193" s="5" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H193" s="5" t="s">
-        <v>630</v>
+        <v>193</v>
       </c>
       <c r="I193" s="5" t="s">
         <v>18</v>
@@ -11935,7 +11939,7 @@
         <v>9</v>
       </c>
       <c r="L193" s="6" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="M193" s="6" t="s">
         <v>68</v>
@@ -11949,25 +11953,25 @@
         <v>193</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D194" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="E194" s="5">
+        <v>22</v>
+      </c>
+      <c r="F194" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G194" s="5" t="s">
         <v>632</v>
       </c>
-      <c r="E194" s="5">
-        <v>21</v>
-      </c>
-      <c r="F194" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G194" s="5" t="s">
+      <c r="H194" s="5" t="s">
         <v>633</v>
-      </c>
-      <c r="H194" s="5" t="s">
-        <v>196</v>
       </c>
       <c r="I194" s="5" t="s">
         <v>18</v>
@@ -11979,7 +11983,7 @@
         <v>9</v>
       </c>
       <c r="L194" s="6" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="M194" s="6" t="s">
         <v>68</v>
@@ -11993,16 +11997,16 @@
         <v>194</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D195" s="5" t="s">
         <v>634</v>
       </c>
       <c r="E195" s="5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F195" s="5" t="s">
         <v>24</v>
@@ -12023,7 +12027,7 @@
         <v>9</v>
       </c>
       <c r="L195" s="6" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="M195" s="6" t="s">
         <v>68</v>
@@ -12037,16 +12041,16 @@
         <v>195</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D196" s="5" t="s">
         <v>637</v>
       </c>
       <c r="E196" s="5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F196" s="5" t="s">
         <v>24</v>
@@ -12061,16 +12065,16 @@
         <v>18</v>
       </c>
       <c r="J196" s="5">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K196" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L196" s="6" t="s">
-        <v>631</v>
+        <v>640</v>
       </c>
       <c r="M196" s="6" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="N196" s="6" t="s">
         <v>18</v>
@@ -12081,25 +12085,25 @@
         <v>196</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D197" s="5" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="E197" s="5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F197" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G197" s="5" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H197" s="5" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="I197" s="5" t="s">
         <v>18</v>
@@ -12111,7 +12115,7 @@
         <v>10</v>
       </c>
       <c r="L197" s="6" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="M197" s="6" t="s">
         <v>84</v>
@@ -12125,16 +12129,16 @@
         <v>197</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D198" s="5" t="s">
         <v>644</v>
       </c>
       <c r="E198" s="5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F198" s="5" t="s">
         <v>24</v>
@@ -12155,7 +12159,7 @@
         <v>10</v>
       </c>
       <c r="L198" s="6" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="M198" s="6" t="s">
         <v>84</v>
@@ -12169,16 +12173,16 @@
         <v>198</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D199" s="5" t="s">
         <v>647</v>
       </c>
       <c r="E199" s="5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F199" s="5" t="s">
         <v>24</v>
@@ -12199,7 +12203,7 @@
         <v>10</v>
       </c>
       <c r="L199" s="6" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="M199" s="6" t="s">
         <v>84</v>
@@ -12213,16 +12217,16 @@
         <v>199</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D200" s="5" t="s">
         <v>650</v>
       </c>
       <c r="E200" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F200" s="5" t="s">
         <v>24</v>
@@ -12237,16 +12241,16 @@
         <v>18</v>
       </c>
       <c r="J200" s="5">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K200" s="5">
         <v>10</v>
       </c>
       <c r="L200" s="6" t="s">
-        <v>643</v>
+        <v>653</v>
       </c>
       <c r="M200" s="6" t="s">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="N200" s="6" t="s">
         <v>18</v>
@@ -12257,25 +12261,25 @@
         <v>200</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D201" s="5" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E201" s="5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F201" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G201" s="5" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H201" s="5" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="I201" s="5" t="s">
         <v>18</v>
@@ -12287,7 +12291,7 @@
         <v>10</v>
       </c>
       <c r="L201" s="6" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="M201" s="6" t="s">
         <v>21</v>
@@ -12301,16 +12305,16 @@
         <v>201</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D202" s="5" t="s">
         <v>657</v>
       </c>
       <c r="E202" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F202" s="5" t="s">
         <v>24</v>
@@ -12331,7 +12335,7 @@
         <v>10</v>
       </c>
       <c r="L202" s="6" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="M202" s="6" t="s">
         <v>21</v>
@@ -12345,25 +12349,25 @@
         <v>202</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D203" s="5" t="s">
         <v>660</v>
       </c>
       <c r="E203" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F203" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G203" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="H203" s="5" t="s">
         <v>661</v>
-      </c>
-      <c r="H203" s="5" t="s">
-        <v>662</v>
       </c>
       <c r="I203" s="5" t="s">
         <v>18</v>
@@ -12375,7 +12379,7 @@
         <v>10</v>
       </c>
       <c r="L203" s="6" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="M203" s="6" t="s">
         <v>21</v>
@@ -12389,40 +12393,40 @@
         <v>203</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>572</v>
+        <v>662</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>573</v>
+        <v>663</v>
       </c>
       <c r="D204" s="5" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E204" s="5">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="F204" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G204" s="5" t="s">
-        <v>73</v>
+        <v>665</v>
       </c>
       <c r="H204" s="5" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="I204" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J204" s="5">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K204" s="5">
         <v>10</v>
       </c>
       <c r="L204" s="6" t="s">
-        <v>656</v>
+        <v>667</v>
       </c>
       <c r="M204" s="6" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="N204" s="6" t="s">
         <v>18</v>
@@ -12433,25 +12437,25 @@
         <v>204</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="D205" s="5" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="E205" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F205" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G205" s="5" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H205" s="5" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="I205" s="5" t="s">
         <v>18</v>
@@ -12463,7 +12467,7 @@
         <v>10</v>
       </c>
       <c r="L205" s="6" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="M205" s="6" t="s">
         <v>40</v>
@@ -12477,16 +12481,16 @@
         <v>205</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="D206" s="5" t="s">
         <v>671</v>
       </c>
       <c r="E206" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F206" s="5" t="s">
         <v>24</v>
@@ -12507,7 +12511,7 @@
         <v>10</v>
       </c>
       <c r="L206" s="6" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="M206" s="6" t="s">
         <v>40</v>
@@ -12521,16 +12525,16 @@
         <v>206</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="D207" s="5" t="s">
         <v>674</v>
       </c>
       <c r="E207" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F207" s="5" t="s">
         <v>24</v>
@@ -12551,7 +12555,7 @@
         <v>10</v>
       </c>
       <c r="L207" s="6" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="M207" s="6" t="s">
         <v>40</v>
@@ -12565,16 +12569,16 @@
         <v>207</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="D208" s="5" t="s">
         <v>677</v>
       </c>
       <c r="E208" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F208" s="5" t="s">
         <v>24</v>
@@ -12589,16 +12593,16 @@
         <v>18</v>
       </c>
       <c r="J208" s="5">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K208" s="5">
         <v>10</v>
       </c>
       <c r="L208" s="6" t="s">
-        <v>670</v>
+        <v>680</v>
       </c>
       <c r="M208" s="6" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="N208" s="6" t="s">
         <v>18</v>
@@ -12609,25 +12613,25 @@
         <v>208</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="D209" s="5" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="E209" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F209" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G209" s="5" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H209" s="5" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="I209" s="5" t="s">
         <v>18</v>
@@ -12639,7 +12643,7 @@
         <v>10</v>
       </c>
       <c r="L209" s="6" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="M209" s="6" t="s">
         <v>54</v>
@@ -12653,16 +12657,16 @@
         <v>209</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="D210" s="5" t="s">
         <v>684</v>
       </c>
       <c r="E210" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F210" s="5" t="s">
         <v>24</v>
@@ -12683,7 +12687,7 @@
         <v>10</v>
       </c>
       <c r="L210" s="6" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="M210" s="6" t="s">
         <v>54</v>
@@ -12697,16 +12701,16 @@
         <v>210</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="D211" s="5" t="s">
         <v>687</v>
       </c>
       <c r="E211" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F211" s="5" t="s">
         <v>24</v>
@@ -12727,7 +12731,7 @@
         <v>10</v>
       </c>
       <c r="L211" s="6" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="M211" s="6" t="s">
         <v>54</v>
@@ -12741,16 +12745,16 @@
         <v>211</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="D212" s="5" t="s">
         <v>690</v>
       </c>
       <c r="E212" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F212" s="5" t="s">
         <v>24</v>
@@ -12765,16 +12769,16 @@
         <v>18</v>
       </c>
       <c r="J212" s="5">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K212" s="5">
         <v>10</v>
       </c>
       <c r="L212" s="6" t="s">
-        <v>683</v>
+        <v>693</v>
       </c>
       <c r="M212" s="6" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="N212" s="6" t="s">
         <v>18</v>
@@ -12785,25 +12789,25 @@
         <v>212</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="D213" s="5" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E213" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F213" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G213" s="5" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H213" s="5" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="I213" s="5" t="s">
         <v>18</v>
@@ -12815,7 +12819,7 @@
         <v>10</v>
       </c>
       <c r="L213" s="6" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="M213" s="6" t="s">
         <v>68</v>
@@ -12829,16 +12833,16 @@
         <v>213</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="D214" s="5" t="s">
         <v>697</v>
       </c>
       <c r="E214" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F214" s="5" t="s">
         <v>24</v>
@@ -12859,7 +12863,7 @@
         <v>10</v>
       </c>
       <c r="L214" s="6" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="M214" s="6" t="s">
         <v>68</v>
@@ -12873,16 +12877,16 @@
         <v>214</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="D215" s="5" t="s">
         <v>700</v>
       </c>
       <c r="E215" s="5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F215" s="5" t="s">
         <v>24</v>
@@ -12903,7 +12907,7 @@
         <v>10</v>
       </c>
       <c r="L215" s="6" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="M215" s="6" t="s">
         <v>68</v>
@@ -12917,16 +12921,16 @@
         <v>215</v>
       </c>
       <c r="B216" s="5" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="D216" s="5" t="s">
         <v>703</v>
       </c>
       <c r="E216" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F216" s="5" t="s">
         <v>24</v>
@@ -12941,16 +12945,16 @@
         <v>18</v>
       </c>
       <c r="J216" s="5">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K216" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L216" s="6" t="s">
-        <v>696</v>
+        <v>706</v>
       </c>
       <c r="M216" s="6" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="N216" s="6" t="s">
         <v>18</v>
@@ -12961,25 +12965,25 @@
         <v>216</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="D217" s="5" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="E217" s="5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F217" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G217" s="5" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H217" s="5" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="I217" s="5" t="s">
         <v>18</v>
@@ -12991,7 +12995,7 @@
         <v>11</v>
       </c>
       <c r="L217" s="6" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="M217" s="6" t="s">
         <v>84</v>
@@ -13005,16 +13009,16 @@
         <v>217</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="D218" s="5" t="s">
         <v>710</v>
       </c>
       <c r="E218" s="5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F218" s="5" t="s">
         <v>24</v>
@@ -13035,7 +13039,7 @@
         <v>11</v>
       </c>
       <c r="L218" s="6" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="M218" s="6" t="s">
         <v>84</v>
@@ -13049,16 +13053,16 @@
         <v>218</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="D219" s="5" t="s">
         <v>713</v>
       </c>
       <c r="E219" s="5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F219" s="5" t="s">
         <v>24</v>
@@ -13079,7 +13083,7 @@
         <v>11</v>
       </c>
       <c r="L219" s="6" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="M219" s="6" t="s">
         <v>84</v>
@@ -13093,16 +13097,16 @@
         <v>219</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="D220" s="5" t="s">
         <v>716</v>
       </c>
       <c r="E220" s="5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F220" s="5" t="s">
         <v>24</v>
@@ -13117,16 +13121,16 @@
         <v>18</v>
       </c>
       <c r="J220" s="5">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K220" s="5">
         <v>11</v>
       </c>
       <c r="L220" s="6" t="s">
-        <v>709</v>
+        <v>719</v>
       </c>
       <c r="M220" s="6" t="s">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="N220" s="6" t="s">
         <v>18</v>
@@ -13137,25 +13141,25 @@
         <v>220</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="D221" s="5" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E221" s="5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F221" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G221" s="5" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H221" s="5" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="I221" s="5" t="s">
         <v>18</v>
@@ -13167,7 +13171,7 @@
         <v>11</v>
       </c>
       <c r="L221" s="6" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="M221" s="6" t="s">
         <v>21</v>
@@ -13181,16 +13185,16 @@
         <v>221</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="D222" s="5" t="s">
         <v>723</v>
       </c>
       <c r="E222" s="5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F222" s="5" t="s">
         <v>24</v>
@@ -13211,7 +13215,7 @@
         <v>11</v>
       </c>
       <c r="L222" s="6" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="M222" s="6" t="s">
         <v>21</v>
@@ -13220,30 +13224,30 @@
         <v>18</v>
       </c>
     </row>
-    <row r="223" spans="1:14">
+    <row r="223" ht="14.4" spans="1:14">
       <c r="A223" s="5">
         <v>222</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="D223" s="5" t="s">
         <v>726</v>
       </c>
       <c r="E223" s="5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F223" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G223" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="H223" s="9" t="s">
         <v>727</v>
-      </c>
-      <c r="H223" s="5" t="s">
-        <v>728</v>
       </c>
       <c r="I223" s="5" t="s">
         <v>18</v>
@@ -13255,56 +13259,53 @@
         <v>11</v>
       </c>
       <c r="L223" s="6" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="M223" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="N223" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="224" ht="14.4" spans="1:14">
-      <c r="A224" s="5">
+      <c r="N223" s="6"/>
+    </row>
+    <row r="224" spans="1:14">
+      <c r="A224">
         <v>223</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>665</v>
-      </c>
-      <c r="C224" s="5" t="s">
-        <v>666</v>
-      </c>
-      <c r="D224" s="5" t="s">
+        <v>728</v>
+      </c>
+      <c r="C224" t="s">
+        <v>728</v>
+      </c>
+      <c r="D224" t="s">
         <v>729</v>
       </c>
-      <c r="E224" s="5">
-        <v>20</v>
-      </c>
-      <c r="F224" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G224" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="H224" s="9" t="s">
+      <c r="E224">
+        <v>21</v>
+      </c>
+      <c r="F224" t="s">
+        <v>16</v>
+      </c>
+      <c r="G224" t="s">
+        <v>728</v>
+      </c>
+      <c r="I224" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="J224">
+        <v>52</v>
+      </c>
+      <c r="K224">
+        <v>11</v>
+      </c>
+      <c r="L224" s="6" t="s">
         <v>730</v>
       </c>
-      <c r="I224" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J224" s="5">
-        <v>51</v>
-      </c>
-      <c r="K224" s="5">
-        <v>11</v>
-      </c>
-      <c r="L224" s="6" t="s">
-        <v>722</v>
-      </c>
       <c r="M224" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="N224" s="6"/>
+        <v>40</v>
+      </c>
+      <c r="N224" s="6" t="s">
+        <v>22</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -13313,7 +13314,7 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="H224" r:id="rId2" display="https://youtu.be/LZWTeYXzAO8"/>
+    <hyperlink ref="H223" r:id="rId2" display="https://youtu.be/LZWTeYXzAO8"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -13454,7 +13455,7 @@
         <v>746</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -13629,16 +13630,16 @@
         <v>765</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>73</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>766</v>
@@ -13729,16 +13730,16 @@
         <v>767</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>75</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>770</v>
@@ -13749,16 +13750,16 @@
         <v>767</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>75</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>403</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>406</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>771</v>

--- a/data/OVTech Master Curriculum.xlsx
+++ b/data/OVTech Master Curriculum.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="23040" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="Master Curriculum" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2326" uniqueCount="772">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2334" uniqueCount="779">
   <si>
     <t>Global Order</t>
   </si>
@@ -611,1318 +611,1339 @@
     <t>MIN &amp; MAX Functions</t>
   </si>
   <si>
+    <t>https://youtu.be/hxE38JqGgNY</t>
+  </si>
+  <si>
+    <t>EX038</t>
+  </si>
+  <si>
+    <t>Average &amp; AverageIF Functions</t>
+  </si>
+  <si>
+    <t>https://youtu.be/fzYS1quf1VQ</t>
+  </si>
+  <si>
+    <t>2026-07-23</t>
+  </si>
+  <si>
+    <t>EX039</t>
+  </si>
+  <si>
+    <t>IF Statement</t>
+  </si>
+  <si>
+    <t>https://youtu.be/9--5M-g9VBU</t>
+  </si>
+  <si>
+    <t>EX040</t>
+  </si>
+  <si>
+    <t>Mini-Project 2 Pt.1</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=0S7bBiSypDM</t>
+  </si>
+  <si>
+    <t>EX041</t>
+  </si>
+  <si>
+    <t>Mini-Project  2 Pt. 2</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=27BZOkUCB9Q</t>
+  </si>
+  <si>
+    <t>EX042</t>
+  </si>
+  <si>
+    <t>Mini-Project 2 Pt. 3</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=CkK5Pw363m4</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>Data Validation, Lookup &amp; Mini Project 3</t>
+  </si>
+  <si>
+    <t>EX-RES043</t>
+  </si>
+  <si>
+    <t>Mini Project 3</t>
+  </si>
+  <si>
+    <t>EX044</t>
+  </si>
+  <si>
+    <t>Data Validation Pt.1</t>
+  </si>
+  <si>
+    <t>https://youtu.be/XPxhNhJ6BsU</t>
+  </si>
+  <si>
+    <t>EX045</t>
+  </si>
+  <si>
+    <t>Data Validation Pt.2</t>
+  </si>
+  <si>
+    <t>https://youtu.be/XrIpwJDB9y8</t>
+  </si>
+  <si>
+    <t>EX046</t>
+  </si>
+  <si>
+    <t>Data Validation Pt.3</t>
+  </si>
+  <si>
+    <t>https://youtu.be/uOIOAwxUBxk</t>
+  </si>
+  <si>
+    <t>EX047</t>
+  </si>
+  <si>
+    <t>Data Validation Pt.4</t>
+  </si>
+  <si>
+    <t>https://youtu.be/3AAFOsDv98o</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>EX048</t>
+  </si>
+  <si>
+    <t>VLOOKUP Function</t>
+  </si>
+  <si>
+    <t>https://youtu.be/uC-eSdiBVrw</t>
+  </si>
+  <si>
+    <t>EX049</t>
+  </si>
+  <si>
+    <t>XLOOKUP Function</t>
+  </si>
+  <si>
+    <t>https://youtu.be/fkIgEH5quCo</t>
+  </si>
+  <si>
+    <t>EX050</t>
+  </si>
+  <si>
+    <t>Text Function</t>
+  </si>
+  <si>
+    <t>https://youtu.be/mu-SFVrdHNI</t>
+  </si>
+  <si>
+    <t>EX051</t>
+  </si>
+  <si>
+    <t>Left &amp; Right Functions</t>
+  </si>
+  <si>
+    <t>https://youtu.be/ddtOXCH6T4o</t>
+  </si>
+  <si>
+    <t>2026-07-28</t>
+  </si>
+  <si>
+    <t>EX052</t>
+  </si>
+  <si>
+    <t>LEN Function</t>
+  </si>
+  <si>
+    <t>https://youtu.be/K7KAsbX-y2g</t>
+  </si>
+  <si>
+    <t>EX053</t>
+  </si>
+  <si>
+    <t>MID Function</t>
+  </si>
+  <si>
+    <t>https://youtu.be/SGRCa2DBijg</t>
+  </si>
+  <si>
+    <t>EX054</t>
+  </si>
+  <si>
+    <t>Date Function</t>
+  </si>
+  <si>
+    <t>https://youtu.be/jNd5Lr4N0S8</t>
+  </si>
+  <si>
+    <t>EX055</t>
+  </si>
+  <si>
+    <t>DATEDIF Function</t>
+  </si>
+  <si>
+    <t>https://youtu.be/I3EzGZzQ7YY</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>EX056</t>
+  </si>
+  <si>
+    <t>Text Functions</t>
+  </si>
+  <si>
+    <t>https://youtu.be/j5qOiGC8qjc</t>
+  </si>
+  <si>
+    <t>EX057</t>
+  </si>
+  <si>
+    <t>Unique Function</t>
+  </si>
+  <si>
+    <t>https://youtu.be/wc_50NXb9zs</t>
+  </si>
+  <si>
+    <t>EX058</t>
+  </si>
+  <si>
+    <t>Sort Function</t>
+  </si>
+  <si>
+    <t>https://youtu.be/fnfnwRaCxPM</t>
+  </si>
+  <si>
+    <t>EX059</t>
+  </si>
+  <si>
+    <t>Mini-Project3 Pt.1</t>
+  </si>
+  <si>
+    <t>https://youtu.be/uqyCNJxiZuM</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>EX060</t>
+  </si>
+  <si>
+    <t>Mini-Project 3 Pt. 2</t>
+  </si>
+  <si>
+    <t>https://youtu.be/o3yAAR_GnQ0</t>
+  </si>
+  <si>
+    <t>EX061</t>
+  </si>
+  <si>
+    <t>Mini-Project 3 Pt.3</t>
+  </si>
+  <si>
+    <t>https://youtu.be/lWPpUuhChSQ</t>
+  </si>
+  <si>
+    <t>EX062</t>
+  </si>
+  <si>
+    <t>Mini-Project 3 Pt.4</t>
+  </si>
+  <si>
+    <t>https://youtu.be/fAVoxFWbuTM</t>
+  </si>
+  <si>
+    <t>Statistical Functions</t>
+  </si>
+  <si>
+    <t>EX063</t>
+  </si>
+  <si>
+    <t>Statistical Functions (Median)</t>
+  </si>
+  <si>
+    <t>https://youtu.be/LMTwjVLThtI</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>EX064</t>
+  </si>
+  <si>
+    <t>Statistical Functions (Mode)</t>
+  </si>
+  <si>
+    <t>https://youtu.be/qJgX6B6TVjk</t>
+  </si>
+  <si>
+    <t>EX065</t>
+  </si>
+  <si>
+    <t>Standard Deviation</t>
+  </si>
+  <si>
+    <t>https://youtu.be/BmL5K4_U2Fg</t>
+  </si>
+  <si>
+    <t>EX066</t>
+  </si>
+  <si>
+    <t>Quartiles</t>
+  </si>
+  <si>
+    <t>https://youtu.be/khShX87eH5Q</t>
+  </si>
+  <si>
+    <t>Logical Functions &amp; Mini Project 4</t>
+  </si>
+  <si>
+    <t>EX-RES067</t>
+  </si>
+  <si>
+    <t>Excel Mini-Project 4 Dataset</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>EX-RES068</t>
+  </si>
+  <si>
+    <t>Excel Mini-Project 4</t>
+  </si>
+  <si>
+    <t>EX069</t>
+  </si>
+  <si>
+    <t>Ampersand Operator</t>
+  </si>
+  <si>
+    <t>https://youtu.be/cQdMqFXnrsg</t>
+  </si>
+  <si>
+    <t>EX070</t>
+  </si>
+  <si>
+    <t>Comparison Operator</t>
+  </si>
+  <si>
+    <t>https://youtu.be/-L32oCBfauE</t>
+  </si>
+  <si>
+    <t>EX071</t>
+  </si>
+  <si>
+    <t>Logical Operators</t>
+  </si>
+  <si>
+    <t>https://youtu.be/-PsBiHH8awA</t>
+  </si>
+  <si>
+    <t>EX072</t>
+  </si>
+  <si>
+    <t>Conditional Functions (IF &amp; IFS)</t>
+  </si>
+  <si>
+    <t>EX073</t>
+  </si>
+  <si>
+    <t>Mini-Project4 Pt.1</t>
+  </si>
+  <si>
+    <t>https://youtu.be/_vihyE0YXHQ</t>
+  </si>
+  <si>
+    <t>2026-08-04</t>
+  </si>
+  <si>
+    <t>EX074</t>
+  </si>
+  <si>
+    <t>Mini-Project4 Pt.2</t>
+  </si>
+  <si>
+    <t>https://youtu.be/vOyvkf0Eg2k</t>
+  </si>
+  <si>
+    <t>EX075</t>
+  </si>
+  <si>
+    <t>Mini-Project4 Pt.3</t>
+  </si>
+  <si>
+    <t>https://youtu.be/DMNUewivrjA</t>
+  </si>
+  <si>
+    <t>EX076</t>
+  </si>
+  <si>
+    <t>Mini-Project4 Pt.4</t>
+  </si>
+  <si>
+    <t>Excel Tables</t>
+  </si>
+  <si>
+    <t>EX-RES077</t>
+  </si>
+  <si>
+    <t>list_of_countries_and_dependencies</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>EX078</t>
+  </si>
+  <si>
+    <t>Adding Tables</t>
+  </si>
+  <si>
+    <t>https://youtu.be/4oIp_G9v7ZA</t>
+  </si>
+  <si>
+    <t>EX079</t>
+  </si>
+  <si>
+    <t>Table Management</t>
+  </si>
+  <si>
+    <t>https://youtu.be/OK-vnknXdOY</t>
+  </si>
+  <si>
+    <t>EX080</t>
+  </si>
+  <si>
+    <t>Table Filters</t>
+  </si>
+  <si>
+    <t>https://youtu.be/O7f3C5Phx3M</t>
+  </si>
+  <si>
+    <t>EX081</t>
+  </si>
+  <si>
+    <t>Pivot Table</t>
+  </si>
+  <si>
+    <t>https://youtu.be/n3qc2RFQbAY</t>
+  </si>
+  <si>
+    <t>Excel Charts</t>
+  </si>
+  <si>
+    <t>EX082</t>
+  </si>
+  <si>
+    <t>https://youtu.be/xq-mLouC4Lw</t>
+  </si>
+  <si>
+    <t>2026-08-06</t>
+  </si>
+  <si>
+    <t>EX083</t>
+  </si>
+  <si>
+    <t>Chart Types</t>
+  </si>
+  <si>
+    <t>https://youtu.be/JWOObDjlFpc</t>
+  </si>
+  <si>
+    <t>EX084</t>
+  </si>
+  <si>
+    <t>Sparklines</t>
+  </si>
+  <si>
+    <t>https://youtu.be/lE-z17LYIDA</t>
+  </si>
+  <si>
+    <t>EX085</t>
+  </si>
+  <si>
+    <t>Pivot Chart</t>
+  </si>
+  <si>
+    <t>https://youtu.be/wtESKgTVu0c</t>
+  </si>
+  <si>
+    <t>EX086</t>
+  </si>
+  <si>
+    <t>Conditional Formatting Pt.1</t>
+  </si>
+  <si>
+    <t>https://youtu.be/-SjF_f-_Mes</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>EX087</t>
+  </si>
+  <si>
+    <t>Conditional Formatting Pt.2</t>
+  </si>
+  <si>
+    <t>https://youtu.be/G4k7ikIPWFc</t>
+  </si>
+  <si>
+    <t>Power Query</t>
+  </si>
+  <si>
+    <t>PQ-RES001</t>
+  </si>
+  <si>
+    <t>films</t>
+  </si>
+  <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>PQ-RES002</t>
+  </si>
+  <si>
+    <t>movie_ratings</t>
+  </si>
+  <si>
+    <t>PQ003</t>
+  </si>
+  <si>
+    <t>Introduction to Power Query</t>
+  </si>
+  <si>
+    <t>https://youtu.be/9bht65Qv9Q0</t>
+  </si>
+  <si>
+    <t>PQ004</t>
+  </si>
+  <si>
+    <t>Accessing Power Query</t>
+  </si>
+  <si>
+    <t>https://youtu.be/OfzMv4csB4M</t>
+  </si>
+  <si>
+    <t>PQ005</t>
+  </si>
+  <si>
+    <t>Reduce Rows Section</t>
+  </si>
+  <si>
+    <t>https://youtu.be/St8pQ6rkJ5Y</t>
+  </si>
+  <si>
+    <t>PQ006</t>
+  </si>
+  <si>
+    <t>Manage Columns</t>
+  </si>
+  <si>
+    <t>https://youtu.be/7d6h1stqUVI</t>
+  </si>
+  <si>
+    <t>PQ007</t>
+  </si>
+  <si>
+    <t>Conditional Columns</t>
+  </si>
+  <si>
+    <t>https://youtu.be/IIzoiGgQh9M</t>
+  </si>
+  <si>
+    <t>2026-08-11</t>
+  </si>
+  <si>
+    <t>PQ008</t>
+  </si>
+  <si>
+    <t>Creating Index Columns</t>
+  </si>
+  <si>
+    <t>https://youtu.be/u4vHsVY6iWg</t>
+  </si>
+  <si>
+    <t>PQ009</t>
+  </si>
+  <si>
+    <t>Power Query Home Tab</t>
+  </si>
+  <si>
+    <t>https://youtu.be/y-g2-xv1wi4</t>
+  </si>
+  <si>
+    <t>PQ010</t>
+  </si>
+  <si>
+    <t>Power Query Transform Tab</t>
+  </si>
+  <si>
+    <t>https://youtu.be/GPCDungCTK8</t>
+  </si>
+  <si>
+    <t>PQ011</t>
+  </si>
+  <si>
+    <t>Close and Load</t>
+  </si>
+  <si>
+    <t>https://youtu.be/o1QVywo65fU</t>
+  </si>
+  <si>
+    <t>2026-08-12</t>
+  </si>
+  <si>
+    <t>PQ012</t>
+  </si>
+  <si>
+    <t>External Data Source (Web)</t>
+  </si>
+  <si>
+    <t>https://youtu.be/7PEovlMLfN4</t>
+  </si>
+  <si>
+    <t>PQ013</t>
+  </si>
+  <si>
+    <t>Merging Queries Pt.1</t>
+  </si>
+  <si>
+    <t>https://youtu.be/53qoq8gTmEw</t>
+  </si>
+  <si>
+    <t>PQ014</t>
+  </si>
+  <si>
+    <t>Merging Queries Pt.2</t>
+  </si>
+  <si>
+    <t>https://youtu.be/rs1O1Q0AZrU</t>
+  </si>
+  <si>
+    <t>Excel Final Project</t>
+  </si>
+  <si>
+    <t>EX-RES088</t>
+  </si>
+  <si>
+    <t>Excel Final Project Dataset</t>
+  </si>
+  <si>
+    <t>2026-08-13</t>
+  </si>
+  <si>
+    <t>EX-RES089</t>
+  </si>
+  <si>
+    <t>EX090</t>
+  </si>
+  <si>
+    <t>Data Protection</t>
+  </si>
+  <si>
+    <t>https://youtu.be/yRL09ge6UvY</t>
+  </si>
+  <si>
+    <t>EX091</t>
+  </si>
+  <si>
+    <t>https://youtu.be/i7Chd1Fne9k</t>
+  </si>
+  <si>
+    <t>EX092</t>
+  </si>
+  <si>
+    <t>Sharing Your Project</t>
+  </si>
+  <si>
+    <t>https://youtu.be/-2s7B3T4ZBw</t>
+  </si>
+  <si>
+    <t>EX093</t>
+  </si>
+  <si>
+    <t>Excel Add-ins</t>
+  </si>
+  <si>
+    <t>https://youtu.be/WLFAy_4rCvA</t>
+  </si>
+  <si>
+    <t>EX094</t>
+  </si>
+  <si>
+    <t>Final Project Pt.1</t>
+  </si>
+  <si>
+    <t>https://youtu.be/bjD7oT2h64Q</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
+  </si>
+  <si>
+    <t>EX095</t>
+  </si>
+  <si>
+    <t>Final Project Pt.2</t>
+  </si>
+  <si>
+    <t>https://youtu.be/p7zCOb5rqHQ</t>
+  </si>
+  <si>
+    <t>EX096</t>
+  </si>
+  <si>
+    <t>Final Project Pt.3</t>
+  </si>
+  <si>
+    <t>https://youtu.be/0HlrW6M_Y_A</t>
+  </si>
+  <si>
+    <t>EX097</t>
+  </si>
+  <si>
+    <t>Final Project Pt.4</t>
+  </si>
+  <si>
+    <t>https://youtu.be/KqqP9gCVt3k</t>
+  </si>
+  <si>
+    <t>Power BI</t>
+  </si>
+  <si>
+    <t>Power BI Basics</t>
+  </si>
+  <si>
+    <t>PB001</t>
+  </si>
+  <si>
+    <t>Course Introduction</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Xa6ZHBx4l1Y</t>
+  </si>
+  <si>
+    <t>2026-08-17</t>
+  </si>
+  <si>
+    <t>PB002</t>
+  </si>
+  <si>
+    <t>Downloading Power BI</t>
+  </si>
+  <si>
+    <t>https://youtu.be/DZm3khttZyU</t>
+  </si>
+  <si>
+    <t>PB003</t>
+  </si>
+  <si>
+    <t>Getting Started with Power BI</t>
+  </si>
+  <si>
+    <t>https://youtu.be/ypbNYxOBEyQ</t>
+  </si>
+  <si>
+    <t>PB004</t>
+  </si>
+  <si>
+    <t>Importing Data</t>
+  </si>
+  <si>
+    <t>https://youtu.be/MI_U3rkuQ3U</t>
+  </si>
+  <si>
+    <t>PB005</t>
+  </si>
+  <si>
+    <t>Transformation Using Power Query</t>
+  </si>
+  <si>
+    <t>https://youtu.be/U9sUno4v1tw</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>PB006</t>
+  </si>
+  <si>
+    <t>Importing Multiple Data</t>
+  </si>
+  <si>
+    <t>https://youtu.be/GIqeQDLI1-s</t>
+  </si>
+  <si>
+    <t>PB007</t>
+  </si>
+  <si>
+    <t>Merging Queries</t>
+  </si>
+  <si>
+    <t>https://youtu.be/HghrbUfyeTo</t>
+  </si>
+  <si>
+    <t>PB008</t>
+  </si>
+  <si>
+    <t>Loading Data to Power BI Model</t>
+  </si>
+  <si>
+    <t>https://youtu.be/U2Ftlpmw2a4</t>
+  </si>
+  <si>
+    <t>PB009</t>
+  </si>
+  <si>
+    <t>Power BI Report Editor</t>
+  </si>
+  <si>
+    <t>https://youtu.be/etCykEN4MtM</t>
+  </si>
+  <si>
+    <t>2026-08-19</t>
+  </si>
+  <si>
+    <t>PB010</t>
+  </si>
+  <si>
+    <t>Text Box</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Q2mIT2ymBrk</t>
+  </si>
+  <si>
+    <t>Power BI Visuals</t>
+  </si>
+  <si>
+    <t>PB011</t>
+  </si>
+  <si>
+    <t>Creating Our First Visual</t>
+  </si>
+  <si>
+    <t>https://youtu.be/TwclhQBd0UY</t>
+  </si>
+  <si>
+    <t>PB012</t>
+  </si>
+  <si>
+    <t>Styling Your Visual</t>
+  </si>
+  <si>
+    <t>https://youtu.be/b-B-qH4flkM</t>
+  </si>
+  <si>
+    <t>PB013</t>
+  </si>
+  <si>
+    <t>Conditional Formatting</t>
+  </si>
+  <si>
+    <t>https://youtu.be/u74yveIYBbk</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>PB014</t>
+  </si>
+  <si>
+    <t>General Formatting</t>
+  </si>
+  <si>
+    <t>https://youtu.be/D7DZyYtTZn4</t>
+  </si>
+  <si>
+    <t>PB015</t>
+  </si>
+  <si>
+    <t>Power BI Filters</t>
+  </si>
+  <si>
+    <t>https://youtu.be/OfPScKQn5vs</t>
+  </si>
+  <si>
+    <t>PB016</t>
+  </si>
+  <si>
+    <t>Power BI Slicers</t>
+  </si>
+  <si>
+    <t>https://youtu.be/3aUPyyHpz7c</t>
+  </si>
+  <si>
+    <t>PB017</t>
+  </si>
+  <si>
+    <t>Power BI Pie Charts</t>
+  </si>
+  <si>
+    <t>https://youtu.be/2E9IvB4DIpk</t>
+  </si>
+  <si>
+    <t>2026-08-21</t>
+  </si>
+  <si>
+    <t>PB018</t>
+  </si>
+  <si>
+    <t>Power BI Donut Chart</t>
+  </si>
+  <si>
+    <t>https://youtu.be/q5O7xaYLHsM</t>
+  </si>
+  <si>
+    <t>PB019</t>
+  </si>
+  <si>
+    <t>More Visuals</t>
+  </si>
+  <si>
+    <t>https://youtu.be/AaNi-sGOQB4</t>
+  </si>
+  <si>
+    <t>PB020</t>
+  </si>
+  <si>
+    <t>Map Visuals</t>
+  </si>
+  <si>
+    <t>https://youtu.be/8rnENhtb6lQ</t>
+  </si>
+  <si>
+    <t>Power BI Navigation &amp; Interactions</t>
+  </si>
+  <si>
+    <t>PB021</t>
+  </si>
+  <si>
+    <t>Controlling Slicer Interactions</t>
+  </si>
+  <si>
+    <t>https://youtu.be/MMgt3NOey8Y</t>
+  </si>
+  <si>
+    <t>2026-08-24</t>
+  </si>
+  <si>
+    <t>PB022</t>
+  </si>
+  <si>
+    <t>Creating Hidden Pages in Power BI Page Management</t>
+  </si>
+  <si>
+    <t>https://youtu.be/sabHynGEtH0</t>
+  </si>
+  <si>
+    <t>PB023</t>
+  </si>
+  <si>
+    <t>Power BI Button Navigation</t>
+  </si>
+  <si>
+    <t>https://youtu.be/d7wg5gCd-5Q</t>
+  </si>
+  <si>
+    <t>PB024</t>
+  </si>
+  <si>
+    <t>Arrow Navigation Controls</t>
+  </si>
+  <si>
+    <t>https://youtu.be/-d3JIt3T_tA</t>
+  </si>
+  <si>
+    <t>PB025</t>
+  </si>
+  <si>
+    <t>Bookmarks</t>
+  </si>
+  <si>
+    <t>https://youtu.be/_H2BJ6Q9wdg</t>
+  </si>
+  <si>
+    <t>2026-08-25</t>
+  </si>
+  <si>
+    <t>PB026</t>
+  </si>
+  <si>
+    <t>Power BI DAX Creating a New Column in Power BI</t>
+  </si>
+  <si>
+    <t>https://youtu.be/9Ckc8KO8cGk</t>
+  </si>
+  <si>
+    <t>PB027</t>
+  </si>
+  <si>
+    <t>DAX Fields</t>
+  </si>
+  <si>
+    <t>https://youtu.be/mcuiS8CNBUU</t>
+  </si>
+  <si>
+    <t>PB028</t>
+  </si>
+  <si>
+    <t>Power BI Measures</t>
+  </si>
+  <si>
+    <t>https://youtu.be/ngAvkgcTyL4</t>
+  </si>
+  <si>
+    <t>PB029</t>
+  </si>
+  <si>
+    <t>Publishing and Sharing Your Reports in Power BI</t>
+  </si>
+  <si>
+    <t>https://youtu.be/tbdOWVJRfq8</t>
+  </si>
+  <si>
+    <t>Power BI DAX, Relationships &amp; Mobile</t>
+  </si>
+  <si>
+    <t>PB-RES030</t>
+  </si>
+  <si>
+    <t>DateTable</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>PB-RES031</t>
+  </si>
+  <si>
+    <t>SalesData</t>
+  </si>
+  <si>
+    <t>PB-RES032</t>
+  </si>
+  <si>
+    <t>SalesData2</t>
+  </si>
+  <si>
+    <t>PB033</t>
+  </si>
+  <si>
+    <t>Signing Into Power BI &amp; Publishing Report</t>
+  </si>
+  <si>
+    <t>https://youtu.be/iXaNCde7nc8</t>
+  </si>
+  <si>
+    <t>PB034</t>
+  </si>
+  <si>
+    <t>Merging Columns in Power BI</t>
+  </si>
+  <si>
+    <t>https://youtu.be/sLD4dXCf-LQ</t>
+  </si>
+  <si>
+    <t>PB035</t>
+  </si>
+  <si>
+    <t>Splitting of Columns in Power BI</t>
+  </si>
+  <si>
+    <t>https://youtu.be/zqhZzeeNL58</t>
+  </si>
+  <si>
+    <t>PB036</t>
+  </si>
+  <si>
+    <t>Power BI DAX Fields</t>
+  </si>
+  <si>
+    <t>https://youtu.be/tTh3Bu33K4E</t>
+  </si>
+  <si>
+    <t>PB037</t>
+  </si>
+  <si>
+    <t>Power BI DAX Fields Pt.2</t>
+  </si>
+  <si>
+    <t>https://youtu.be/58SuKknttOU</t>
+  </si>
+  <si>
+    <t>2026-08-27</t>
+  </si>
+  <si>
+    <t>PB038</t>
+  </si>
+  <si>
+    <t>Power BI DAX Fields Pt.3</t>
+  </si>
+  <si>
+    <t>https://youtu.be/hjwiy5TPoNY</t>
+  </si>
+  <si>
+    <t>PB039</t>
+  </si>
+  <si>
+    <t>Data Modelling and Relationships</t>
+  </si>
+  <si>
+    <t>https://youtu.be/OWQL3RCN-_o</t>
+  </si>
+  <si>
+    <t>PB040</t>
+  </si>
+  <si>
+    <t>More DAX Functions</t>
+  </si>
+  <si>
+    <t>https://youtu.be/iEMs4HF83rk</t>
+  </si>
+  <si>
+    <t>PB041</t>
+  </si>
+  <si>
+    <t>Time Intelligence</t>
+  </si>
+  <si>
+    <t>https://youtu.be/6bgcizv8fRs</t>
+  </si>
+  <si>
+    <t>PB042</t>
+  </si>
+  <si>
+    <t>Time Intelligence Pt.2</t>
+  </si>
+  <si>
+    <t>https://youtu.be/rFu4h_8OViY</t>
+  </si>
+  <si>
+    <t>2026-08-28</t>
+  </si>
+  <si>
+    <t>PB043</t>
+  </si>
+  <si>
+    <t>Power BI Mobile Pt.1</t>
+  </si>
+  <si>
+    <t>https://youtu.be/4Qn6ifcMnHc</t>
+  </si>
+  <si>
+    <t>PB044</t>
+  </si>
+  <si>
+    <t>Power BI Mobile Pt.2</t>
+  </si>
+  <si>
+    <t>PB045</t>
+  </si>
+  <si>
+    <t>The End</t>
+  </si>
+  <si>
+    <t>https://youtu.be/17xQxRbu8pQ</t>
+  </si>
+  <si>
+    <t>PB046</t>
+  </si>
+  <si>
+    <t>DAX / MEASURES HANDOUT</t>
+  </si>
+  <si>
+    <t>SQL</t>
+  </si>
+  <si>
+    <t>SQL Course</t>
+  </si>
+  <si>
+    <t>SQL-RES001</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
+  </si>
+  <si>
+    <t>SQL-RES002</t>
+  </si>
+  <si>
+    <t>SQL-RES003</t>
+  </si>
+  <si>
+    <t>SQL004</t>
+  </si>
+  <si>
+    <t>https://youtu.be/wBWNm9VHlp8</t>
+  </si>
+  <si>
+    <t>SQL005</t>
+  </si>
+  <si>
+    <t>What is SQL</t>
+  </si>
+  <si>
+    <t>https://youtu.be/W1hOhq_J338</t>
+  </si>
+  <si>
+    <t>SQL006</t>
+  </si>
+  <si>
+    <t>Setting Up Our SQLite Studio Environment</t>
+  </si>
+  <si>
+    <t>https://youtu.be/7OFSoI5PNHc</t>
+  </si>
+  <si>
+    <t>SQL007</t>
+  </si>
+  <si>
+    <t>Creating a Database</t>
+  </si>
+  <si>
+    <t>https://youtu.be/5TyAYl00hvE</t>
+  </si>
+  <si>
+    <t>SQL008</t>
+  </si>
+  <si>
+    <t>Importing Tables</t>
+  </si>
+  <si>
+    <t>https://youtu.be/e9g-tgdMKSA</t>
+  </si>
+  <si>
+    <t>2026-09-01</t>
+  </si>
+  <si>
+    <t>SQL009</t>
+  </si>
+  <si>
+    <t>Executing Queries</t>
+  </si>
+  <si>
+    <t>https://youtu.be/CyZD-TqV10M</t>
+  </si>
+  <si>
+    <t>SQL010</t>
+  </si>
+  <si>
+    <t>Essential Database Terminologies</t>
+  </si>
+  <si>
+    <t>https://youtu.be/DWNvvSX564M</t>
+  </si>
+  <si>
+    <t>SQL011</t>
+  </si>
+  <si>
+    <t>The SFW Framework</t>
+  </si>
+  <si>
+    <t>https://youtu.be/4faqpT_klD4</t>
+  </si>
+  <si>
+    <t>SQL012</t>
+  </si>
+  <si>
+    <t>SQL Comments and Documentation</t>
+  </si>
+  <si>
+    <t>https://youtu.be/iBzmS1lUjA8</t>
+  </si>
+  <si>
+    <t>2026-09-02</t>
+  </si>
+  <si>
+    <t>SQL013</t>
+  </si>
+  <si>
+    <t>Select Distinct</t>
+  </si>
+  <si>
+    <t>https://youtu.be/BYzBYBDYbHQ</t>
+  </si>
+  <si>
+    <t>SQL014</t>
+  </si>
+  <si>
+    <t>SQL Where Clause</t>
+  </si>
+  <si>
+    <t>https://youtu.be/4ioDb3XFlG4</t>
+  </si>
+  <si>
+    <t>SQL015</t>
+  </si>
+  <si>
+    <t>SQL Order By Keyword</t>
+  </si>
+  <si>
+    <t>https://youtu.be/84r6UTwX6do</t>
+  </si>
+  <si>
+    <t>SQL016</t>
+  </si>
+  <si>
+    <t>SQL OR with AND Operator</t>
+  </si>
+  <si>
+    <t>https://youtu.be/RE_Xj1ZUwec</t>
+  </si>
+  <si>
+    <t>2026-09-03</t>
+  </si>
+  <si>
+    <t>SQL017</t>
+  </si>
+  <si>
+    <t>SQL NOT Operator</t>
+  </si>
+  <si>
+    <t>https://youtu.be/FtBt-FGr7ag</t>
+  </si>
+  <si>
+    <t>SQL018</t>
+  </si>
+  <si>
+    <t>SQL UPDATE</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Vx-wL9nNj5o</t>
+  </si>
+  <si>
+    <t>SQL019</t>
+  </si>
+  <si>
+    <t>SQL DELETE</t>
+  </si>
+  <si>
+    <t>https://youtu.be/-JMHQzDqX4A</t>
+  </si>
+  <si>
+    <t>SQL020</t>
+  </si>
+  <si>
+    <t>Limit Keyword</t>
+  </si>
+  <si>
+    <t>https://youtu.be/ZIpZmT-mVjY</t>
+  </si>
+  <si>
+    <t>2026-09-04</t>
+  </si>
+  <si>
+    <t>SQL021</t>
+  </si>
+  <si>
+    <t>SQL Max &amp; Min Keywords</t>
+  </si>
+  <si>
     <t>https://youtu.be/cWNBSV9B94Y</t>
-  </si>
-  <si>
-    <t>EX038</t>
-  </si>
-  <si>
-    <t>Average &amp; AverageIF Functions</t>
-  </si>
-  <si>
-    <t>https://youtu.be/fzYS1quf1VQ</t>
-  </si>
-  <si>
-    <t>2026-07-23</t>
-  </si>
-  <si>
-    <t>EX039</t>
-  </si>
-  <si>
-    <t>IF Statement</t>
-  </si>
-  <si>
-    <t>https://youtu.be/9--5M-g9VBU</t>
-  </si>
-  <si>
-    <t>EX040</t>
-  </si>
-  <si>
-    <t>Mini-Project 2 Pt.1</t>
-  </si>
-  <si>
-    <t>https://youtu.be/GbuEOaRAjkE</t>
-  </si>
-  <si>
-    <t>EX041</t>
-  </si>
-  <si>
-    <t>Mini-Project Pt.2</t>
-  </si>
-  <si>
-    <t>https://youtu.be/o3yAAR_GnQ0</t>
-  </si>
-  <si>
-    <t>EX042</t>
-  </si>
-  <si>
-    <t>Mini-Project Pt.3</t>
-  </si>
-  <si>
-    <t>https://youtu.be/lWPpUuhChSQ</t>
-  </si>
-  <si>
-    <t>2026-07-24</t>
-  </si>
-  <si>
-    <t>Data Validation, Lookup &amp; Mini Project 3</t>
-  </si>
-  <si>
-    <t>EX-RES043</t>
-  </si>
-  <si>
-    <t>Mini Project 3</t>
-  </si>
-  <si>
-    <t>EX044</t>
-  </si>
-  <si>
-    <t>Data Validation Pt.1</t>
-  </si>
-  <si>
-    <t>https://youtu.be/XPxhNhJ6BsU</t>
-  </si>
-  <si>
-    <t>EX045</t>
-  </si>
-  <si>
-    <t>Data Validation Pt.2</t>
-  </si>
-  <si>
-    <t>https://youtu.be/XrIpwJDB9y8</t>
-  </si>
-  <si>
-    <t>EX046</t>
-  </si>
-  <si>
-    <t>Data Validation Pt.3</t>
-  </si>
-  <si>
-    <t>https://youtu.be/uOIOAwxUBxk</t>
-  </si>
-  <si>
-    <t>EX047</t>
-  </si>
-  <si>
-    <t>Data Validation Pt.4</t>
-  </si>
-  <si>
-    <t>https://youtu.be/3AAFOsDv98o</t>
-  </si>
-  <si>
-    <t>2026-07-27</t>
-  </si>
-  <si>
-    <t>EX048</t>
-  </si>
-  <si>
-    <t>VLOOKUP Function</t>
-  </si>
-  <si>
-    <t>https://youtu.be/uC-eSdiBVrw</t>
-  </si>
-  <si>
-    <t>EX049</t>
-  </si>
-  <si>
-    <t>XLOOKUP Function</t>
-  </si>
-  <si>
-    <t>https://youtu.be/fkIgEH5quCo</t>
-  </si>
-  <si>
-    <t>EX050</t>
-  </si>
-  <si>
-    <t>Text Function</t>
-  </si>
-  <si>
-    <t>https://youtu.be/mu-SFVrdHNI</t>
-  </si>
-  <si>
-    <t>EX051</t>
-  </si>
-  <si>
-    <t>Left &amp; Right Functions</t>
-  </si>
-  <si>
-    <t>https://youtu.be/ddtOXCH6T4o</t>
-  </si>
-  <si>
-    <t>2026-07-28</t>
-  </si>
-  <si>
-    <t>EX052</t>
-  </si>
-  <si>
-    <t>LEN Function</t>
-  </si>
-  <si>
-    <t>https://youtu.be/K7KAsbX-y2g</t>
-  </si>
-  <si>
-    <t>EX053</t>
-  </si>
-  <si>
-    <t>MID Function</t>
-  </si>
-  <si>
-    <t>https://youtu.be/SGRCa2DBijg</t>
-  </si>
-  <si>
-    <t>EX054</t>
-  </si>
-  <si>
-    <t>Date Function</t>
-  </si>
-  <si>
-    <t>https://youtu.be/jNd5Lr4N0S8</t>
-  </si>
-  <si>
-    <t>EX055</t>
-  </si>
-  <si>
-    <t>DATEDIF Function</t>
-  </si>
-  <si>
-    <t>https://youtu.be/I3EzGZzQ7YY</t>
-  </si>
-  <si>
-    <t>2026-07-29</t>
-  </si>
-  <si>
-    <t>EX056</t>
-  </si>
-  <si>
-    <t>Text Functions</t>
-  </si>
-  <si>
-    <t>https://youtu.be/j5qOiGC8qjc</t>
-  </si>
-  <si>
-    <t>EX057</t>
-  </si>
-  <si>
-    <t>Unique Function</t>
-  </si>
-  <si>
-    <t>https://youtu.be/wc_50NXb9zs</t>
-  </si>
-  <si>
-    <t>EX058</t>
-  </si>
-  <si>
-    <t>Sort Function</t>
-  </si>
-  <si>
-    <t>https://youtu.be/fnfnwRaCxPM</t>
-  </si>
-  <si>
-    <t>EX059</t>
-  </si>
-  <si>
-    <t>Mini-Project3 Pt.1</t>
-  </si>
-  <si>
-    <t>https://youtu.be/uqyCNJxiZuM</t>
-  </si>
-  <si>
-    <t>2026-07-30</t>
-  </si>
-  <si>
-    <t>EX060</t>
-  </si>
-  <si>
-    <t>EX061</t>
-  </si>
-  <si>
-    <t>EX062</t>
-  </si>
-  <si>
-    <t>Mini-Project Pt.4</t>
-  </si>
-  <si>
-    <t>https://youtu.be/fAVoxFWbuTM</t>
-  </si>
-  <si>
-    <t>Statistical Functions</t>
-  </si>
-  <si>
-    <t>EX063</t>
-  </si>
-  <si>
-    <t>Statistical Functions (Median)</t>
-  </si>
-  <si>
-    <t>https://youtu.be/LMTwjVLThtI</t>
-  </si>
-  <si>
-    <t>2026-07-31</t>
-  </si>
-  <si>
-    <t>EX064</t>
-  </si>
-  <si>
-    <t>Statistical Functions (Mode)</t>
-  </si>
-  <si>
-    <t>https://youtu.be/qJgX6B6TVjk</t>
-  </si>
-  <si>
-    <t>EX065</t>
-  </si>
-  <si>
-    <t>Standard Deviation</t>
-  </si>
-  <si>
-    <t>https://youtu.be/BmL5K4_U2Fg</t>
-  </si>
-  <si>
-    <t>EX066</t>
-  </si>
-  <si>
-    <t>Quartiles</t>
-  </si>
-  <si>
-    <t>https://youtu.be/khShX87eH5Q</t>
-  </si>
-  <si>
-    <t>Logical Functions &amp; Mini Project 4</t>
-  </si>
-  <si>
-    <t>EX-RES067</t>
-  </si>
-  <si>
-    <t>Excel Mini-Project 4 Dataset</t>
-  </si>
-  <si>
-    <t>2026-08-03</t>
-  </si>
-  <si>
-    <t>EX-RES068</t>
-  </si>
-  <si>
-    <t>Excel Mini-Project 4</t>
-  </si>
-  <si>
-    <t>EX069</t>
-  </si>
-  <si>
-    <t>Ampersand Operator</t>
-  </si>
-  <si>
-    <t>https://youtu.be/cQdMqFXnrsg</t>
-  </si>
-  <si>
-    <t>EX070</t>
-  </si>
-  <si>
-    <t>Comparison Operator</t>
-  </si>
-  <si>
-    <t>https://youtu.be/-L32oCBfauE</t>
-  </si>
-  <si>
-    <t>EX071</t>
-  </si>
-  <si>
-    <t>Logical Operators</t>
-  </si>
-  <si>
-    <t>https://youtu.be/-PsBiHH8awA</t>
-  </si>
-  <si>
-    <t>EX072</t>
-  </si>
-  <si>
-    <t>Conditional Functions (IF &amp; IFS)</t>
-  </si>
-  <si>
-    <t>EX073</t>
-  </si>
-  <si>
-    <t>Mini-Project4 Pt.1</t>
-  </si>
-  <si>
-    <t>https://youtu.be/_vihyE0YXHQ</t>
-  </si>
-  <si>
-    <t>2026-08-04</t>
-  </si>
-  <si>
-    <t>EX074</t>
-  </si>
-  <si>
-    <t>Mini-Project4 Pt.2</t>
-  </si>
-  <si>
-    <t>https://youtu.be/vOyvkf0Eg2k</t>
-  </si>
-  <si>
-    <t>EX075</t>
-  </si>
-  <si>
-    <t>Mini-Project4 Pt.3</t>
-  </si>
-  <si>
-    <t>https://youtu.be/DMNUewivrjA</t>
-  </si>
-  <si>
-    <t>EX076</t>
-  </si>
-  <si>
-    <t>Mini-Project4 Pt.4</t>
-  </si>
-  <si>
-    <t>Excel Tables</t>
-  </si>
-  <si>
-    <t>EX-RES077</t>
-  </si>
-  <si>
-    <t>list_of_countries_and_dependencies</t>
-  </si>
-  <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
-    <t>EX078</t>
-  </si>
-  <si>
-    <t>Adding Tables</t>
-  </si>
-  <si>
-    <t>https://youtu.be/4oIp_G9v7ZA</t>
-  </si>
-  <si>
-    <t>EX079</t>
-  </si>
-  <si>
-    <t>Table Management</t>
-  </si>
-  <si>
-    <t>https://youtu.be/OK-vnknXdOY</t>
-  </si>
-  <si>
-    <t>EX080</t>
-  </si>
-  <si>
-    <t>Table Filters</t>
-  </si>
-  <si>
-    <t>https://youtu.be/O7f3C5Phx3M</t>
-  </si>
-  <si>
-    <t>EX081</t>
-  </si>
-  <si>
-    <t>Pivot Table</t>
-  </si>
-  <si>
-    <t>https://youtu.be/n3qc2RFQbAY</t>
-  </si>
-  <si>
-    <t>Excel Charts</t>
-  </si>
-  <si>
-    <t>EX082</t>
-  </si>
-  <si>
-    <t>https://youtu.be/xq-mLouC4Lw</t>
-  </si>
-  <si>
-    <t>2026-08-06</t>
-  </si>
-  <si>
-    <t>EX083</t>
-  </si>
-  <si>
-    <t>Chart Types</t>
-  </si>
-  <si>
-    <t>https://youtu.be/JWOObDjlFpc</t>
-  </si>
-  <si>
-    <t>EX084</t>
-  </si>
-  <si>
-    <t>Sparklines</t>
-  </si>
-  <si>
-    <t>https://youtu.be/lE-z17LYIDA</t>
-  </si>
-  <si>
-    <t>EX085</t>
-  </si>
-  <si>
-    <t>Pivot Chart</t>
-  </si>
-  <si>
-    <t>https://youtu.be/wtESKgTVu0c</t>
-  </si>
-  <si>
-    <t>EX086</t>
-  </si>
-  <si>
-    <t>Conditional Formatting Pt.1</t>
-  </si>
-  <si>
-    <t>https://youtu.be/-SjF_f-_Mes</t>
-  </si>
-  <si>
-    <t>2026-08-07</t>
-  </si>
-  <si>
-    <t>EX087</t>
-  </si>
-  <si>
-    <t>Conditional Formatting Pt.2</t>
-  </si>
-  <si>
-    <t>https://youtu.be/G4k7ikIPWFc</t>
-  </si>
-  <si>
-    <t>Power Query</t>
-  </si>
-  <si>
-    <t>PQ-RES001</t>
-  </si>
-  <si>
-    <t>films</t>
-  </si>
-  <si>
-    <t>2026-08-10</t>
-  </si>
-  <si>
-    <t>PQ-RES002</t>
-  </si>
-  <si>
-    <t>movie_ratings</t>
-  </si>
-  <si>
-    <t>PQ003</t>
-  </si>
-  <si>
-    <t>Introduction to Power Query</t>
-  </si>
-  <si>
-    <t>https://youtu.be/9bht65Qv9Q0</t>
-  </si>
-  <si>
-    <t>PQ004</t>
-  </si>
-  <si>
-    <t>Accessing Power Query</t>
-  </si>
-  <si>
-    <t>https://youtu.be/OfzMv4csB4M</t>
-  </si>
-  <si>
-    <t>PQ005</t>
-  </si>
-  <si>
-    <t>Reduce Rows Section</t>
-  </si>
-  <si>
-    <t>https://youtu.be/St8pQ6rkJ5Y</t>
-  </si>
-  <si>
-    <t>PQ006</t>
-  </si>
-  <si>
-    <t>Manage Columns</t>
-  </si>
-  <si>
-    <t>https://youtu.be/7d6h1stqUVI</t>
-  </si>
-  <si>
-    <t>PQ007</t>
-  </si>
-  <si>
-    <t>Conditional Columns</t>
-  </si>
-  <si>
-    <t>https://youtu.be/IIzoiGgQh9M</t>
-  </si>
-  <si>
-    <t>2026-08-11</t>
-  </si>
-  <si>
-    <t>PQ008</t>
-  </si>
-  <si>
-    <t>Creating Index Columns</t>
-  </si>
-  <si>
-    <t>https://youtu.be/u4vHsVY6iWg</t>
-  </si>
-  <si>
-    <t>PQ009</t>
-  </si>
-  <si>
-    <t>Power Query Home Tab</t>
-  </si>
-  <si>
-    <t>https://youtu.be/y-g2-xv1wi4</t>
-  </si>
-  <si>
-    <t>PQ010</t>
-  </si>
-  <si>
-    <t>Power Query Transform Tab</t>
-  </si>
-  <si>
-    <t>https://youtu.be/GPCDungCTK8</t>
-  </si>
-  <si>
-    <t>PQ011</t>
-  </si>
-  <si>
-    <t>Close and Load</t>
-  </si>
-  <si>
-    <t>https://youtu.be/o1QVywo65fU</t>
-  </si>
-  <si>
-    <t>2026-08-12</t>
-  </si>
-  <si>
-    <t>PQ012</t>
-  </si>
-  <si>
-    <t>External Data Source (Web)</t>
-  </si>
-  <si>
-    <t>https://youtu.be/7PEovlMLfN4</t>
-  </si>
-  <si>
-    <t>PQ013</t>
-  </si>
-  <si>
-    <t>Merging Queries Pt.1</t>
-  </si>
-  <si>
-    <t>https://youtu.be/53qoq8gTmEw</t>
-  </si>
-  <si>
-    <t>PQ014</t>
-  </si>
-  <si>
-    <t>Merging Queries Pt.2</t>
-  </si>
-  <si>
-    <t>https://youtu.be/rs1O1Q0AZrU</t>
-  </si>
-  <si>
-    <t>Excel Final Project</t>
-  </si>
-  <si>
-    <t>EX-RES088</t>
-  </si>
-  <si>
-    <t>Excel Final Project Dataset</t>
-  </si>
-  <si>
-    <t>2026-08-13</t>
-  </si>
-  <si>
-    <t>EX-RES089</t>
-  </si>
-  <si>
-    <t>EX090</t>
-  </si>
-  <si>
-    <t>Data Protection</t>
-  </si>
-  <si>
-    <t>https://youtu.be/yRL09ge6UvY</t>
-  </si>
-  <si>
-    <t>EX091</t>
-  </si>
-  <si>
-    <t>https://youtu.be/i7Chd1Fne9k</t>
-  </si>
-  <si>
-    <t>EX092</t>
-  </si>
-  <si>
-    <t>Sharing Your Project</t>
-  </si>
-  <si>
-    <t>https://youtu.be/-2s7B3T4ZBw</t>
-  </si>
-  <si>
-    <t>EX093</t>
-  </si>
-  <si>
-    <t>Excel Add-ins</t>
-  </si>
-  <si>
-    <t>https://youtu.be/WLFAy_4rCvA</t>
-  </si>
-  <si>
-    <t>EX094</t>
-  </si>
-  <si>
-    <t>Final Project Pt.1</t>
-  </si>
-  <si>
-    <t>https://youtu.be/bjD7oT2h64Q</t>
-  </si>
-  <si>
-    <t>2026-08-14</t>
-  </si>
-  <si>
-    <t>EX095</t>
-  </si>
-  <si>
-    <t>Final Project Pt.2</t>
-  </si>
-  <si>
-    <t>https://youtu.be/p7zCOb5rqHQ</t>
-  </si>
-  <si>
-    <t>EX096</t>
-  </si>
-  <si>
-    <t>Final Project Pt.3</t>
-  </si>
-  <si>
-    <t>https://youtu.be/0HlrW6M_Y_A</t>
-  </si>
-  <si>
-    <t>EX097</t>
-  </si>
-  <si>
-    <t>Final Project Pt.4</t>
-  </si>
-  <si>
-    <t>https://youtu.be/KqqP9gCVt3k</t>
-  </si>
-  <si>
-    <t>Power BI</t>
-  </si>
-  <si>
-    <t>Power BI Basics</t>
-  </si>
-  <si>
-    <t>PB001</t>
-  </si>
-  <si>
-    <t>Course Introduction</t>
-  </si>
-  <si>
-    <t>https://youtu.be/Xa6ZHBx4l1Y</t>
-  </si>
-  <si>
-    <t>2026-08-17</t>
-  </si>
-  <si>
-    <t>PB002</t>
-  </si>
-  <si>
-    <t>Downloading Power BI</t>
-  </si>
-  <si>
-    <t>https://youtu.be/DZm3khttZyU</t>
-  </si>
-  <si>
-    <t>PB003</t>
-  </si>
-  <si>
-    <t>Getting Started with Power BI</t>
-  </si>
-  <si>
-    <t>https://youtu.be/ypbNYxOBEyQ</t>
-  </si>
-  <si>
-    <t>PB004</t>
-  </si>
-  <si>
-    <t>Importing Data</t>
-  </si>
-  <si>
-    <t>https://youtu.be/MI_U3rkuQ3U</t>
-  </si>
-  <si>
-    <t>PB005</t>
-  </si>
-  <si>
-    <t>Transformation Using Power Query</t>
-  </si>
-  <si>
-    <t>https://youtu.be/U9sUno4v1tw</t>
-  </si>
-  <si>
-    <t>2026-08-18</t>
-  </si>
-  <si>
-    <t>PB006</t>
-  </si>
-  <si>
-    <t>Importing Multiple Data</t>
-  </si>
-  <si>
-    <t>https://youtu.be/GIqeQDLI1-s</t>
-  </si>
-  <si>
-    <t>PB007</t>
-  </si>
-  <si>
-    <t>Merging Queries</t>
-  </si>
-  <si>
-    <t>https://youtu.be/HghrbUfyeTo</t>
-  </si>
-  <si>
-    <t>PB008</t>
-  </si>
-  <si>
-    <t>Loading Data to Power BI Model</t>
-  </si>
-  <si>
-    <t>https://youtu.be/U2Ftlpmw2a4</t>
-  </si>
-  <si>
-    <t>PB009</t>
-  </si>
-  <si>
-    <t>Power BI Report Editor</t>
-  </si>
-  <si>
-    <t>https://youtu.be/etCykEN4MtM</t>
-  </si>
-  <si>
-    <t>2026-08-19</t>
-  </si>
-  <si>
-    <t>PB010</t>
-  </si>
-  <si>
-    <t>Text Box</t>
-  </si>
-  <si>
-    <t>https://youtu.be/Q2mIT2ymBrk</t>
-  </si>
-  <si>
-    <t>Power BI Visuals</t>
-  </si>
-  <si>
-    <t>PB011</t>
-  </si>
-  <si>
-    <t>Creating Our First Visual</t>
-  </si>
-  <si>
-    <t>https://youtu.be/TwclhQBd0UY</t>
-  </si>
-  <si>
-    <t>PB012</t>
-  </si>
-  <si>
-    <t>Styling Your Visual</t>
-  </si>
-  <si>
-    <t>https://youtu.be/b-B-qH4flkM</t>
-  </si>
-  <si>
-    <t>PB013</t>
-  </si>
-  <si>
-    <t>Conditional Formatting</t>
-  </si>
-  <si>
-    <t>https://youtu.be/u74yveIYBbk</t>
-  </si>
-  <si>
-    <t>2026-08-20</t>
-  </si>
-  <si>
-    <t>PB014</t>
-  </si>
-  <si>
-    <t>General Formatting</t>
-  </si>
-  <si>
-    <t>https://youtu.be/D7DZyYtTZn4</t>
-  </si>
-  <si>
-    <t>PB015</t>
-  </si>
-  <si>
-    <t>Power BI Filters</t>
-  </si>
-  <si>
-    <t>https://youtu.be/OfPScKQn5vs</t>
-  </si>
-  <si>
-    <t>PB016</t>
-  </si>
-  <si>
-    <t>Power BI Slicers</t>
-  </si>
-  <si>
-    <t>https://youtu.be/3aUPyyHpz7c</t>
-  </si>
-  <si>
-    <t>PB017</t>
-  </si>
-  <si>
-    <t>Power BI Pie Charts</t>
-  </si>
-  <si>
-    <t>https://youtu.be/2E9IvB4DIpk</t>
-  </si>
-  <si>
-    <t>2026-08-21</t>
-  </si>
-  <si>
-    <t>PB018</t>
-  </si>
-  <si>
-    <t>Power BI Donut Chart</t>
-  </si>
-  <si>
-    <t>https://youtu.be/q5O7xaYLHsM</t>
-  </si>
-  <si>
-    <t>PB019</t>
-  </si>
-  <si>
-    <t>More Visuals</t>
-  </si>
-  <si>
-    <t>https://youtu.be/AaNi-sGOQB4</t>
-  </si>
-  <si>
-    <t>PB020</t>
-  </si>
-  <si>
-    <t>Map Visuals</t>
-  </si>
-  <si>
-    <t>https://youtu.be/8rnENhtb6lQ</t>
-  </si>
-  <si>
-    <t>Power BI Navigation &amp; Interactions</t>
-  </si>
-  <si>
-    <t>PB021</t>
-  </si>
-  <si>
-    <t>Controlling Slicer Interactions</t>
-  </si>
-  <si>
-    <t>https://youtu.be/MMgt3NOey8Y</t>
-  </si>
-  <si>
-    <t>2026-08-24</t>
-  </si>
-  <si>
-    <t>PB022</t>
-  </si>
-  <si>
-    <t>Creating Hidden Pages in Power BI Page Management</t>
-  </si>
-  <si>
-    <t>https://youtu.be/sabHynGEtH0</t>
-  </si>
-  <si>
-    <t>PB023</t>
-  </si>
-  <si>
-    <t>Power BI Button Navigation</t>
-  </si>
-  <si>
-    <t>https://youtu.be/d7wg5gCd-5Q</t>
-  </si>
-  <si>
-    <t>PB024</t>
-  </si>
-  <si>
-    <t>Arrow Navigation Controls</t>
-  </si>
-  <si>
-    <t>https://youtu.be/-d3JIt3T_tA</t>
-  </si>
-  <si>
-    <t>PB025</t>
-  </si>
-  <si>
-    <t>Bookmarks</t>
-  </si>
-  <si>
-    <t>https://youtu.be/_H2BJ6Q9wdg</t>
-  </si>
-  <si>
-    <t>2026-08-25</t>
-  </si>
-  <si>
-    <t>PB026</t>
-  </si>
-  <si>
-    <t>Power BI DAX Creating a New Column in Power BI</t>
-  </si>
-  <si>
-    <t>https://youtu.be/9Ckc8KO8cGk</t>
-  </si>
-  <si>
-    <t>PB027</t>
-  </si>
-  <si>
-    <t>DAX Fields</t>
-  </si>
-  <si>
-    <t>https://youtu.be/mcuiS8CNBUU</t>
-  </si>
-  <si>
-    <t>PB028</t>
-  </si>
-  <si>
-    <t>Power BI Measures</t>
-  </si>
-  <si>
-    <t>https://youtu.be/ngAvkgcTyL4</t>
-  </si>
-  <si>
-    <t>PB029</t>
-  </si>
-  <si>
-    <t>Publishing and Sharing Your Reports in Power BI</t>
-  </si>
-  <si>
-    <t>https://youtu.be/tbdOWVJRfq8</t>
-  </si>
-  <si>
-    <t>Power BI DAX, Relationships &amp; Mobile</t>
-  </si>
-  <si>
-    <t>PB-RES030</t>
-  </si>
-  <si>
-    <t>DateTable</t>
-  </si>
-  <si>
-    <t>2026-08-26</t>
-  </si>
-  <si>
-    <t>PB-RES031</t>
-  </si>
-  <si>
-    <t>SalesData</t>
-  </si>
-  <si>
-    <t>PB-RES032</t>
-  </si>
-  <si>
-    <t>SalesData2</t>
-  </si>
-  <si>
-    <t>PB033</t>
-  </si>
-  <si>
-    <t>Signing Into Power BI &amp; Publishing Report</t>
-  </si>
-  <si>
-    <t>https://youtu.be/iXaNCde7nc8</t>
-  </si>
-  <si>
-    <t>PB034</t>
-  </si>
-  <si>
-    <t>Merging Columns in Power BI</t>
-  </si>
-  <si>
-    <t>https://youtu.be/sLD4dXCf-LQ</t>
-  </si>
-  <si>
-    <t>PB035</t>
-  </si>
-  <si>
-    <t>Splitting of Columns in Power BI</t>
-  </si>
-  <si>
-    <t>https://youtu.be/zqhZzeeNL58</t>
-  </si>
-  <si>
-    <t>PB036</t>
-  </si>
-  <si>
-    <t>Power BI DAX Fields</t>
-  </si>
-  <si>
-    <t>https://youtu.be/tTh3Bu33K4E</t>
-  </si>
-  <si>
-    <t>PB037</t>
-  </si>
-  <si>
-    <t>Power BI DAX Fields Pt.2</t>
-  </si>
-  <si>
-    <t>https://youtu.be/58SuKknttOU</t>
-  </si>
-  <si>
-    <t>2026-08-27</t>
-  </si>
-  <si>
-    <t>PB038</t>
-  </si>
-  <si>
-    <t>Power BI DAX Fields Pt.3</t>
-  </si>
-  <si>
-    <t>https://youtu.be/hjwiy5TPoNY</t>
-  </si>
-  <si>
-    <t>PB039</t>
-  </si>
-  <si>
-    <t>Data Modelling and Relationships</t>
-  </si>
-  <si>
-    <t>https://youtu.be/OWQL3RCN-_o</t>
-  </si>
-  <si>
-    <t>PB040</t>
-  </si>
-  <si>
-    <t>More DAX Functions</t>
-  </si>
-  <si>
-    <t>https://youtu.be/iEMs4HF83rk</t>
-  </si>
-  <si>
-    <t>PB041</t>
-  </si>
-  <si>
-    <t>Time Intelligence</t>
-  </si>
-  <si>
-    <t>https://youtu.be/6bgcizv8fRs</t>
-  </si>
-  <si>
-    <t>PB042</t>
-  </si>
-  <si>
-    <t>Time Intelligence Pt.2</t>
-  </si>
-  <si>
-    <t>https://youtu.be/rFu4h_8OViY</t>
-  </si>
-  <si>
-    <t>2026-08-28</t>
-  </si>
-  <si>
-    <t>PB043</t>
-  </si>
-  <si>
-    <t>Power BI Mobile Pt.1</t>
-  </si>
-  <si>
-    <t>https://youtu.be/4Qn6ifcMnHc</t>
-  </si>
-  <si>
-    <t>PB044</t>
-  </si>
-  <si>
-    <t>Power BI Mobile Pt.2</t>
-  </si>
-  <si>
-    <t>PB045</t>
-  </si>
-  <si>
-    <t>The End</t>
-  </si>
-  <si>
-    <t>https://youtu.be/17xQxRbu8pQ</t>
-  </si>
-  <si>
-    <t>SQL</t>
-  </si>
-  <si>
-    <t>SQL Course</t>
-  </si>
-  <si>
-    <t>SQL-RES001</t>
-  </si>
-  <si>
-    <t>2026-08-31</t>
-  </si>
-  <si>
-    <t>SQL-RES002</t>
-  </si>
-  <si>
-    <t>SQL-RES003</t>
-  </si>
-  <si>
-    <t>SQL004</t>
-  </si>
-  <si>
-    <t>https://youtu.be/wBWNm9VHlp8</t>
-  </si>
-  <si>
-    <t>SQL005</t>
-  </si>
-  <si>
-    <t>What is SQL</t>
-  </si>
-  <si>
-    <t>https://youtu.be/W1hOhq_J338</t>
-  </si>
-  <si>
-    <t>SQL006</t>
-  </si>
-  <si>
-    <t>Setting Up Our SQLite Studio Environment</t>
-  </si>
-  <si>
-    <t>https://youtu.be/7OFSoI5PNHc</t>
-  </si>
-  <si>
-    <t>SQL007</t>
-  </si>
-  <si>
-    <t>Creating a Database</t>
-  </si>
-  <si>
-    <t>https://youtu.be/5TyAYl00hvE</t>
-  </si>
-  <si>
-    <t>SQL008</t>
-  </si>
-  <si>
-    <t>Importing Tables</t>
-  </si>
-  <si>
-    <t>https://youtu.be/e9g-tgdMKSA</t>
-  </si>
-  <si>
-    <t>2026-09-01</t>
-  </si>
-  <si>
-    <t>SQL009</t>
-  </si>
-  <si>
-    <t>Executing Queries</t>
-  </si>
-  <si>
-    <t>https://youtu.be/CyZD-TqV10M</t>
-  </si>
-  <si>
-    <t>SQL010</t>
-  </si>
-  <si>
-    <t>Essential Database Terminologies</t>
-  </si>
-  <si>
-    <t>https://youtu.be/DWNvvSX564M</t>
-  </si>
-  <si>
-    <t>SQL011</t>
-  </si>
-  <si>
-    <t>The SFW Framework</t>
-  </si>
-  <si>
-    <t>https://youtu.be/4faqpT_klD4</t>
-  </si>
-  <si>
-    <t>SQL012</t>
-  </si>
-  <si>
-    <t>SQL Comments and Documentation</t>
-  </si>
-  <si>
-    <t>https://youtu.be/iBzmS1lUjA8</t>
-  </si>
-  <si>
-    <t>2026-09-02</t>
-  </si>
-  <si>
-    <t>SQL013</t>
-  </si>
-  <si>
-    <t>Select Distinct</t>
-  </si>
-  <si>
-    <t>https://youtu.be/BYzBYBDYbHQ</t>
-  </si>
-  <si>
-    <t>SQL014</t>
-  </si>
-  <si>
-    <t>SQL Where Clause</t>
-  </si>
-  <si>
-    <t>https://youtu.be/4ioDb3XFlG4</t>
-  </si>
-  <si>
-    <t>SQL015</t>
-  </si>
-  <si>
-    <t>SQL Order By Keyword</t>
-  </si>
-  <si>
-    <t>https://youtu.be/84r6UTwX6do</t>
-  </si>
-  <si>
-    <t>SQL016</t>
-  </si>
-  <si>
-    <t>SQL OR with AND Operator</t>
-  </si>
-  <si>
-    <t>https://youtu.be/RE_Xj1ZUwec</t>
-  </si>
-  <si>
-    <t>2026-09-03</t>
-  </si>
-  <si>
-    <t>SQL017</t>
-  </si>
-  <si>
-    <t>SQL NOT Operator</t>
-  </si>
-  <si>
-    <t>https://youtu.be/FtBt-FGr7ag</t>
-  </si>
-  <si>
-    <t>SQL018</t>
-  </si>
-  <si>
-    <t>SQL UPDATE</t>
-  </si>
-  <si>
-    <t>https://youtu.be/Vx-wL9nNj5o</t>
-  </si>
-  <si>
-    <t>SQL019</t>
-  </si>
-  <si>
-    <t>SQL DELETE</t>
-  </si>
-  <si>
-    <t>https://youtu.be/-JMHQzDqX4A</t>
-  </si>
-  <si>
-    <t>SQL020</t>
-  </si>
-  <si>
-    <t>Limit Keyword</t>
-  </si>
-  <si>
-    <t>https://youtu.be/ZIpZmT-mVjY</t>
-  </si>
-  <si>
-    <t>2026-09-04</t>
-  </si>
-  <si>
-    <t>SQL021</t>
-  </si>
-  <si>
-    <t>SQL Max &amp; Min Keywords</t>
   </si>
   <si>
     <t>SQL022</t>
@@ -3260,7 +3281,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MasterCurriculumTable" displayName="MasterCurriculumTable" ref="A1:K224">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MasterCurriculumTable" displayName="MasterCurriculumTable" ref="A1:K225">
   <tableColumns count="11">
     <tableColumn id="1" name="Global Order"/>
     <tableColumn id="2" name="Course"/>
@@ -3439,7 +3460,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N224"/>
+  <dimension ref="A1:N225"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -5876,7 +5897,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="56" spans="1:14">
+    <row r="56" ht="27.6" spans="1:14">
       <c r="A56" s="5">
         <v>55</v>
       </c>
@@ -5920,7 +5941,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="57" spans="1:14">
+    <row r="57" ht="27.6" spans="1:14">
       <c r="A57" s="5">
         <v>56</v>
       </c>
@@ -5964,7 +5985,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="58" spans="1:14">
+    <row r="58" ht="27.6" spans="1:14">
       <c r="A58" s="5">
         <v>57</v>
       </c>
@@ -6776,10 +6797,10 @@
         <v>24</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>205</v>
+        <v>267</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>206</v>
+        <v>268</v>
       </c>
       <c r="I76" s="5" t="s">
         <v>18</v>
@@ -6811,7 +6832,7 @@
         <v>211</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E77" s="5">
         <v>60</v>
@@ -6820,10 +6841,10 @@
         <v>24</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>208</v>
+        <v>270</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>209</v>
+        <v>271</v>
       </c>
       <c r="I77" s="5" t="s">
         <v>18</v>
@@ -6855,7 +6876,7 @@
         <v>211</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="E78" s="5">
         <v>61</v>
@@ -6864,10 +6885,10 @@
         <v>24</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="I78" s="5" t="s">
         <v>18</v>
@@ -6896,10 +6917,10 @@
         <v>75</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="E79" s="5">
         <v>62</v>
@@ -6908,10 +6929,10 @@
         <v>24</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="H79" s="5" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="I79" s="5" t="s">
         <v>18</v>
@@ -6923,7 +6944,7 @@
         <v>4</v>
       </c>
       <c r="L79" s="6" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="M79" s="6" t="s">
         <v>68</v>
@@ -6940,10 +6961,10 @@
         <v>75</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="E80" s="5">
         <v>63</v>
@@ -6952,10 +6973,10 @@
         <v>24</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="I80" s="5" t="s">
         <v>18</v>
@@ -6967,7 +6988,7 @@
         <v>4</v>
       </c>
       <c r="L80" s="6" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="M80" s="6" t="s">
         <v>68</v>
@@ -6984,10 +7005,10 @@
         <v>75</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="E81" s="5">
         <v>64</v>
@@ -6996,10 +7017,10 @@
         <v>24</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="H81" s="5" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="I81" s="5" t="s">
         <v>18</v>
@@ -7011,7 +7032,7 @@
         <v>4</v>
       </c>
       <c r="L81" s="6" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="M81" s="6" t="s">
         <v>68</v>
@@ -7028,10 +7049,10 @@
         <v>75</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="E82" s="5">
         <v>65</v>
@@ -7040,10 +7061,10 @@
         <v>24</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="H82" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="I82" s="5" t="s">
         <v>18</v>
@@ -7055,7 +7076,7 @@
         <v>4</v>
       </c>
       <c r="L82" s="6" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="M82" s="6" t="s">
         <v>68</v>
@@ -7072,10 +7093,10 @@
         <v>75</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E83" s="5">
         <v>66</v>
@@ -7084,7 +7105,7 @@
         <v>16</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="H83" s="5" t="s">
         <v>18</v>
@@ -7099,7 +7120,7 @@
         <v>5</v>
       </c>
       <c r="L83" s="6" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="M83" s="6" t="s">
         <v>84</v>
@@ -7116,10 +7137,10 @@
         <v>75</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E84" s="5">
         <v>67</v>
@@ -7128,7 +7149,7 @@
         <v>16</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="H84" s="5" t="s">
         <v>18</v>
@@ -7143,7 +7164,7 @@
         <v>5</v>
       </c>
       <c r="L84" s="6" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="M84" s="6" t="s">
         <v>84</v>
@@ -7160,10 +7181,10 @@
         <v>75</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="E85" s="5">
         <v>68</v>
@@ -7172,10 +7193,10 @@
         <v>24</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="H85" s="5" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="I85" s="5" t="s">
         <v>18</v>
@@ -7187,7 +7208,7 @@
         <v>5</v>
       </c>
       <c r="L85" s="6" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="M85" s="6" t="s">
         <v>84</v>
@@ -7204,10 +7225,10 @@
         <v>75</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="E86" s="5">
         <v>69</v>
@@ -7216,10 +7237,10 @@
         <v>24</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="H86" s="5" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="I86" s="5" t="s">
         <v>18</v>
@@ -7231,7 +7252,7 @@
         <v>5</v>
       </c>
       <c r="L86" s="6" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="M86" s="6" t="s">
         <v>84</v>
@@ -7248,10 +7269,10 @@
         <v>75</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="E87" s="5">
         <v>70</v>
@@ -7260,10 +7281,10 @@
         <v>24</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="H87" s="5" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="I87" s="5" t="s">
         <v>18</v>
@@ -7275,7 +7296,7 @@
         <v>5</v>
       </c>
       <c r="L87" s="6" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="M87" s="6" t="s">
         <v>84</v>
@@ -7292,10 +7313,10 @@
         <v>75</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="E88" s="5">
         <v>71</v>
@@ -7304,7 +7325,7 @@
         <v>24</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="H88" s="5" t="s">
         <v>196</v>
@@ -7319,7 +7340,7 @@
         <v>5</v>
       </c>
       <c r="L88" s="6" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="M88" s="6" t="s">
         <v>84</v>
@@ -7336,10 +7357,10 @@
         <v>75</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="E89" s="5">
         <v>72</v>
@@ -7348,10 +7369,10 @@
         <v>24</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="H89" s="5" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="I89" s="5" t="s">
         <v>18</v>
@@ -7363,7 +7384,7 @@
         <v>5</v>
       </c>
       <c r="L89" s="6" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="M89" s="6" t="s">
         <v>21</v>
@@ -7380,10 +7401,10 @@
         <v>75</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="E90" s="5">
         <v>73</v>
@@ -7392,10 +7413,10 @@
         <v>24</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="H90" s="5" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="I90" s="5" t="s">
         <v>18</v>
@@ -7407,7 +7428,7 @@
         <v>5</v>
       </c>
       <c r="L90" s="6" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="M90" s="6" t="s">
         <v>21</v>
@@ -7424,10 +7445,10 @@
         <v>75</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="E91" s="5">
         <v>74</v>
@@ -7436,10 +7457,10 @@
         <v>24</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="H91" s="5" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="I91" s="5" t="s">
         <v>18</v>
@@ -7451,7 +7472,7 @@
         <v>5</v>
       </c>
       <c r="L91" s="6" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="M91" s="6" t="s">
         <v>21</v>
@@ -7468,10 +7489,10 @@
         <v>75</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="E92" s="5">
         <v>75</v>
@@ -7480,10 +7501,10 @@
         <v>24</v>
       </c>
       <c r="G92" s="5" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="H92" s="5" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="I92" s="5" t="s">
         <v>18</v>
@@ -7495,7 +7516,7 @@
         <v>5</v>
       </c>
       <c r="L92" s="6" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="M92" s="6" t="s">
         <v>21</v>
@@ -7512,10 +7533,10 @@
         <v>75</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="E93" s="5">
         <v>76</v>
@@ -7524,7 +7545,7 @@
         <v>16</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="H93" s="5" t="s">
         <v>18</v>
@@ -7539,7 +7560,7 @@
         <v>5</v>
       </c>
       <c r="L93" s="6" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="M93" s="6" t="s">
         <v>40</v>
@@ -7556,10 +7577,10 @@
         <v>75</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="E94" s="5">
         <v>77</v>
@@ -7568,10 +7589,10 @@
         <v>24</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="H94" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="I94" s="5" t="s">
         <v>18</v>
@@ -7583,7 +7604,7 @@
         <v>5</v>
       </c>
       <c r="L94" s="6" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="M94" s="6" t="s">
         <v>40</v>
@@ -7600,10 +7621,10 @@
         <v>75</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="E95" s="5">
         <v>78</v>
@@ -7612,10 +7633,10 @@
         <v>24</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="H95" s="5" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="I95" s="5" t="s">
         <v>18</v>
@@ -7627,7 +7648,7 @@
         <v>5</v>
       </c>
       <c r="L95" s="6" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="M95" s="6" t="s">
         <v>40</v>
@@ -7644,10 +7665,10 @@
         <v>75</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="E96" s="5">
         <v>79</v>
@@ -7656,10 +7677,10 @@
         <v>24</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="H96" s="5" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="I96" s="5" t="s">
         <v>18</v>
@@ -7671,7 +7692,7 @@
         <v>5</v>
       </c>
       <c r="L96" s="6" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="M96" s="6" t="s">
         <v>40</v>
@@ -7688,10 +7709,10 @@
         <v>75</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="E97" s="5">
         <v>80</v>
@@ -7700,10 +7721,10 @@
         <v>24</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="H97" s="5" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="I97" s="5" t="s">
         <v>18</v>
@@ -7715,7 +7736,7 @@
         <v>5</v>
       </c>
       <c r="L97" s="6" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="M97" s="6" t="s">
         <v>40</v>
@@ -7732,10 +7753,10 @@
         <v>75</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E98" s="5">
         <v>81</v>
@@ -7744,10 +7765,10 @@
         <v>24</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="H98" s="5" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="I98" s="5" t="s">
         <v>18</v>
@@ -7759,7 +7780,7 @@
         <v>5</v>
       </c>
       <c r="L98" s="6" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="M98" s="6" t="s">
         <v>54</v>
@@ -7776,10 +7797,10 @@
         <v>75</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="E99" s="5">
         <v>82</v>
@@ -7788,10 +7809,10 @@
         <v>24</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="H99" s="5" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="I99" s="5" t="s">
         <v>18</v>
@@ -7803,7 +7824,7 @@
         <v>5</v>
       </c>
       <c r="L99" s="6" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="M99" s="6" t="s">
         <v>54</v>
@@ -7820,10 +7841,10 @@
         <v>75</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E100" s="5">
         <v>83</v>
@@ -7832,10 +7853,10 @@
         <v>24</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="H100" s="5" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="I100" s="5" t="s">
         <v>18</v>
@@ -7847,7 +7868,7 @@
         <v>5</v>
       </c>
       <c r="L100" s="6" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="M100" s="6" t="s">
         <v>54</v>
@@ -7864,10 +7885,10 @@
         <v>75</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="E101" s="5">
         <v>84</v>
@@ -7876,10 +7897,10 @@
         <v>24</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="H101" s="5" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="I101" s="5" t="s">
         <v>18</v>
@@ -7891,7 +7912,7 @@
         <v>5</v>
       </c>
       <c r="L101" s="6" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="M101" s="6" t="s">
         <v>54</v>
@@ -7908,10 +7929,10 @@
         <v>75</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="E102" s="5">
         <v>85</v>
@@ -7920,10 +7941,10 @@
         <v>24</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="H102" s="5" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="I102" s="5" t="s">
         <v>18</v>
@@ -7935,7 +7956,7 @@
         <v>5</v>
       </c>
       <c r="L102" s="6" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="M102" s="6" t="s">
         <v>68</v>
@@ -7952,10 +7973,10 @@
         <v>75</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="E103" s="5">
         <v>86</v>
@@ -7964,10 +7985,10 @@
         <v>24</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="H103" s="5" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="I103" s="5" t="s">
         <v>18</v>
@@ -7979,7 +8000,7 @@
         <v>5</v>
       </c>
       <c r="L103" s="6" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="M103" s="6" t="s">
         <v>68</v>
@@ -7993,13 +8014,13 @@
         <v>103</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E104" s="5">
         <v>1</v>
@@ -8008,7 +8029,7 @@
         <v>16</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="H104" s="5" t="s">
         <v>18</v>
@@ -8023,7 +8044,7 @@
         <v>6</v>
       </c>
       <c r="L104" s="6" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="M104" s="6" t="s">
         <v>84</v>
@@ -8037,13 +8058,13 @@
         <v>104</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="E105" s="5">
         <v>2</v>
@@ -8052,7 +8073,7 @@
         <v>16</v>
       </c>
       <c r="G105" s="5" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="H105" s="5" t="s">
         <v>18</v>
@@ -8067,7 +8088,7 @@
         <v>6</v>
       </c>
       <c r="L105" s="6" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="M105" s="6" t="s">
         <v>84</v>
@@ -8081,13 +8102,13 @@
         <v>105</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="E106" s="5">
         <v>3</v>
@@ -8096,10 +8117,10 @@
         <v>24</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="H106" s="5" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="I106" s="5" t="s">
         <v>18</v>
@@ -8111,7 +8132,7 @@
         <v>6</v>
       </c>
       <c r="L106" s="6" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="M106" s="6" t="s">
         <v>84</v>
@@ -8125,13 +8146,13 @@
         <v>106</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="E107" s="5">
         <v>4</v>
@@ -8140,10 +8161,10 @@
         <v>24</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H107" s="5" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="I107" s="5" t="s">
         <v>18</v>
@@ -8155,7 +8176,7 @@
         <v>6</v>
       </c>
       <c r="L107" s="6" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="M107" s="6" t="s">
         <v>84</v>
@@ -8169,13 +8190,13 @@
         <v>107</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="E108" s="5">
         <v>5</v>
@@ -8184,10 +8205,10 @@
         <v>24</v>
       </c>
       <c r="G108" s="5" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="H108" s="5" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="I108" s="5" t="s">
         <v>18</v>
@@ -8199,7 +8220,7 @@
         <v>6</v>
       </c>
       <c r="L108" s="6" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="M108" s="6" t="s">
         <v>84</v>
@@ -8213,13 +8234,13 @@
         <v>108</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="E109" s="5">
         <v>6</v>
@@ -8228,10 +8249,10 @@
         <v>24</v>
       </c>
       <c r="G109" s="5" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="H109" s="5" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="I109" s="5" t="s">
         <v>18</v>
@@ -8243,7 +8264,7 @@
         <v>6</v>
       </c>
       <c r="L109" s="6" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="M109" s="6" t="s">
         <v>84</v>
@@ -8257,13 +8278,13 @@
         <v>109</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="E110" s="5">
         <v>7</v>
@@ -8272,10 +8293,10 @@
         <v>24</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="H110" s="5" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="I110" s="5" t="s">
         <v>18</v>
@@ -8287,7 +8308,7 @@
         <v>6</v>
       </c>
       <c r="L110" s="6" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="M110" s="6" t="s">
         <v>21</v>
@@ -8301,13 +8322,13 @@
         <v>110</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="E111" s="5">
         <v>8</v>
@@ -8316,10 +8337,10 @@
         <v>24</v>
       </c>
       <c r="G111" s="5" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="H111" s="5" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="I111" s="5" t="s">
         <v>18</v>
@@ -8331,7 +8352,7 @@
         <v>6</v>
       </c>
       <c r="L111" s="6" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="M111" s="6" t="s">
         <v>21</v>
@@ -8345,13 +8366,13 @@
         <v>111</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E112" s="5">
         <v>9</v>
@@ -8360,10 +8381,10 @@
         <v>24</v>
       </c>
       <c r="G112" s="5" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="H112" s="5" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="I112" s="5" t="s">
         <v>18</v>
@@ -8375,7 +8396,7 @@
         <v>6</v>
       </c>
       <c r="L112" s="6" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="M112" s="6" t="s">
         <v>21</v>
@@ -8389,13 +8410,13 @@
         <v>112</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="E113" s="5">
         <v>10</v>
@@ -8404,10 +8425,10 @@
         <v>24</v>
       </c>
       <c r="G113" s="5" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="H113" s="5" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="I113" s="5" t="s">
         <v>18</v>
@@ -8419,7 +8440,7 @@
         <v>6</v>
       </c>
       <c r="L113" s="6" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="M113" s="6" t="s">
         <v>21</v>
@@ -8433,13 +8454,13 @@
         <v>113</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="E114" s="5">
         <v>11</v>
@@ -8448,10 +8469,10 @@
         <v>24</v>
       </c>
       <c r="G114" s="5" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="H114" s="5" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="I114" s="5" t="s">
         <v>18</v>
@@ -8463,7 +8484,7 @@
         <v>6</v>
       </c>
       <c r="L114" s="6" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="M114" s="6" t="s">
         <v>40</v>
@@ -8477,13 +8498,13 @@
         <v>114</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="E115" s="5">
         <v>12</v>
@@ -8492,10 +8513,10 @@
         <v>24</v>
       </c>
       <c r="G115" s="5" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="H115" s="5" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="I115" s="5" t="s">
         <v>18</v>
@@ -8507,7 +8528,7 @@
         <v>6</v>
       </c>
       <c r="L115" s="6" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="M115" s="6" t="s">
         <v>40</v>
@@ -8521,13 +8542,13 @@
         <v>115</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="E116" s="5">
         <v>13</v>
@@ -8536,10 +8557,10 @@
         <v>24</v>
       </c>
       <c r="G116" s="5" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="H116" s="5" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="I116" s="5" t="s">
         <v>18</v>
@@ -8551,7 +8572,7 @@
         <v>6</v>
       </c>
       <c r="L116" s="6" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="M116" s="6" t="s">
         <v>40</v>
@@ -8565,13 +8586,13 @@
         <v>116</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="E117" s="5">
         <v>14</v>
@@ -8580,10 +8601,10 @@
         <v>24</v>
       </c>
       <c r="G117" s="5" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="H117" s="5" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="I117" s="5" t="s">
         <v>18</v>
@@ -8595,7 +8616,7 @@
         <v>6</v>
       </c>
       <c r="L117" s="6" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="M117" s="6" t="s">
         <v>40</v>
@@ -8612,10 +8633,10 @@
         <v>75</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="E118" s="5">
         <v>88</v>
@@ -8624,7 +8645,7 @@
         <v>16</v>
       </c>
       <c r="G118" s="5" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="H118" s="5" t="s">
         <v>18</v>
@@ -8639,7 +8660,7 @@
         <v>6</v>
       </c>
       <c r="L118" s="6" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="M118" s="6" t="s">
         <v>54</v>
@@ -8656,10 +8677,10 @@
         <v>75</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="E119" s="5">
         <v>89</v>
@@ -8668,7 +8689,7 @@
         <v>16</v>
       </c>
       <c r="G119" s="5" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="H119" s="5" t="s">
         <v>18</v>
@@ -8683,7 +8704,7 @@
         <v>6</v>
       </c>
       <c r="L119" s="6" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="M119" s="6" t="s">
         <v>54</v>
@@ -8700,10 +8721,10 @@
         <v>75</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="E120" s="5">
         <v>90</v>
@@ -8712,10 +8733,10 @@
         <v>24</v>
       </c>
       <c r="G120" s="5" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="H120" s="5" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="I120" s="5" t="s">
         <v>18</v>
@@ -8727,7 +8748,7 @@
         <v>6</v>
       </c>
       <c r="L120" s="6" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="M120" s="6" t="s">
         <v>54</v>
@@ -8744,10 +8765,10 @@
         <v>75</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="E121" s="5">
         <v>91</v>
@@ -8756,10 +8777,10 @@
         <v>24</v>
       </c>
       <c r="G121" s="5" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="H121" s="5" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="I121" s="5" t="s">
         <v>18</v>
@@ -8771,7 +8792,7 @@
         <v>6</v>
       </c>
       <c r="L121" s="6" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="M121" s="6" t="s">
         <v>54</v>
@@ -8788,10 +8809,10 @@
         <v>75</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E122" s="5">
         <v>92</v>
@@ -8800,10 +8821,10 @@
         <v>24</v>
       </c>
       <c r="G122" s="5" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="H122" s="5" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="I122" s="5" t="s">
         <v>18</v>
@@ -8815,7 +8836,7 @@
         <v>6</v>
       </c>
       <c r="L122" s="6" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="M122" s="6" t="s">
         <v>54</v>
@@ -8832,10 +8853,10 @@
         <v>75</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="E123" s="5">
         <v>93</v>
@@ -8844,10 +8865,10 @@
         <v>24</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="H123" s="5" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="I123" s="5" t="s">
         <v>18</v>
@@ -8859,7 +8880,7 @@
         <v>6</v>
       </c>
       <c r="L123" s="6" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="M123" s="6" t="s">
         <v>54</v>
@@ -8876,10 +8897,10 @@
         <v>75</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="E124" s="5">
         <v>94</v>
@@ -8888,10 +8909,10 @@
         <v>24</v>
       </c>
       <c r="G124" s="5" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="H124" s="5" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="I124" s="5" t="s">
         <v>18</v>
@@ -8903,7 +8924,7 @@
         <v>6</v>
       </c>
       <c r="L124" s="6" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="M124" s="6" t="s">
         <v>68</v>
@@ -8920,10 +8941,10 @@
         <v>75</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="E125" s="5">
         <v>95</v>
@@ -8932,10 +8953,10 @@
         <v>24</v>
       </c>
       <c r="G125" s="5" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="H125" s="5" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="I125" s="5" t="s">
         <v>18</v>
@@ -8947,7 +8968,7 @@
         <v>6</v>
       </c>
       <c r="L125" s="6" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="M125" s="6" t="s">
         <v>68</v>
@@ -8964,10 +8985,10 @@
         <v>75</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="E126" s="5">
         <v>96</v>
@@ -8976,10 +8997,10 @@
         <v>24</v>
       </c>
       <c r="G126" s="5" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="H126" s="5" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="I126" s="5" t="s">
         <v>18</v>
@@ -8991,7 +9012,7 @@
         <v>6</v>
       </c>
       <c r="L126" s="6" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="M126" s="6" t="s">
         <v>68</v>
@@ -9008,10 +9029,10 @@
         <v>75</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="E127" s="5">
         <v>97</v>
@@ -9020,10 +9041,10 @@
         <v>24</v>
       </c>
       <c r="G127" s="5" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="H127" s="5" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="I127" s="5" t="s">
         <v>18</v>
@@ -9035,7 +9056,7 @@
         <v>6</v>
       </c>
       <c r="L127" s="6" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="M127" s="6" t="s">
         <v>68</v>
@@ -9049,13 +9070,13 @@
         <v>127</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="E128" s="5">
         <v>1</v>
@@ -9064,10 +9085,10 @@
         <v>24</v>
       </c>
       <c r="G128" s="5" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="H128" s="5" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="I128" s="5" t="s">
         <v>18</v>
@@ -9079,7 +9100,7 @@
         <v>7</v>
       </c>
       <c r="L128" s="6" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="M128" s="6" t="s">
         <v>84</v>
@@ -9093,13 +9114,13 @@
         <v>128</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="E129" s="5">
         <v>2</v>
@@ -9108,10 +9129,10 @@
         <v>24</v>
       </c>
       <c r="G129" s="5" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="H129" s="5" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="I129" s="5" t="s">
         <v>18</v>
@@ -9123,7 +9144,7 @@
         <v>7</v>
       </c>
       <c r="L129" s="6" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="M129" s="6" t="s">
         <v>84</v>
@@ -9137,13 +9158,13 @@
         <v>129</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="E130" s="5">
         <v>3</v>
@@ -9152,10 +9173,10 @@
         <v>24</v>
       </c>
       <c r="G130" s="5" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="H130" s="5" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="I130" s="5" t="s">
         <v>18</v>
@@ -9167,7 +9188,7 @@
         <v>7</v>
       </c>
       <c r="L130" s="6" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="M130" s="6" t="s">
         <v>84</v>
@@ -9181,13 +9202,13 @@
         <v>130</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="E131" s="5">
         <v>4</v>
@@ -9196,10 +9217,10 @@
         <v>24</v>
       </c>
       <c r="G131" s="5" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="H131" s="5" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="I131" s="5" t="s">
         <v>18</v>
@@ -9211,7 +9232,7 @@
         <v>7</v>
       </c>
       <c r="L131" s="6" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="M131" s="6" t="s">
         <v>84</v>
@@ -9225,13 +9246,13 @@
         <v>131</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E132" s="5">
         <v>5</v>
@@ -9240,10 +9261,10 @@
         <v>24</v>
       </c>
       <c r="G132" s="5" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="H132" s="5" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="I132" s="5" t="s">
         <v>18</v>
@@ -9255,7 +9276,7 @@
         <v>7</v>
       </c>
       <c r="L132" s="6" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="M132" s="6" t="s">
         <v>21</v>
@@ -9269,13 +9290,13 @@
         <v>132</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="E133" s="5">
         <v>6</v>
@@ -9284,10 +9305,10 @@
         <v>24</v>
       </c>
       <c r="G133" s="5" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="H133" s="5" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="I133" s="5" t="s">
         <v>18</v>
@@ -9299,7 +9320,7 @@
         <v>7</v>
       </c>
       <c r="L133" s="6" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="M133" s="6" t="s">
         <v>21</v>
@@ -9313,13 +9334,13 @@
         <v>133</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="E134" s="5">
         <v>7</v>
@@ -9328,10 +9349,10 @@
         <v>24</v>
       </c>
       <c r="G134" s="5" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="H134" s="5" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="I134" s="5" t="s">
         <v>18</v>
@@ -9343,7 +9364,7 @@
         <v>7</v>
       </c>
       <c r="L134" s="6" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="M134" s="6" t="s">
         <v>21</v>
@@ -9357,13 +9378,13 @@
         <v>134</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="E135" s="5">
         <v>8</v>
@@ -9372,10 +9393,10 @@
         <v>24</v>
       </c>
       <c r="G135" s="5" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="H135" s="5" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="I135" s="5" t="s">
         <v>18</v>
@@ -9387,7 +9408,7 @@
         <v>7</v>
       </c>
       <c r="L135" s="6" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="M135" s="6" t="s">
         <v>21</v>
@@ -9401,13 +9422,13 @@
         <v>135</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="E136" s="5">
         <v>9</v>
@@ -9416,10 +9437,10 @@
         <v>24</v>
       </c>
       <c r="G136" s="5" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="H136" s="5" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="I136" s="5" t="s">
         <v>18</v>
@@ -9431,7 +9452,7 @@
         <v>7</v>
       </c>
       <c r="L136" s="6" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="M136" s="6" t="s">
         <v>40</v>
@@ -9445,13 +9466,13 @@
         <v>136</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="E137" s="5">
         <v>10</v>
@@ -9460,10 +9481,10 @@
         <v>24</v>
       </c>
       <c r="G137" s="5" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="H137" s="5" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="I137" s="5" t="s">
         <v>18</v>
@@ -9475,7 +9496,7 @@
         <v>7</v>
       </c>
       <c r="L137" s="6" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="M137" s="6" t="s">
         <v>40</v>
@@ -9489,13 +9510,13 @@
         <v>137</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="E138" s="5">
         <v>11</v>
@@ -9504,10 +9525,10 @@
         <v>24</v>
       </c>
       <c r="G138" s="5" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="H138" s="5" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="I138" s="5" t="s">
         <v>18</v>
@@ -9519,7 +9540,7 @@
         <v>7</v>
       </c>
       <c r="L138" s="6" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="M138" s="6" t="s">
         <v>40</v>
@@ -9533,13 +9554,13 @@
         <v>138</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="E139" s="5">
         <v>12</v>
@@ -9548,10 +9569,10 @@
         <v>24</v>
       </c>
       <c r="G139" s="5" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="H139" s="5" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="I139" s="5" t="s">
         <v>18</v>
@@ -9563,7 +9584,7 @@
         <v>7</v>
       </c>
       <c r="L139" s="6" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="M139" s="6" t="s">
         <v>40</v>
@@ -9577,13 +9598,13 @@
         <v>139</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="E140" s="5">
         <v>13</v>
@@ -9592,10 +9613,10 @@
         <v>24</v>
       </c>
       <c r="G140" s="5" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="H140" s="5" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="I140" s="5" t="s">
         <v>18</v>
@@ -9607,7 +9628,7 @@
         <v>7</v>
       </c>
       <c r="L140" s="6" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="M140" s="6" t="s">
         <v>54</v>
@@ -9621,13 +9642,13 @@
         <v>140</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="E141" s="5">
         <v>14</v>
@@ -9636,10 +9657,10 @@
         <v>24</v>
       </c>
       <c r="G141" s="5" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="H141" s="5" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="I141" s="5" t="s">
         <v>18</v>
@@ -9651,7 +9672,7 @@
         <v>7</v>
       </c>
       <c r="L141" s="6" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="M141" s="6" t="s">
         <v>54</v>
@@ -9665,13 +9686,13 @@
         <v>141</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="E142" s="5">
         <v>15</v>
@@ -9680,10 +9701,10 @@
         <v>24</v>
       </c>
       <c r="G142" s="5" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="H142" s="5" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="I142" s="5" t="s">
         <v>18</v>
@@ -9695,7 +9716,7 @@
         <v>7</v>
       </c>
       <c r="L142" s="6" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="M142" s="6" t="s">
         <v>54</v>
@@ -9709,13 +9730,13 @@
         <v>142</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="E143" s="5">
         <v>16</v>
@@ -9724,10 +9745,10 @@
         <v>24</v>
       </c>
       <c r="G143" s="5" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="H143" s="5" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="I143" s="5" t="s">
         <v>18</v>
@@ -9739,7 +9760,7 @@
         <v>7</v>
       </c>
       <c r="L143" s="6" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="M143" s="6" t="s">
         <v>54</v>
@@ -9753,13 +9774,13 @@
         <v>143</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="E144" s="5">
         <v>17</v>
@@ -9768,10 +9789,10 @@
         <v>24</v>
       </c>
       <c r="G144" s="5" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="H144" s="5" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="I144" s="5" t="s">
         <v>18</v>
@@ -9783,7 +9804,7 @@
         <v>7</v>
       </c>
       <c r="L144" s="6" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="M144" s="6" t="s">
         <v>68</v>
@@ -9797,13 +9818,13 @@
         <v>144</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="E145" s="5">
         <v>18</v>
@@ -9812,10 +9833,10 @@
         <v>24</v>
       </c>
       <c r="G145" s="5" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="H145" s="5" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="I145" s="5" t="s">
         <v>18</v>
@@ -9827,7 +9848,7 @@
         <v>7</v>
       </c>
       <c r="L145" s="6" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="M145" s="6" t="s">
         <v>68</v>
@@ -9841,13 +9862,13 @@
         <v>145</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="E146" s="5">
         <v>19</v>
@@ -9856,10 +9877,10 @@
         <v>24</v>
       </c>
       <c r="G146" s="5" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="H146" s="5" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="I146" s="5" t="s">
         <v>18</v>
@@ -9871,7 +9892,7 @@
         <v>7</v>
       </c>
       <c r="L146" s="6" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="M146" s="6" t="s">
         <v>68</v>
@@ -9885,13 +9906,13 @@
         <v>146</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="E147" s="5">
         <v>20</v>
@@ -9900,10 +9921,10 @@
         <v>24</v>
       </c>
       <c r="G147" s="5" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="H147" s="5" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="I147" s="5" t="s">
         <v>18</v>
@@ -9915,7 +9936,7 @@
         <v>7</v>
       </c>
       <c r="L147" s="6" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="M147" s="6" t="s">
         <v>68</v>
@@ -9929,13 +9950,13 @@
         <v>147</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="E148" s="5">
         <v>21</v>
@@ -9944,10 +9965,10 @@
         <v>24</v>
       </c>
       <c r="G148" s="5" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="H148" s="5" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="I148" s="5" t="s">
         <v>18</v>
@@ -9959,7 +9980,7 @@
         <v>8</v>
       </c>
       <c r="L148" s="6" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="M148" s="6" t="s">
         <v>84</v>
@@ -9973,13 +9994,13 @@
         <v>148</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="E149" s="5">
         <v>22</v>
@@ -9988,10 +10009,10 @@
         <v>24</v>
       </c>
       <c r="G149" s="5" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="H149" s="5" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="I149" s="5" t="s">
         <v>18</v>
@@ -10003,7 +10024,7 @@
         <v>8</v>
       </c>
       <c r="L149" s="6" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="M149" s="6" t="s">
         <v>84</v>
@@ -10017,13 +10038,13 @@
         <v>149</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="E150" s="5">
         <v>23</v>
@@ -10032,10 +10053,10 @@
         <v>24</v>
       </c>
       <c r="G150" s="5" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="H150" s="5" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="I150" s="5" t="s">
         <v>18</v>
@@ -10047,7 +10068,7 @@
         <v>8</v>
       </c>
       <c r="L150" s="6" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="M150" s="6" t="s">
         <v>84</v>
@@ -10061,13 +10082,13 @@
         <v>150</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="E151" s="5">
         <v>24</v>
@@ -10076,10 +10097,10 @@
         <v>24</v>
       </c>
       <c r="G151" s="5" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="H151" s="5" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="I151" s="5" t="s">
         <v>18</v>
@@ -10091,7 +10112,7 @@
         <v>8</v>
       </c>
       <c r="L151" s="6" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="M151" s="6" t="s">
         <v>84</v>
@@ -10105,13 +10126,13 @@
         <v>151</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="E152" s="5">
         <v>25</v>
@@ -10120,10 +10141,10 @@
         <v>24</v>
       </c>
       <c r="G152" s="5" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="H152" s="5" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="I152" s="5" t="s">
         <v>18</v>
@@ -10135,7 +10156,7 @@
         <v>8</v>
       </c>
       <c r="L152" s="6" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="M152" s="6" t="s">
         <v>21</v>
@@ -10149,13 +10170,13 @@
         <v>152</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="E153" s="5">
         <v>26</v>
@@ -10164,10 +10185,10 @@
         <v>24</v>
       </c>
       <c r="G153" s="5" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="H153" s="5" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="I153" s="5" t="s">
         <v>18</v>
@@ -10179,7 +10200,7 @@
         <v>8</v>
       </c>
       <c r="L153" s="6" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="M153" s="6" t="s">
         <v>21</v>
@@ -10193,13 +10214,13 @@
         <v>153</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="E154" s="5">
         <v>27</v>
@@ -10208,10 +10229,10 @@
         <v>24</v>
       </c>
       <c r="G154" s="5" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="H154" s="5" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="I154" s="5" t="s">
         <v>18</v>
@@ -10223,7 +10244,7 @@
         <v>8</v>
       </c>
       <c r="L154" s="6" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="M154" s="6" t="s">
         <v>21</v>
@@ -10237,13 +10258,13 @@
         <v>154</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="E155" s="5">
         <v>28</v>
@@ -10252,10 +10273,10 @@
         <v>24</v>
       </c>
       <c r="G155" s="5" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="H155" s="5" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="I155" s="5" t="s">
         <v>18</v>
@@ -10267,7 +10288,7 @@
         <v>8</v>
       </c>
       <c r="L155" s="6" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="M155" s="6" t="s">
         <v>21</v>
@@ -10281,13 +10302,13 @@
         <v>155</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="E156" s="5">
         <v>29</v>
@@ -10296,10 +10317,10 @@
         <v>24</v>
       </c>
       <c r="G156" s="5" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="H156" s="5" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="I156" s="5" t="s">
         <v>18</v>
@@ -10311,7 +10332,7 @@
         <v>8</v>
       </c>
       <c r="L156" s="6" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="M156" s="6" t="s">
         <v>21</v>
@@ -10325,13 +10346,13 @@
         <v>156</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E157" s="5">
         <v>30</v>
@@ -10340,7 +10361,7 @@
         <v>16</v>
       </c>
       <c r="G157" s="5" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="H157" s="5" t="s">
         <v>18</v>
@@ -10355,7 +10376,7 @@
         <v>8</v>
       </c>
       <c r="L157" s="6" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="M157" s="6" t="s">
         <v>40</v>
@@ -10369,13 +10390,13 @@
         <v>157</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="E158" s="5">
         <v>31</v>
@@ -10384,7 +10405,7 @@
         <v>16</v>
       </c>
       <c r="G158" s="5" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="H158" s="5" t="s">
         <v>18</v>
@@ -10399,7 +10420,7 @@
         <v>8</v>
       </c>
       <c r="L158" s="6" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="M158" s="6" t="s">
         <v>40</v>
@@ -10413,13 +10434,13 @@
         <v>158</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="E159" s="5">
         <v>32</v>
@@ -10428,7 +10449,7 @@
         <v>16</v>
       </c>
       <c r="G159" s="5" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="H159" s="5" t="s">
         <v>18</v>
@@ -10443,7 +10464,7 @@
         <v>8</v>
       </c>
       <c r="L159" s="6" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="M159" s="6" t="s">
         <v>40</v>
@@ -10457,13 +10478,13 @@
         <v>159</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="E160" s="5">
         <v>33</v>
@@ -10472,10 +10493,10 @@
         <v>24</v>
       </c>
       <c r="G160" s="5" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="H160" s="5" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="I160" s="5" t="s">
         <v>18</v>
@@ -10487,7 +10508,7 @@
         <v>8</v>
       </c>
       <c r="L160" s="6" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="M160" s="6" t="s">
         <v>40</v>
@@ -10501,13 +10522,13 @@
         <v>160</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="E161" s="5">
         <v>34</v>
@@ -10516,10 +10537,10 @@
         <v>24</v>
       </c>
       <c r="G161" s="5" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="H161" s="5" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="I161" s="5" t="s">
         <v>18</v>
@@ -10531,7 +10552,7 @@
         <v>8</v>
       </c>
       <c r="L161" s="6" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="M161" s="6" t="s">
         <v>40</v>
@@ -10545,13 +10566,13 @@
         <v>161</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="E162" s="5">
         <v>35</v>
@@ -10560,10 +10581,10 @@
         <v>24</v>
       </c>
       <c r="G162" s="5" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="H162" s="5" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="I162" s="5" t="s">
         <v>18</v>
@@ -10575,7 +10596,7 @@
         <v>8</v>
       </c>
       <c r="L162" s="6" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="M162" s="6" t="s">
         <v>40</v>
@@ -10589,13 +10610,13 @@
         <v>162</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="E163" s="5">
         <v>36</v>
@@ -10604,10 +10625,10 @@
         <v>24</v>
       </c>
       <c r="G163" s="5" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="H163" s="5" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="I163" s="5" t="s">
         <v>18</v>
@@ -10619,7 +10640,7 @@
         <v>8</v>
       </c>
       <c r="L163" s="6" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="M163" s="6" t="s">
         <v>40</v>
@@ -10633,13 +10654,13 @@
         <v>163</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="E164" s="5">
         <v>37</v>
@@ -10648,10 +10669,10 @@
         <v>24</v>
       </c>
       <c r="G164" s="5" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="H164" s="5" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="I164" s="5" t="s">
         <v>18</v>
@@ -10663,7 +10684,7 @@
         <v>8</v>
       </c>
       <c r="L164" s="6" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="M164" s="6" t="s">
         <v>54</v>
@@ -10677,13 +10698,13 @@
         <v>164</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="E165" s="5">
         <v>38</v>
@@ -10692,10 +10713,10 @@
         <v>24</v>
       </c>
       <c r="G165" s="5" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="H165" s="5" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="I165" s="5" t="s">
         <v>18</v>
@@ -10707,7 +10728,7 @@
         <v>8</v>
       </c>
       <c r="L165" s="6" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="M165" s="6" t="s">
         <v>54</v>
@@ -10721,13 +10742,13 @@
         <v>165</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="E166" s="5">
         <v>39</v>
@@ -10736,10 +10757,10 @@
         <v>24</v>
       </c>
       <c r="G166" s="5" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="H166" s="5" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="I166" s="5" t="s">
         <v>18</v>
@@ -10751,7 +10772,7 @@
         <v>8</v>
       </c>
       <c r="L166" s="6" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="M166" s="6" t="s">
         <v>54</v>
@@ -10765,13 +10786,13 @@
         <v>166</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="E167" s="5">
         <v>40</v>
@@ -10780,10 +10801,10 @@
         <v>24</v>
       </c>
       <c r="G167" s="5" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="H167" s="5" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="I167" s="5" t="s">
         <v>18</v>
@@ -10795,7 +10816,7 @@
         <v>8</v>
       </c>
       <c r="L167" s="6" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="M167" s="6" t="s">
         <v>54</v>
@@ -10809,13 +10830,13 @@
         <v>167</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="E168" s="5">
         <v>41</v>
@@ -10824,10 +10845,10 @@
         <v>24</v>
       </c>
       <c r="G168" s="5" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="H168" s="5" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="I168" s="5" t="s">
         <v>18</v>
@@ -10839,7 +10860,7 @@
         <v>8</v>
       </c>
       <c r="L168" s="6" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="M168" s="6" t="s">
         <v>54</v>
@@ -10853,13 +10874,13 @@
         <v>168</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="E169" s="5">
         <v>42</v>
@@ -10868,10 +10889,10 @@
         <v>24</v>
       </c>
       <c r="G169" s="5" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="H169" s="5" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="I169" s="5" t="s">
         <v>18</v>
@@ -10883,7 +10904,7 @@
         <v>8</v>
       </c>
       <c r="L169" s="6" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="M169" s="6" t="s">
         <v>68</v>
@@ -10897,13 +10918,13 @@
         <v>169</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D170" s="5" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="E170" s="5">
         <v>43</v>
@@ -10912,10 +10933,10 @@
         <v>24</v>
       </c>
       <c r="G170" s="5" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="H170" s="5" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="I170" s="5" t="s">
         <v>18</v>
@@ -10927,7 +10948,7 @@
         <v>8</v>
       </c>
       <c r="L170" s="6" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="M170" s="6" t="s">
         <v>68</v>
@@ -10941,13 +10962,13 @@
         <v>170</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D171" s="5" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="E171" s="5">
         <v>44</v>
@@ -10956,10 +10977,10 @@
         <v>24</v>
       </c>
       <c r="G171" s="5" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="H171" s="5" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="I171" s="5" t="s">
         <v>18</v>
@@ -10971,7 +10992,7 @@
         <v>8</v>
       </c>
       <c r="L171" s="6" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="M171" s="6" t="s">
         <v>68</v>
@@ -10985,13 +11006,13 @@
         <v>171</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D172" s="5" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="E172" s="5">
         <v>45</v>
@@ -11000,10 +11021,10 @@
         <v>24</v>
       </c>
       <c r="G172" s="5" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="H172" s="5" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="I172" s="5" t="s">
         <v>18</v>
@@ -11015,7 +11036,7 @@
         <v>8</v>
       </c>
       <c r="L172" s="6" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="M172" s="6" t="s">
         <v>68</v>
@@ -11024,71 +11045,67 @@
         <v>18</v>
       </c>
     </row>
-    <row r="173" spans="1:14">
+    <row r="173" ht="27.6" spans="1:14">
       <c r="A173" s="5">
         <v>172</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>569</v>
+        <v>427</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>570</v>
+        <v>525</v>
       </c>
       <c r="D173" s="5" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E173" s="5">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="F173" s="5" t="s">
         <v>16</v>
       </c>
       <c r="G173" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="H173" s="5" t="s">
-        <v>18</v>
-      </c>
+        <v>574</v>
+      </c>
+      <c r="H173" s="5"/>
       <c r="I173" s="5" t="s">
-        <v>172</v>
+        <v>19</v>
       </c>
       <c r="J173" s="5">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K173" s="5">
         <v>9</v>
       </c>
       <c r="L173" s="6" t="s">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="M173" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="N173" s="6" t="s">
-        <v>22</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="N173" s="6"/>
     </row>
     <row r="174" spans="1:14">
       <c r="A174" s="5">
         <v>173</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="D174" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="E174" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F174" s="5" t="s">
         <v>16</v>
       </c>
       <c r="G174" s="5" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H174" s="5" t="s">
         <v>18</v>
@@ -11103,7 +11120,7 @@
         <v>9</v>
       </c>
       <c r="L174" s="6" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="M174" s="6" t="s">
         <v>84</v>
@@ -11117,28 +11134,28 @@
         <v>174</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="D175" s="5" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="E175" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F175" s="5" t="s">
         <v>16</v>
       </c>
       <c r="G175" s="5" t="s">
-        <v>13</v>
+        <v>359</v>
       </c>
       <c r="H175" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I175" s="5" t="s">
-        <v>132</v>
+        <v>172</v>
       </c>
       <c r="J175" s="5">
         <v>40</v>
@@ -11147,7 +11164,7 @@
         <v>9</v>
       </c>
       <c r="L175" s="6" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="M175" s="6" t="s">
         <v>84</v>
@@ -11161,28 +11178,28 @@
         <v>175</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="D176" s="5" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="E176" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F176" s="5" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G176" s="5" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="H176" s="5" t="s">
-        <v>576</v>
+        <v>18</v>
       </c>
       <c r="I176" s="5" t="s">
-        <v>18</v>
+        <v>132</v>
       </c>
       <c r="J176" s="5">
         <v>40</v>
@@ -11191,13 +11208,13 @@
         <v>9</v>
       </c>
       <c r="L176" s="6" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="M176" s="6" t="s">
         <v>84</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="177" spans="1:14">
@@ -11205,25 +11222,25 @@
         <v>176</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="D177" s="5" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="E177" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F177" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G177" s="5" t="s">
-        <v>578</v>
+        <v>25</v>
       </c>
       <c r="H177" s="5" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="I177" s="5" t="s">
         <v>18</v>
@@ -11235,7 +11252,7 @@
         <v>9</v>
       </c>
       <c r="L177" s="6" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="M177" s="6" t="s">
         <v>84</v>
@@ -11244,30 +11261,30 @@
         <v>18</v>
       </c>
     </row>
-    <row r="178" ht="27.6" spans="1:14">
+    <row r="178" spans="1:14">
       <c r="A178" s="5">
         <v>177</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="D178" s="5" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="E178" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F178" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G178" s="5" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="H178" s="5" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="I178" s="5" t="s">
         <v>18</v>
@@ -11279,7 +11296,7 @@
         <v>9</v>
       </c>
       <c r="L178" s="6" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="M178" s="6" t="s">
         <v>84</v>
@@ -11288,30 +11305,30 @@
         <v>18</v>
       </c>
     </row>
-    <row r="179" spans="1:14">
+    <row r="179" ht="27.6" spans="1:14">
       <c r="A179" s="5">
         <v>178</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="D179" s="5" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="E179" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F179" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G179" s="5" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="H179" s="5" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="I179" s="5" t="s">
         <v>18</v>
@@ -11323,7 +11340,7 @@
         <v>9</v>
       </c>
       <c r="L179" s="6" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="M179" s="6" t="s">
         <v>84</v>
@@ -11337,40 +11354,40 @@
         <v>179</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="D180" s="5" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="E180" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F180" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G180" s="5" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="H180" s="5" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="I180" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J180" s="5">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K180" s="5">
         <v>9</v>
       </c>
       <c r="L180" s="6" t="s">
-        <v>589</v>
+        <v>578</v>
       </c>
       <c r="M180" s="6" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="N180" s="6" t="s">
         <v>18</v>
@@ -11381,25 +11398,25 @@
         <v>180</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="D181" s="5" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="E181" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F181" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G181" s="5" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="H181" s="5" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="I181" s="5" t="s">
         <v>18</v>
@@ -11411,7 +11428,7 @@
         <v>9</v>
       </c>
       <c r="L181" s="6" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="M181" s="6" t="s">
         <v>21</v>
@@ -11425,25 +11442,25 @@
         <v>181</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="D182" s="5" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="E182" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F182" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G182" s="5" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="H182" s="5" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="I182" s="5" t="s">
         <v>18</v>
@@ -11455,7 +11472,7 @@
         <v>9</v>
       </c>
       <c r="L182" s="6" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="M182" s="6" t="s">
         <v>21</v>
@@ -11469,25 +11486,25 @@
         <v>182</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="E183" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F183" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G183" s="5" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="H183" s="5" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="I183" s="5" t="s">
         <v>18</v>
@@ -11499,7 +11516,7 @@
         <v>9</v>
       </c>
       <c r="L183" s="6" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="M183" s="6" t="s">
         <v>21</v>
@@ -11513,40 +11530,40 @@
         <v>183</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="D184" s="5" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="E184" s="5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F184" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G184" s="5" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="H184" s="5" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="I184" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J184" s="5">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K184" s="5">
         <v>9</v>
       </c>
       <c r="L184" s="6" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
       <c r="M184" s="6" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="N184" s="6" t="s">
         <v>18</v>
@@ -11557,25 +11574,25 @@
         <v>184</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="D185" s="5" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="E185" s="5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F185" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G185" s="5" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="H185" s="5" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="I185" s="5" t="s">
         <v>18</v>
@@ -11587,7 +11604,7 @@
         <v>9</v>
       </c>
       <c r="L185" s="6" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="M185" s="6" t="s">
         <v>40</v>
@@ -11601,25 +11618,25 @@
         <v>185</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="D186" s="5" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="E186" s="5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F186" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G186" s="5" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="H186" s="5" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="I186" s="5" t="s">
         <v>18</v>
@@ -11631,7 +11648,7 @@
         <v>9</v>
       </c>
       <c r="L186" s="6" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="M186" s="6" t="s">
         <v>40</v>
@@ -11645,25 +11662,25 @@
         <v>186</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="D187" s="5" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="E187" s="5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F187" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G187" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="H187" s="5" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="I187" s="5" t="s">
         <v>18</v>
@@ -11675,7 +11692,7 @@
         <v>9</v>
       </c>
       <c r="L187" s="6" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="M187" s="6" t="s">
         <v>40</v>
@@ -11689,40 +11706,40 @@
         <v>187</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="D188" s="5" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="E188" s="5">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F188" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G188" s="5" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="H188" s="5" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="I188" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J188" s="5">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K188" s="5">
         <v>9</v>
       </c>
       <c r="L188" s="6" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="M188" s="6" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="N188" s="6" t="s">
         <v>18</v>
@@ -11733,25 +11750,25 @@
         <v>188</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="D189" s="5" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="E189" s="5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F189" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G189" s="5" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="H189" s="5" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="I189" s="5" t="s">
         <v>18</v>
@@ -11763,7 +11780,7 @@
         <v>9</v>
       </c>
       <c r="L189" s="6" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="M189" s="6" t="s">
         <v>54</v>
@@ -11777,25 +11794,25 @@
         <v>189</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="D190" s="5" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="E190" s="5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F190" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G190" s="5" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="H190" s="5" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="I190" s="5" t="s">
         <v>18</v>
@@ -11807,7 +11824,7 @@
         <v>9</v>
       </c>
       <c r="L190" s="6" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="M190" s="6" t="s">
         <v>54</v>
@@ -11821,25 +11838,25 @@
         <v>190</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="D191" s="5" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="E191" s="5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F191" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G191" s="5" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="H191" s="5" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="I191" s="5" t="s">
         <v>18</v>
@@ -11851,7 +11868,7 @@
         <v>9</v>
       </c>
       <c r="L191" s="6" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="M191" s="6" t="s">
         <v>54</v>
@@ -11865,40 +11882,40 @@
         <v>191</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="D192" s="5" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="E192" s="5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F192" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G192" s="5" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="H192" s="5" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="I192" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J192" s="5">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K192" s="5">
         <v>9</v>
       </c>
       <c r="L192" s="6" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="M192" s="6" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="N192" s="6" t="s">
         <v>18</v>
@@ -11909,25 +11926,25 @@
         <v>192</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="D193" s="5" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="E193" s="5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F193" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G193" s="5" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="H193" s="5" t="s">
-        <v>193</v>
+        <v>633</v>
       </c>
       <c r="I193" s="5" t="s">
         <v>18</v>
@@ -11939,7 +11956,7 @@
         <v>9</v>
       </c>
       <c r="L193" s="6" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="M193" s="6" t="s">
         <v>68</v>
@@ -11953,25 +11970,25 @@
         <v>193</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="D194" s="5" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="E194" s="5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F194" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G194" s="5" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="H194" s="5" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="I194" s="5" t="s">
         <v>18</v>
@@ -11983,7 +12000,7 @@
         <v>9</v>
       </c>
       <c r="L194" s="6" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="M194" s="6" t="s">
         <v>68</v>
@@ -11997,25 +12014,25 @@
         <v>194</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="D195" s="5" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="E195" s="5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F195" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G195" s="5" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="H195" s="5" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="I195" s="5" t="s">
         <v>18</v>
@@ -12027,7 +12044,7 @@
         <v>9</v>
       </c>
       <c r="L195" s="6" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="M195" s="6" t="s">
         <v>68</v>
@@ -12041,40 +12058,40 @@
         <v>195</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="D196" s="5" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="E196" s="5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F196" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G196" s="5" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="H196" s="5" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="I196" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J196" s="5">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K196" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L196" s="6" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="M196" s="6" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="N196" s="6" t="s">
         <v>18</v>
@@ -12085,25 +12102,25 @@
         <v>196</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="D197" s="5" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="E197" s="5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F197" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G197" s="5" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="H197" s="5" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="I197" s="5" t="s">
         <v>18</v>
@@ -12115,7 +12132,7 @@
         <v>10</v>
       </c>
       <c r="L197" s="6" t="s">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="M197" s="6" t="s">
         <v>84</v>
@@ -12129,25 +12146,25 @@
         <v>197</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="D198" s="5" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="E198" s="5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F198" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G198" s="5" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="H198" s="5" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="I198" s="5" t="s">
         <v>18</v>
@@ -12159,7 +12176,7 @@
         <v>10</v>
       </c>
       <c r="L198" s="6" t="s">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="M198" s="6" t="s">
         <v>84</v>
@@ -12173,25 +12190,25 @@
         <v>198</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="D199" s="5" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="E199" s="5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F199" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G199" s="5" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="H199" s="5" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="I199" s="5" t="s">
         <v>18</v>
@@ -12203,7 +12220,7 @@
         <v>10</v>
       </c>
       <c r="L199" s="6" t="s">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="M199" s="6" t="s">
         <v>84</v>
@@ -12217,40 +12234,40 @@
         <v>199</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="D200" s="5" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="E200" s="5">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F200" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G200" s="5" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="H200" s="5" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="I200" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J200" s="5">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K200" s="5">
         <v>10</v>
       </c>
       <c r="L200" s="6" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="M200" s="6" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="N200" s="6" t="s">
         <v>18</v>
@@ -12261,25 +12278,25 @@
         <v>200</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="D201" s="5" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="E201" s="5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F201" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G201" s="5" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="H201" s="5" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="I201" s="5" t="s">
         <v>18</v>
@@ -12291,7 +12308,7 @@
         <v>10</v>
       </c>
       <c r="L201" s="6" t="s">
-        <v>653</v>
+        <v>660</v>
       </c>
       <c r="M201" s="6" t="s">
         <v>21</v>
@@ -12305,25 +12322,25 @@
         <v>201</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="D202" s="5" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="E202" s="5">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F202" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G202" s="5" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="H202" s="5" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="I202" s="5" t="s">
         <v>18</v>
@@ -12335,7 +12352,7 @@
         <v>10</v>
       </c>
       <c r="L202" s="6" t="s">
-        <v>653</v>
+        <v>660</v>
       </c>
       <c r="M202" s="6" t="s">
         <v>21</v>
@@ -12349,25 +12366,25 @@
         <v>202</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="D203" s="5" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="E203" s="5">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F203" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G203" s="5" t="s">
-        <v>73</v>
+        <v>665</v>
       </c>
       <c r="H203" s="5" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="I203" s="5" t="s">
         <v>18</v>
@@ -12379,7 +12396,7 @@
         <v>10</v>
       </c>
       <c r="L203" s="6" t="s">
-        <v>653</v>
+        <v>660</v>
       </c>
       <c r="M203" s="6" t="s">
         <v>21</v>
@@ -12393,40 +12410,40 @@
         <v>203</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>662</v>
+        <v>575</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>663</v>
+        <v>576</v>
       </c>
       <c r="D204" s="5" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="E204" s="5">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="F204" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G204" s="5" t="s">
-        <v>665</v>
+        <v>73</v>
       </c>
       <c r="H204" s="5" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="I204" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J204" s="5">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K204" s="5">
         <v>10</v>
       </c>
       <c r="L204" s="6" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="M204" s="6" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="N204" s="6" t="s">
         <v>18</v>
@@ -12437,25 +12454,25 @@
         <v>204</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="D205" s="5" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="E205" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F205" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G205" s="5" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="H205" s="5" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="I205" s="5" t="s">
         <v>18</v>
@@ -12467,7 +12484,7 @@
         <v>10</v>
       </c>
       <c r="L205" s="6" t="s">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="M205" s="6" t="s">
         <v>40</v>
@@ -12481,25 +12498,25 @@
         <v>205</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="D206" s="5" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="E206" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F206" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G206" s="5" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="H206" s="5" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="I206" s="5" t="s">
         <v>18</v>
@@ -12511,7 +12528,7 @@
         <v>10</v>
       </c>
       <c r="L206" s="6" t="s">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="M206" s="6" t="s">
         <v>40</v>
@@ -12525,25 +12542,25 @@
         <v>206</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="D207" s="5" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="E207" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F207" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G207" s="5" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="H207" s="5" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="I207" s="5" t="s">
         <v>18</v>
@@ -12555,7 +12572,7 @@
         <v>10</v>
       </c>
       <c r="L207" s="6" t="s">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="M207" s="6" t="s">
         <v>40</v>
@@ -12569,40 +12586,40 @@
         <v>207</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="D208" s="5" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="E208" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F208" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G208" s="5" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="H208" s="5" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="I208" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J208" s="5">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K208" s="5">
         <v>10</v>
       </c>
       <c r="L208" s="6" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="M208" s="6" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="N208" s="6" t="s">
         <v>18</v>
@@ -12613,25 +12630,25 @@
         <v>208</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="D209" s="5" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="E209" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F209" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G209" s="5" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="H209" s="5" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="I209" s="5" t="s">
         <v>18</v>
@@ -12643,7 +12660,7 @@
         <v>10</v>
       </c>
       <c r="L209" s="6" t="s">
-        <v>680</v>
+        <v>687</v>
       </c>
       <c r="M209" s="6" t="s">
         <v>54</v>
@@ -12657,25 +12674,25 @@
         <v>209</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="D210" s="5" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="E210" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F210" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G210" s="5" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="H210" s="5" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="I210" s="5" t="s">
         <v>18</v>
@@ -12687,7 +12704,7 @@
         <v>10</v>
       </c>
       <c r="L210" s="6" t="s">
-        <v>680</v>
+        <v>687</v>
       </c>
       <c r="M210" s="6" t="s">
         <v>54</v>
@@ -12701,25 +12718,25 @@
         <v>210</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="D211" s="5" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="E211" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F211" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G211" s="5" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="H211" s="5" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="I211" s="5" t="s">
         <v>18</v>
@@ -12731,7 +12748,7 @@
         <v>10</v>
       </c>
       <c r="L211" s="6" t="s">
-        <v>680</v>
+        <v>687</v>
       </c>
       <c r="M211" s="6" t="s">
         <v>54</v>
@@ -12745,40 +12762,40 @@
         <v>211</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="D212" s="5" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="E212" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F212" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G212" s="5" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="H212" s="5" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="I212" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J212" s="5">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K212" s="5">
         <v>10</v>
       </c>
       <c r="L212" s="6" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="M212" s="6" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="N212" s="6" t="s">
         <v>18</v>
@@ -12789,25 +12806,25 @@
         <v>212</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="D213" s="5" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="E213" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F213" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G213" s="5" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="H213" s="5" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="I213" s="5" t="s">
         <v>18</v>
@@ -12819,7 +12836,7 @@
         <v>10</v>
       </c>
       <c r="L213" s="6" t="s">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="M213" s="6" t="s">
         <v>68</v>
@@ -12833,25 +12850,25 @@
         <v>213</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="D214" s="5" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="E214" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F214" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G214" s="5" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="H214" s="5" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="I214" s="5" t="s">
         <v>18</v>
@@ -12863,7 +12880,7 @@
         <v>10</v>
       </c>
       <c r="L214" s="6" t="s">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="M214" s="6" t="s">
         <v>68</v>
@@ -12877,25 +12894,25 @@
         <v>214</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="D215" s="5" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="E215" s="5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F215" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G215" s="5" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="H215" s="5" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="I215" s="5" t="s">
         <v>18</v>
@@ -12907,7 +12924,7 @@
         <v>10</v>
       </c>
       <c r="L215" s="6" t="s">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="M215" s="6" t="s">
         <v>68</v>
@@ -12921,40 +12938,40 @@
         <v>215</v>
       </c>
       <c r="B216" s="5" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="D216" s="5" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="E216" s="5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F216" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G216" s="5" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="H216" s="5" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="I216" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J216" s="5">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K216" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L216" s="6" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="M216" s="6" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="N216" s="6" t="s">
         <v>18</v>
@@ -12965,25 +12982,25 @@
         <v>216</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="D217" s="5" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="E217" s="5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F217" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G217" s="5" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="H217" s="5" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="I217" s="5" t="s">
         <v>18</v>
@@ -12995,7 +13012,7 @@
         <v>11</v>
       </c>
       <c r="L217" s="6" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="M217" s="6" t="s">
         <v>84</v>
@@ -13009,25 +13026,25 @@
         <v>217</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="D218" s="5" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="E218" s="5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F218" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G218" s="5" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="H218" s="5" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="I218" s="5" t="s">
         <v>18</v>
@@ -13039,7 +13056,7 @@
         <v>11</v>
       </c>
       <c r="L218" s="6" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="M218" s="6" t="s">
         <v>84</v>
@@ -13053,25 +13070,25 @@
         <v>218</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="D219" s="5" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="E219" s="5">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F219" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G219" s="5" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="H219" s="5" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="I219" s="5" t="s">
         <v>18</v>
@@ -13083,7 +13100,7 @@
         <v>11</v>
       </c>
       <c r="L219" s="6" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="M219" s="6" t="s">
         <v>84</v>
@@ -13097,40 +13114,40 @@
         <v>219</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="D220" s="5" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="E220" s="5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F220" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G220" s="5" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="H220" s="5" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="I220" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J220" s="5">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K220" s="5">
         <v>11</v>
       </c>
       <c r="L220" s="6" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="M220" s="6" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="N220" s="6" t="s">
         <v>18</v>
@@ -13141,25 +13158,25 @@
         <v>220</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="D221" s="5" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="E221" s="5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F221" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G221" s="5" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="H221" s="5" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="I221" s="5" t="s">
         <v>18</v>
@@ -13171,7 +13188,7 @@
         <v>11</v>
       </c>
       <c r="L221" s="6" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
       <c r="M221" s="6" t="s">
         <v>21</v>
@@ -13185,25 +13202,25 @@
         <v>221</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="D222" s="5" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="E222" s="5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F222" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G222" s="5" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="H222" s="5" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="I222" s="5" t="s">
         <v>18</v>
@@ -13215,7 +13232,7 @@
         <v>11</v>
       </c>
       <c r="L222" s="6" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
       <c r="M222" s="6" t="s">
         <v>21</v>
@@ -13224,30 +13241,30 @@
         <v>18</v>
       </c>
     </row>
-    <row r="223" ht="14.4" spans="1:14">
+    <row r="223" spans="1:14">
       <c r="A223" s="5">
         <v>222</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="D223" s="5" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="E223" s="5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F223" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G223" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="H223" s="9" t="s">
-        <v>727</v>
+        <v>731</v>
+      </c>
+      <c r="H223" s="5" t="s">
+        <v>732</v>
       </c>
       <c r="I223" s="5" t="s">
         <v>18</v>
@@ -13259,62 +13276,106 @@
         <v>11</v>
       </c>
       <c r="L223" s="6" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
       <c r="M223" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="N223" s="6"/>
-    </row>
-    <row r="224" spans="1:14">
-      <c r="A224">
+      <c r="N223" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="224" ht="14.4" spans="1:14">
+      <c r="A224" s="5">
         <v>223</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>728</v>
-      </c>
-      <c r="C224" t="s">
-        <v>728</v>
-      </c>
-      <c r="D224" t="s">
-        <v>729</v>
-      </c>
-      <c r="E224">
+        <v>669</v>
+      </c>
+      <c r="C224" s="5" t="s">
+        <v>670</v>
+      </c>
+      <c r="D224" s="5" t="s">
+        <v>733</v>
+      </c>
+      <c r="E224" s="5">
+        <v>20</v>
+      </c>
+      <c r="F224" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G224" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="H224" s="9" t="s">
+        <v>734</v>
+      </c>
+      <c r="I224" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J224" s="5">
+        <v>51</v>
+      </c>
+      <c r="K224" s="5">
+        <v>11</v>
+      </c>
+      <c r="L224" s="6" t="s">
+        <v>726</v>
+      </c>
+      <c r="M224" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F224" t="s">
+      <c r="N224" s="6"/>
+    </row>
+    <row r="225" spans="1:14">
+      <c r="A225" s="5">
+        <v>224</v>
+      </c>
+      <c r="B225" s="5" t="s">
+        <v>735</v>
+      </c>
+      <c r="C225" t="s">
+        <v>735</v>
+      </c>
+      <c r="D225" t="s">
+        <v>736</v>
+      </c>
+      <c r="E225">
+        <v>21</v>
+      </c>
+      <c r="F225" t="s">
         <v>16</v>
       </c>
-      <c r="G224" t="s">
-        <v>728</v>
-      </c>
-      <c r="I224" s="5" t="s">
+      <c r="G225" t="s">
+        <v>735</v>
+      </c>
+      <c r="I225" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="J224">
+      <c r="J225">
         <v>52</v>
       </c>
-      <c r="K224">
+      <c r="K225">
         <v>11</v>
       </c>
-      <c r="L224" s="6" t="s">
-        <v>730</v>
-      </c>
-      <c r="M224" s="6" t="s">
+      <c r="L225" s="6" t="s">
+        <v>737</v>
+      </c>
+      <c r="M225" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="N224" s="6" t="s">
+      <c r="N225" s="6" t="s">
         <v>22</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="F2:F224">
+    <dataValidation type="list" sqref="F173 F2:F172 F174:F225">
       <formula1>"Video,Resource"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="H223" r:id="rId2" display="https://youtu.be/LZWTeYXzAO8"/>
+    <hyperlink ref="H224" r:id="rId2" display="https://youtu.be/LZWTeYXzAO8"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -13338,24 +13399,24 @@
   <sheetData>
     <row r="1" ht="27.6" spans="1:4">
       <c r="A1" s="3" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="C2" s="2">
         <v>15</v>
@@ -13366,7 +13427,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="B3" s="2">
         <v>223</v>
@@ -13380,7 +13441,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="B4" s="2">
         <v>204</v>
@@ -13394,7 +13455,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="B5" s="2">
         <v>19</v>
@@ -13408,10 +13469,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="C6" s="2">
         <v>28</v>
@@ -13422,10 +13483,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="C7" s="2">
         <v>20</v>
@@ -13436,15 +13497,15 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="B9" s="2">
         <v>51</v>
@@ -13452,18 +13513,18 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>748</v>
+        <v>755</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -13523,50 +13584,50 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="3" t="s">
-        <v>749</v>
+        <v>756</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>750</v>
+        <v>757</v>
       </c>
     </row>
     <row r="2" ht="27.6" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>752</v>
+        <v>759</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>756</v>
+        <v>763</v>
       </c>
     </row>
     <row r="6" ht="27.6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -13574,15 +13635,15 @@
         <v>9</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>759</v>
+        <v>766</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>760</v>
+        <v>767</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>761</v>
+        <v>768</v>
       </c>
     </row>
   </sheetData>
@@ -13607,7 +13668,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
@@ -13619,35 +13680,35 @@
         <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>763</v>
+        <v>770</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
     </row>
     <row r="2" ht="27.6" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>765</v>
+        <v>772</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>726</v>
+        <v>733</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>73</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>661</v>
+        <v>668</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>766</v>
+        <v>773</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>23</v>
@@ -13662,12 +13723,12 @@
         <v>26</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>72</v>
@@ -13682,12 +13743,12 @@
         <v>74</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>88</v>
@@ -13702,12 +13763,12 @@
         <v>90</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>770</v>
+        <v>777</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>91</v>
@@ -13722,47 +13783,47 @@
         <v>92</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>771</v>
+        <v>778</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>75</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>770</v>
+        <v>777</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>75</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>771</v>
+        <v>778</v>
       </c>
     </row>
     <row r="9" spans="1:6">

--- a/data/OVTech Master Curriculum.xlsx
+++ b/data/OVTech Master Curriculum.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8400"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Master Curriculum" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2334" uniqueCount="779">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2334" uniqueCount="780">
   <si>
     <t>Global Order</t>
   </si>
@@ -968,22 +968,25 @@
     <t>Mini-Project4 Pt.2</t>
   </si>
   <si>
+    <t>https://www.youtube.com/watch?v=GbuEOaRAjkE</t>
+  </si>
+  <si>
+    <t>EX075</t>
+  </si>
+  <si>
+    <t>Mini-Project4 Pt.3</t>
+  </si>
+  <si>
+    <t>https://youtu.be/DMNUewivrjA</t>
+  </si>
+  <si>
+    <t>EX076</t>
+  </si>
+  <si>
+    <t>Mini-Project4 Pt.4</t>
+  </si>
+  <si>
     <t>https://youtu.be/vOyvkf0Eg2k</t>
-  </si>
-  <si>
-    <t>EX075</t>
-  </si>
-  <si>
-    <t>Mini-Project4 Pt.3</t>
-  </si>
-  <si>
-    <t>https://youtu.be/DMNUewivrjA</t>
-  </si>
-  <si>
-    <t>EX076</t>
-  </si>
-  <si>
-    <t>Mini-Project4 Pt.4</t>
   </si>
   <si>
     <t>Excel Tables</t>
@@ -7393,7 +7396,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="90" spans="1:14">
+    <row r="90" ht="27.6" spans="1:14">
       <c r="A90" s="5">
         <v>89</v>
       </c>
@@ -7504,7 +7507,7 @@
         <v>317</v>
       </c>
       <c r="H92" s="5" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="I92" s="5" t="s">
         <v>18</v>
@@ -7533,10 +7536,10 @@
         <v>75</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E93" s="5">
         <v>76</v>
@@ -7545,7 +7548,7 @@
         <v>16</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H93" s="5" t="s">
         <v>18</v>
@@ -7560,7 +7563,7 @@
         <v>5</v>
       </c>
       <c r="L93" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M93" s="6" t="s">
         <v>40</v>
@@ -7577,10 +7580,10 @@
         <v>75</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E94" s="5">
         <v>77</v>
@@ -7589,10 +7592,10 @@
         <v>24</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H94" s="5" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I94" s="5" t="s">
         <v>18</v>
@@ -7604,7 +7607,7 @@
         <v>5</v>
       </c>
       <c r="L94" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M94" s="6" t="s">
         <v>40</v>
@@ -7621,10 +7624,10 @@
         <v>75</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E95" s="5">
         <v>78</v>
@@ -7633,10 +7636,10 @@
         <v>24</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H95" s="5" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I95" s="5" t="s">
         <v>18</v>
@@ -7648,7 +7651,7 @@
         <v>5</v>
       </c>
       <c r="L95" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M95" s="6" t="s">
         <v>40</v>
@@ -7665,10 +7668,10 @@
         <v>75</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E96" s="5">
         <v>79</v>
@@ -7677,10 +7680,10 @@
         <v>24</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H96" s="5" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I96" s="5" t="s">
         <v>18</v>
@@ -7692,7 +7695,7 @@
         <v>5</v>
       </c>
       <c r="L96" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M96" s="6" t="s">
         <v>40</v>
@@ -7709,10 +7712,10 @@
         <v>75</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E97" s="5">
         <v>80</v>
@@ -7721,10 +7724,10 @@
         <v>24</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H97" s="5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="I97" s="5" t="s">
         <v>18</v>
@@ -7736,7 +7739,7 @@
         <v>5</v>
       </c>
       <c r="L97" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M97" s="6" t="s">
         <v>40</v>
@@ -7753,10 +7756,10 @@
         <v>75</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E98" s="5">
         <v>81</v>
@@ -7765,10 +7768,10 @@
         <v>24</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H98" s="5" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I98" s="5" t="s">
         <v>18</v>
@@ -7780,7 +7783,7 @@
         <v>5</v>
       </c>
       <c r="L98" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M98" s="6" t="s">
         <v>54</v>
@@ -7797,10 +7800,10 @@
         <v>75</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E99" s="5">
         <v>82</v>
@@ -7809,10 +7812,10 @@
         <v>24</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H99" s="5" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="I99" s="5" t="s">
         <v>18</v>
@@ -7824,7 +7827,7 @@
         <v>5</v>
       </c>
       <c r="L99" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M99" s="6" t="s">
         <v>54</v>
@@ -7841,10 +7844,10 @@
         <v>75</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E100" s="5">
         <v>83</v>
@@ -7853,10 +7856,10 @@
         <v>24</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H100" s="5" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="I100" s="5" t="s">
         <v>18</v>
@@ -7868,7 +7871,7 @@
         <v>5</v>
       </c>
       <c r="L100" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M100" s="6" t="s">
         <v>54</v>
@@ -7885,10 +7888,10 @@
         <v>75</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E101" s="5">
         <v>84</v>
@@ -7897,10 +7900,10 @@
         <v>24</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H101" s="5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I101" s="5" t="s">
         <v>18</v>
@@ -7912,7 +7915,7 @@
         <v>5</v>
       </c>
       <c r="L101" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M101" s="6" t="s">
         <v>54</v>
@@ -7929,10 +7932,10 @@
         <v>75</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E102" s="5">
         <v>85</v>
@@ -7941,10 +7944,10 @@
         <v>24</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H102" s="5" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="I102" s="5" t="s">
         <v>18</v>
@@ -7956,7 +7959,7 @@
         <v>5</v>
       </c>
       <c r="L102" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M102" s="6" t="s">
         <v>68</v>
@@ -7973,10 +7976,10 @@
         <v>75</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E103" s="5">
         <v>86</v>
@@ -7985,10 +7988,10 @@
         <v>24</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H103" s="5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="I103" s="5" t="s">
         <v>18</v>
@@ -8000,7 +8003,7 @@
         <v>5</v>
       </c>
       <c r="L103" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M103" s="6" t="s">
         <v>68</v>
@@ -8014,13 +8017,13 @@
         <v>103</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E104" s="5">
         <v>1</v>
@@ -8029,7 +8032,7 @@
         <v>16</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H104" s="5" t="s">
         <v>18</v>
@@ -8044,7 +8047,7 @@
         <v>6</v>
       </c>
       <c r="L104" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M104" s="6" t="s">
         <v>84</v>
@@ -8058,13 +8061,13 @@
         <v>104</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E105" s="5">
         <v>2</v>
@@ -8073,7 +8076,7 @@
         <v>16</v>
       </c>
       <c r="G105" s="5" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H105" s="5" t="s">
         <v>18</v>
@@ -8088,7 +8091,7 @@
         <v>6</v>
       </c>
       <c r="L105" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M105" s="6" t="s">
         <v>84</v>
@@ -8102,13 +8105,13 @@
         <v>105</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E106" s="5">
         <v>3</v>
@@ -8117,10 +8120,10 @@
         <v>24</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H106" s="5" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="I106" s="5" t="s">
         <v>18</v>
@@ -8132,7 +8135,7 @@
         <v>6</v>
       </c>
       <c r="L106" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M106" s="6" t="s">
         <v>84</v>
@@ -8146,13 +8149,13 @@
         <v>106</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E107" s="5">
         <v>4</v>
@@ -8161,10 +8164,10 @@
         <v>24</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H107" s="5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I107" s="5" t="s">
         <v>18</v>
@@ -8176,7 +8179,7 @@
         <v>6</v>
       </c>
       <c r="L107" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M107" s="6" t="s">
         <v>84</v>
@@ -8190,13 +8193,13 @@
         <v>107</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E108" s="5">
         <v>5</v>
@@ -8205,10 +8208,10 @@
         <v>24</v>
       </c>
       <c r="G108" s="5" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H108" s="5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="I108" s="5" t="s">
         <v>18</v>
@@ -8220,7 +8223,7 @@
         <v>6</v>
       </c>
       <c r="L108" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M108" s="6" t="s">
         <v>84</v>
@@ -8234,13 +8237,13 @@
         <v>108</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E109" s="5">
         <v>6</v>
@@ -8249,10 +8252,10 @@
         <v>24</v>
       </c>
       <c r="G109" s="5" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H109" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="I109" s="5" t="s">
         <v>18</v>
@@ -8264,7 +8267,7 @@
         <v>6</v>
       </c>
       <c r="L109" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M109" s="6" t="s">
         <v>84</v>
@@ -8278,13 +8281,13 @@
         <v>109</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E110" s="5">
         <v>7</v>
@@ -8293,10 +8296,10 @@
         <v>24</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H110" s="5" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="I110" s="5" t="s">
         <v>18</v>
@@ -8308,7 +8311,7 @@
         <v>6</v>
       </c>
       <c r="L110" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M110" s="6" t="s">
         <v>21</v>
@@ -8322,13 +8325,13 @@
         <v>110</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E111" s="5">
         <v>8</v>
@@ -8337,10 +8340,10 @@
         <v>24</v>
       </c>
       <c r="G111" s="5" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H111" s="5" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="I111" s="5" t="s">
         <v>18</v>
@@ -8352,7 +8355,7 @@
         <v>6</v>
       </c>
       <c r="L111" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M111" s="6" t="s">
         <v>21</v>
@@ -8366,13 +8369,13 @@
         <v>111</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E112" s="5">
         <v>9</v>
@@ -8381,10 +8384,10 @@
         <v>24</v>
       </c>
       <c r="G112" s="5" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H112" s="5" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="I112" s="5" t="s">
         <v>18</v>
@@ -8396,7 +8399,7 @@
         <v>6</v>
       </c>
       <c r="L112" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M112" s="6" t="s">
         <v>21</v>
@@ -8410,13 +8413,13 @@
         <v>112</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E113" s="5">
         <v>10</v>
@@ -8425,10 +8428,10 @@
         <v>24</v>
       </c>
       <c r="G113" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H113" s="5" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="I113" s="5" t="s">
         <v>18</v>
@@ -8440,7 +8443,7 @@
         <v>6</v>
       </c>
       <c r="L113" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M113" s="6" t="s">
         <v>21</v>
@@ -8454,13 +8457,13 @@
         <v>113</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E114" s="5">
         <v>11</v>
@@ -8469,10 +8472,10 @@
         <v>24</v>
       </c>
       <c r="G114" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H114" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="I114" s="5" t="s">
         <v>18</v>
@@ -8484,7 +8487,7 @@
         <v>6</v>
       </c>
       <c r="L114" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M114" s="6" t="s">
         <v>40</v>
@@ -8498,13 +8501,13 @@
         <v>114</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E115" s="5">
         <v>12</v>
@@ -8513,10 +8516,10 @@
         <v>24</v>
       </c>
       <c r="G115" s="5" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H115" s="5" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I115" s="5" t="s">
         <v>18</v>
@@ -8528,7 +8531,7 @@
         <v>6</v>
       </c>
       <c r="L115" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M115" s="6" t="s">
         <v>40</v>
@@ -8542,13 +8545,13 @@
         <v>115</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E116" s="5">
         <v>13</v>
@@ -8557,10 +8560,10 @@
         <v>24</v>
       </c>
       <c r="G116" s="5" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H116" s="5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="I116" s="5" t="s">
         <v>18</v>
@@ -8572,7 +8575,7 @@
         <v>6</v>
       </c>
       <c r="L116" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M116" s="6" t="s">
         <v>40</v>
@@ -8586,13 +8589,13 @@
         <v>116</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E117" s="5">
         <v>14</v>
@@ -8601,10 +8604,10 @@
         <v>24</v>
       </c>
       <c r="G117" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H117" s="5" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="I117" s="5" t="s">
         <v>18</v>
@@ -8616,7 +8619,7 @@
         <v>6</v>
       </c>
       <c r="L117" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M117" s="6" t="s">
         <v>40</v>
@@ -8633,10 +8636,10 @@
         <v>75</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E118" s="5">
         <v>88</v>
@@ -8645,7 +8648,7 @@
         <v>16</v>
       </c>
       <c r="G118" s="5" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H118" s="5" t="s">
         <v>18</v>
@@ -8660,7 +8663,7 @@
         <v>6</v>
       </c>
       <c r="L118" s="6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M118" s="6" t="s">
         <v>54</v>
@@ -8677,10 +8680,10 @@
         <v>75</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E119" s="5">
         <v>89</v>
@@ -8689,7 +8692,7 @@
         <v>16</v>
       </c>
       <c r="G119" s="5" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H119" s="5" t="s">
         <v>18</v>
@@ -8704,7 +8707,7 @@
         <v>6</v>
       </c>
       <c r="L119" s="6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M119" s="6" t="s">
         <v>54</v>
@@ -8721,10 +8724,10 @@
         <v>75</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E120" s="5">
         <v>90</v>
@@ -8733,10 +8736,10 @@
         <v>24</v>
       </c>
       <c r="G120" s="5" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H120" s="5" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="I120" s="5" t="s">
         <v>18</v>
@@ -8748,7 +8751,7 @@
         <v>6</v>
       </c>
       <c r="L120" s="6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M120" s="6" t="s">
         <v>54</v>
@@ -8765,10 +8768,10 @@
         <v>75</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E121" s="5">
         <v>91</v>
@@ -8777,10 +8780,10 @@
         <v>24</v>
       </c>
       <c r="G121" s="5" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H121" s="5" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="I121" s="5" t="s">
         <v>18</v>
@@ -8792,7 +8795,7 @@
         <v>6</v>
       </c>
       <c r="L121" s="6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M121" s="6" t="s">
         <v>54</v>
@@ -8809,10 +8812,10 @@
         <v>75</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E122" s="5">
         <v>92</v>
@@ -8821,10 +8824,10 @@
         <v>24</v>
       </c>
       <c r="G122" s="5" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H122" s="5" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="I122" s="5" t="s">
         <v>18</v>
@@ -8836,7 +8839,7 @@
         <v>6</v>
       </c>
       <c r="L122" s="6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M122" s="6" t="s">
         <v>54</v>
@@ -8853,10 +8856,10 @@
         <v>75</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E123" s="5">
         <v>93</v>
@@ -8865,10 +8868,10 @@
         <v>24</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H123" s="5" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="I123" s="5" t="s">
         <v>18</v>
@@ -8880,7 +8883,7 @@
         <v>6</v>
       </c>
       <c r="L123" s="6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M123" s="6" t="s">
         <v>54</v>
@@ -8897,10 +8900,10 @@
         <v>75</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E124" s="5">
         <v>94</v>
@@ -8909,10 +8912,10 @@
         <v>24</v>
       </c>
       <c r="G124" s="5" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H124" s="5" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I124" s="5" t="s">
         <v>18</v>
@@ -8924,7 +8927,7 @@
         <v>6</v>
       </c>
       <c r="L124" s="6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M124" s="6" t="s">
         <v>68</v>
@@ -8941,10 +8944,10 @@
         <v>75</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E125" s="5">
         <v>95</v>
@@ -8953,10 +8956,10 @@
         <v>24</v>
       </c>
       <c r="G125" s="5" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H125" s="5" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="I125" s="5" t="s">
         <v>18</v>
@@ -8968,7 +8971,7 @@
         <v>6</v>
       </c>
       <c r="L125" s="6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M125" s="6" t="s">
         <v>68</v>
@@ -8985,10 +8988,10 @@
         <v>75</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E126" s="5">
         <v>96</v>
@@ -8997,10 +9000,10 @@
         <v>24</v>
       </c>
       <c r="G126" s="5" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H126" s="5" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="I126" s="5" t="s">
         <v>18</v>
@@ -9012,7 +9015,7 @@
         <v>6</v>
       </c>
       <c r="L126" s="6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M126" s="6" t="s">
         <v>68</v>
@@ -9029,10 +9032,10 @@
         <v>75</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E127" s="5">
         <v>97</v>
@@ -9041,10 +9044,10 @@
         <v>24</v>
       </c>
       <c r="G127" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H127" s="5" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="I127" s="5" t="s">
         <v>18</v>
@@ -9056,7 +9059,7 @@
         <v>6</v>
       </c>
       <c r="L127" s="6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M127" s="6" t="s">
         <v>68</v>
@@ -9070,13 +9073,13 @@
         <v>127</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E128" s="5">
         <v>1</v>
@@ -9085,10 +9088,10 @@
         <v>24</v>
       </c>
       <c r="G128" s="5" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H128" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="I128" s="5" t="s">
         <v>18</v>
@@ -9100,7 +9103,7 @@
         <v>7</v>
       </c>
       <c r="L128" s="6" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M128" s="6" t="s">
         <v>84</v>
@@ -9114,13 +9117,13 @@
         <v>128</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E129" s="5">
         <v>2</v>
@@ -9129,10 +9132,10 @@
         <v>24</v>
       </c>
       <c r="G129" s="5" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H129" s="5" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="I129" s="5" t="s">
         <v>18</v>
@@ -9144,7 +9147,7 @@
         <v>7</v>
       </c>
       <c r="L129" s="6" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M129" s="6" t="s">
         <v>84</v>
@@ -9158,13 +9161,13 @@
         <v>129</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E130" s="5">
         <v>3</v>
@@ -9173,10 +9176,10 @@
         <v>24</v>
       </c>
       <c r="G130" s="5" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H130" s="5" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="I130" s="5" t="s">
         <v>18</v>
@@ -9188,7 +9191,7 @@
         <v>7</v>
       </c>
       <c r="L130" s="6" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M130" s="6" t="s">
         <v>84</v>
@@ -9202,13 +9205,13 @@
         <v>130</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E131" s="5">
         <v>4</v>
@@ -9217,10 +9220,10 @@
         <v>24</v>
       </c>
       <c r="G131" s="5" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H131" s="5" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="I131" s="5" t="s">
         <v>18</v>
@@ -9232,7 +9235,7 @@
         <v>7</v>
       </c>
       <c r="L131" s="6" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M131" s="6" t="s">
         <v>84</v>
@@ -9246,13 +9249,13 @@
         <v>131</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E132" s="5">
         <v>5</v>
@@ -9261,10 +9264,10 @@
         <v>24</v>
       </c>
       <c r="G132" s="5" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H132" s="5" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="I132" s="5" t="s">
         <v>18</v>
@@ -9276,7 +9279,7 @@
         <v>7</v>
       </c>
       <c r="L132" s="6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M132" s="6" t="s">
         <v>21</v>
@@ -9290,13 +9293,13 @@
         <v>132</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E133" s="5">
         <v>6</v>
@@ -9305,10 +9308,10 @@
         <v>24</v>
       </c>
       <c r="G133" s="5" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H133" s="5" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="I133" s="5" t="s">
         <v>18</v>
@@ -9320,7 +9323,7 @@
         <v>7</v>
       </c>
       <c r="L133" s="6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M133" s="6" t="s">
         <v>21</v>
@@ -9334,13 +9337,13 @@
         <v>133</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E134" s="5">
         <v>7</v>
@@ -9349,10 +9352,10 @@
         <v>24</v>
       </c>
       <c r="G134" s="5" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H134" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="I134" s="5" t="s">
         <v>18</v>
@@ -9364,7 +9367,7 @@
         <v>7</v>
       </c>
       <c r="L134" s="6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M134" s="6" t="s">
         <v>21</v>
@@ -9378,13 +9381,13 @@
         <v>134</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E135" s="5">
         <v>8</v>
@@ -9393,10 +9396,10 @@
         <v>24</v>
       </c>
       <c r="G135" s="5" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H135" s="5" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="I135" s="5" t="s">
         <v>18</v>
@@ -9408,7 +9411,7 @@
         <v>7</v>
       </c>
       <c r="L135" s="6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M135" s="6" t="s">
         <v>21</v>
@@ -9422,13 +9425,13 @@
         <v>135</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E136" s="5">
         <v>9</v>
@@ -9437,10 +9440,10 @@
         <v>24</v>
       </c>
       <c r="G136" s="5" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H136" s="5" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="I136" s="5" t="s">
         <v>18</v>
@@ -9452,7 +9455,7 @@
         <v>7</v>
       </c>
       <c r="L136" s="6" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M136" s="6" t="s">
         <v>40</v>
@@ -9466,13 +9469,13 @@
         <v>136</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E137" s="5">
         <v>10</v>
@@ -9481,10 +9484,10 @@
         <v>24</v>
       </c>
       <c r="G137" s="5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H137" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="I137" s="5" t="s">
         <v>18</v>
@@ -9496,7 +9499,7 @@
         <v>7</v>
       </c>
       <c r="L137" s="6" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M137" s="6" t="s">
         <v>40</v>
@@ -9510,13 +9513,13 @@
         <v>137</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E138" s="5">
         <v>11</v>
@@ -9525,10 +9528,10 @@
         <v>24</v>
       </c>
       <c r="G138" s="5" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H138" s="5" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="I138" s="5" t="s">
         <v>18</v>
@@ -9540,7 +9543,7 @@
         <v>7</v>
       </c>
       <c r="L138" s="6" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M138" s="6" t="s">
         <v>40</v>
@@ -9554,13 +9557,13 @@
         <v>138</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E139" s="5">
         <v>12</v>
@@ -9569,10 +9572,10 @@
         <v>24</v>
       </c>
       <c r="G139" s="5" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H139" s="5" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="I139" s="5" t="s">
         <v>18</v>
@@ -9584,7 +9587,7 @@
         <v>7</v>
       </c>
       <c r="L139" s="6" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M139" s="6" t="s">
         <v>40</v>
@@ -9598,13 +9601,13 @@
         <v>139</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E140" s="5">
         <v>13</v>
@@ -9613,10 +9616,10 @@
         <v>24</v>
       </c>
       <c r="G140" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H140" s="5" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="I140" s="5" t="s">
         <v>18</v>
@@ -9628,7 +9631,7 @@
         <v>7</v>
       </c>
       <c r="L140" s="6" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M140" s="6" t="s">
         <v>54</v>
@@ -9642,13 +9645,13 @@
         <v>140</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E141" s="5">
         <v>14</v>
@@ -9657,10 +9660,10 @@
         <v>24</v>
       </c>
       <c r="G141" s="5" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H141" s="5" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I141" s="5" t="s">
         <v>18</v>
@@ -9672,7 +9675,7 @@
         <v>7</v>
       </c>
       <c r="L141" s="6" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M141" s="6" t="s">
         <v>54</v>
@@ -9686,13 +9689,13 @@
         <v>141</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E142" s="5">
         <v>15</v>
@@ -9701,10 +9704,10 @@
         <v>24</v>
       </c>
       <c r="G142" s="5" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H142" s="5" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="I142" s="5" t="s">
         <v>18</v>
@@ -9716,7 +9719,7 @@
         <v>7</v>
       </c>
       <c r="L142" s="6" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M142" s="6" t="s">
         <v>54</v>
@@ -9730,13 +9733,13 @@
         <v>142</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E143" s="5">
         <v>16</v>
@@ -9745,10 +9748,10 @@
         <v>24</v>
       </c>
       <c r="G143" s="5" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H143" s="5" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="I143" s="5" t="s">
         <v>18</v>
@@ -9760,7 +9763,7 @@
         <v>7</v>
       </c>
       <c r="L143" s="6" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M143" s="6" t="s">
         <v>54</v>
@@ -9774,13 +9777,13 @@
         <v>143</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E144" s="5">
         <v>17</v>
@@ -9789,10 +9792,10 @@
         <v>24</v>
       </c>
       <c r="G144" s="5" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H144" s="5" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="I144" s="5" t="s">
         <v>18</v>
@@ -9804,7 +9807,7 @@
         <v>7</v>
       </c>
       <c r="L144" s="6" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M144" s="6" t="s">
         <v>68</v>
@@ -9818,13 +9821,13 @@
         <v>144</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E145" s="5">
         <v>18</v>
@@ -9833,10 +9836,10 @@
         <v>24</v>
       </c>
       <c r="G145" s="5" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H145" s="5" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="I145" s="5" t="s">
         <v>18</v>
@@ -9848,7 +9851,7 @@
         <v>7</v>
       </c>
       <c r="L145" s="6" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M145" s="6" t="s">
         <v>68</v>
@@ -9862,13 +9865,13 @@
         <v>145</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E146" s="5">
         <v>19</v>
@@ -9877,10 +9880,10 @@
         <v>24</v>
       </c>
       <c r="G146" s="5" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H146" s="5" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="I146" s="5" t="s">
         <v>18</v>
@@ -9892,7 +9895,7 @@
         <v>7</v>
       </c>
       <c r="L146" s="6" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M146" s="6" t="s">
         <v>68</v>
@@ -9906,13 +9909,13 @@
         <v>146</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E147" s="5">
         <v>20</v>
@@ -9921,10 +9924,10 @@
         <v>24</v>
       </c>
       <c r="G147" s="5" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H147" s="5" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="I147" s="5" t="s">
         <v>18</v>
@@ -9936,7 +9939,7 @@
         <v>7</v>
       </c>
       <c r="L147" s="6" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M147" s="6" t="s">
         <v>68</v>
@@ -9950,13 +9953,13 @@
         <v>147</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E148" s="5">
         <v>21</v>
@@ -9965,10 +9968,10 @@
         <v>24</v>
       </c>
       <c r="G148" s="5" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H148" s="5" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="I148" s="5" t="s">
         <v>18</v>
@@ -9980,7 +9983,7 @@
         <v>8</v>
       </c>
       <c r="L148" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M148" s="6" t="s">
         <v>84</v>
@@ -9994,13 +9997,13 @@
         <v>148</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E149" s="5">
         <v>22</v>
@@ -10009,10 +10012,10 @@
         <v>24</v>
       </c>
       <c r="G149" s="5" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H149" s="5" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="I149" s="5" t="s">
         <v>18</v>
@@ -10024,7 +10027,7 @@
         <v>8</v>
       </c>
       <c r="L149" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M149" s="6" t="s">
         <v>84</v>
@@ -10038,13 +10041,13 @@
         <v>149</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E150" s="5">
         <v>23</v>
@@ -10053,10 +10056,10 @@
         <v>24</v>
       </c>
       <c r="G150" s="5" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H150" s="5" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="I150" s="5" t="s">
         <v>18</v>
@@ -10068,7 +10071,7 @@
         <v>8</v>
       </c>
       <c r="L150" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M150" s="6" t="s">
         <v>84</v>
@@ -10082,13 +10085,13 @@
         <v>150</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E151" s="5">
         <v>24</v>
@@ -10097,10 +10100,10 @@
         <v>24</v>
       </c>
       <c r="G151" s="5" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H151" s="5" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="I151" s="5" t="s">
         <v>18</v>
@@ -10112,7 +10115,7 @@
         <v>8</v>
       </c>
       <c r="L151" s="6" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M151" s="6" t="s">
         <v>84</v>
@@ -10126,13 +10129,13 @@
         <v>151</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E152" s="5">
         <v>25</v>
@@ -10141,10 +10144,10 @@
         <v>24</v>
       </c>
       <c r="G152" s="5" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H152" s="5" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="I152" s="5" t="s">
         <v>18</v>
@@ -10156,7 +10159,7 @@
         <v>8</v>
       </c>
       <c r="L152" s="6" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M152" s="6" t="s">
         <v>21</v>
@@ -10170,13 +10173,13 @@
         <v>152</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E153" s="5">
         <v>26</v>
@@ -10185,10 +10188,10 @@
         <v>24</v>
       </c>
       <c r="G153" s="5" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H153" s="5" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="I153" s="5" t="s">
         <v>18</v>
@@ -10200,7 +10203,7 @@
         <v>8</v>
       </c>
       <c r="L153" s="6" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M153" s="6" t="s">
         <v>21</v>
@@ -10214,13 +10217,13 @@
         <v>153</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E154" s="5">
         <v>27</v>
@@ -10229,10 +10232,10 @@
         <v>24</v>
       </c>
       <c r="G154" s="5" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H154" s="5" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="I154" s="5" t="s">
         <v>18</v>
@@ -10244,7 +10247,7 @@
         <v>8</v>
       </c>
       <c r="L154" s="6" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M154" s="6" t="s">
         <v>21</v>
@@ -10258,13 +10261,13 @@
         <v>154</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="E155" s="5">
         <v>28</v>
@@ -10273,10 +10276,10 @@
         <v>24</v>
       </c>
       <c r="G155" s="5" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H155" s="5" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="I155" s="5" t="s">
         <v>18</v>
@@ -10288,7 +10291,7 @@
         <v>8</v>
       </c>
       <c r="L155" s="6" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M155" s="6" t="s">
         <v>21</v>
@@ -10302,13 +10305,13 @@
         <v>155</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E156" s="5">
         <v>29</v>
@@ -10317,10 +10320,10 @@
         <v>24</v>
       </c>
       <c r="G156" s="5" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H156" s="5" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="I156" s="5" t="s">
         <v>18</v>
@@ -10332,7 +10335,7 @@
         <v>8</v>
       </c>
       <c r="L156" s="6" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M156" s="6" t="s">
         <v>21</v>
@@ -10346,13 +10349,13 @@
         <v>156</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E157" s="5">
         <v>30</v>
@@ -10361,7 +10364,7 @@
         <v>16</v>
       </c>
       <c r="G157" s="5" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H157" s="5" t="s">
         <v>18</v>
@@ -10376,7 +10379,7 @@
         <v>8</v>
       </c>
       <c r="L157" s="6" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M157" s="6" t="s">
         <v>40</v>
@@ -10390,13 +10393,13 @@
         <v>157</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E158" s="5">
         <v>31</v>
@@ -10405,7 +10408,7 @@
         <v>16</v>
       </c>
       <c r="G158" s="5" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H158" s="5" t="s">
         <v>18</v>
@@ -10420,7 +10423,7 @@
         <v>8</v>
       </c>
       <c r="L158" s="6" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M158" s="6" t="s">
         <v>40</v>
@@ -10434,13 +10437,13 @@
         <v>158</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E159" s="5">
         <v>32</v>
@@ -10449,7 +10452,7 @@
         <v>16</v>
       </c>
       <c r="G159" s="5" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H159" s="5" t="s">
         <v>18</v>
@@ -10464,7 +10467,7 @@
         <v>8</v>
       </c>
       <c r="L159" s="6" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M159" s="6" t="s">
         <v>40</v>
@@ -10478,13 +10481,13 @@
         <v>159</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E160" s="5">
         <v>33</v>
@@ -10493,10 +10496,10 @@
         <v>24</v>
       </c>
       <c r="G160" s="5" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H160" s="5" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="I160" s="5" t="s">
         <v>18</v>
@@ -10508,7 +10511,7 @@
         <v>8</v>
       </c>
       <c r="L160" s="6" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M160" s="6" t="s">
         <v>40</v>
@@ -10522,13 +10525,13 @@
         <v>160</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E161" s="5">
         <v>34</v>
@@ -10537,10 +10540,10 @@
         <v>24</v>
       </c>
       <c r="G161" s="5" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H161" s="5" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="I161" s="5" t="s">
         <v>18</v>
@@ -10552,7 +10555,7 @@
         <v>8</v>
       </c>
       <c r="L161" s="6" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M161" s="6" t="s">
         <v>40</v>
@@ -10566,13 +10569,13 @@
         <v>161</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E162" s="5">
         <v>35</v>
@@ -10581,10 +10584,10 @@
         <v>24</v>
       </c>
       <c r="G162" s="5" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H162" s="5" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="I162" s="5" t="s">
         <v>18</v>
@@ -10596,7 +10599,7 @@
         <v>8</v>
       </c>
       <c r="L162" s="6" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M162" s="6" t="s">
         <v>40</v>
@@ -10610,13 +10613,13 @@
         <v>162</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E163" s="5">
         <v>36</v>
@@ -10625,10 +10628,10 @@
         <v>24</v>
       </c>
       <c r="G163" s="5" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H163" s="5" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="I163" s="5" t="s">
         <v>18</v>
@@ -10640,7 +10643,7 @@
         <v>8</v>
       </c>
       <c r="L163" s="6" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M163" s="6" t="s">
         <v>40</v>
@@ -10654,13 +10657,13 @@
         <v>163</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E164" s="5">
         <v>37</v>
@@ -10669,10 +10672,10 @@
         <v>24</v>
       </c>
       <c r="G164" s="5" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H164" s="5" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="I164" s="5" t="s">
         <v>18</v>
@@ -10684,7 +10687,7 @@
         <v>8</v>
       </c>
       <c r="L164" s="6" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M164" s="6" t="s">
         <v>54</v>
@@ -10698,13 +10701,13 @@
         <v>164</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E165" s="5">
         <v>38</v>
@@ -10713,10 +10716,10 @@
         <v>24</v>
       </c>
       <c r="G165" s="5" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H165" s="5" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="I165" s="5" t="s">
         <v>18</v>
@@ -10728,7 +10731,7 @@
         <v>8</v>
       </c>
       <c r="L165" s="6" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M165" s="6" t="s">
         <v>54</v>
@@ -10742,13 +10745,13 @@
         <v>165</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E166" s="5">
         <v>39</v>
@@ -10757,10 +10760,10 @@
         <v>24</v>
       </c>
       <c r="G166" s="5" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H166" s="5" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="I166" s="5" t="s">
         <v>18</v>
@@ -10772,7 +10775,7 @@
         <v>8</v>
       </c>
       <c r="L166" s="6" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M166" s="6" t="s">
         <v>54</v>
@@ -10786,13 +10789,13 @@
         <v>166</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E167" s="5">
         <v>40</v>
@@ -10801,10 +10804,10 @@
         <v>24</v>
       </c>
       <c r="G167" s="5" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H167" s="5" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="I167" s="5" t="s">
         <v>18</v>
@@ -10816,7 +10819,7 @@
         <v>8</v>
       </c>
       <c r="L167" s="6" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M167" s="6" t="s">
         <v>54</v>
@@ -10830,13 +10833,13 @@
         <v>167</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E168" s="5">
         <v>41</v>
@@ -10845,10 +10848,10 @@
         <v>24</v>
       </c>
       <c r="G168" s="5" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H168" s="5" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="I168" s="5" t="s">
         <v>18</v>
@@ -10860,7 +10863,7 @@
         <v>8</v>
       </c>
       <c r="L168" s="6" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M168" s="6" t="s">
         <v>54</v>
@@ -10874,13 +10877,13 @@
         <v>168</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E169" s="5">
         <v>42</v>
@@ -10889,10 +10892,10 @@
         <v>24</v>
       </c>
       <c r="G169" s="5" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H169" s="5" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="I169" s="5" t="s">
         <v>18</v>
@@ -10904,7 +10907,7 @@
         <v>8</v>
       </c>
       <c r="L169" s="6" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M169" s="6" t="s">
         <v>68</v>
@@ -10918,13 +10921,13 @@
         <v>169</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D170" s="5" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E170" s="5">
         <v>43</v>
@@ -10933,10 +10936,10 @@
         <v>24</v>
       </c>
       <c r="G170" s="5" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H170" s="5" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="I170" s="5" t="s">
         <v>18</v>
@@ -10948,7 +10951,7 @@
         <v>8</v>
       </c>
       <c r="L170" s="6" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M170" s="6" t="s">
         <v>68</v>
@@ -10962,13 +10965,13 @@
         <v>170</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D171" s="5" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E171" s="5">
         <v>44</v>
@@ -10977,10 +10980,10 @@
         <v>24</v>
       </c>
       <c r="G171" s="5" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H171" s="5" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="I171" s="5" t="s">
         <v>18</v>
@@ -10992,7 +10995,7 @@
         <v>8</v>
       </c>
       <c r="L171" s="6" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M171" s="6" t="s">
         <v>68</v>
@@ -11006,13 +11009,13 @@
         <v>171</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D172" s="5" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E172" s="5">
         <v>45</v>
@@ -11021,10 +11024,10 @@
         <v>24</v>
       </c>
       <c r="G172" s="5" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H172" s="5" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="I172" s="5" t="s">
         <v>18</v>
@@ -11036,7 +11039,7 @@
         <v>8</v>
       </c>
       <c r="L172" s="6" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M172" s="6" t="s">
         <v>68</v>
@@ -11050,13 +11053,13 @@
         <v>172</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D173" s="5" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E173" s="5">
         <v>46</v>
@@ -11065,7 +11068,7 @@
         <v>16</v>
       </c>
       <c r="G173" s="5" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H173" s="5"/>
       <c r="I173" s="5" t="s">
@@ -11078,7 +11081,7 @@
         <v>9</v>
       </c>
       <c r="L173" s="6" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M173" s="6" t="s">
         <v>68</v>
@@ -11090,13 +11093,13 @@
         <v>173</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D174" s="5" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E174" s="5">
         <v>1</v>
@@ -11105,7 +11108,7 @@
         <v>16</v>
       </c>
       <c r="G174" s="5" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H174" s="5" t="s">
         <v>18</v>
@@ -11120,7 +11123,7 @@
         <v>9</v>
       </c>
       <c r="L174" s="6" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M174" s="6" t="s">
         <v>84</v>
@@ -11134,13 +11137,13 @@
         <v>174</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D175" s="5" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E175" s="5">
         <v>2</v>
@@ -11149,7 +11152,7 @@
         <v>16</v>
       </c>
       <c r="G175" s="5" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H175" s="5" t="s">
         <v>18</v>
@@ -11164,7 +11167,7 @@
         <v>9</v>
       </c>
       <c r="L175" s="6" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M175" s="6" t="s">
         <v>84</v>
@@ -11178,13 +11181,13 @@
         <v>175</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D176" s="5" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E176" s="5">
         <v>3</v>
@@ -11208,7 +11211,7 @@
         <v>9</v>
       </c>
       <c r="L176" s="6" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M176" s="6" t="s">
         <v>84</v>
@@ -11222,13 +11225,13 @@
         <v>176</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D177" s="5" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E177" s="5">
         <v>4</v>
@@ -11240,7 +11243,7 @@
         <v>25</v>
       </c>
       <c r="H177" s="5" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="I177" s="5" t="s">
         <v>18</v>
@@ -11252,7 +11255,7 @@
         <v>9</v>
       </c>
       <c r="L177" s="6" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M177" s="6" t="s">
         <v>84</v>
@@ -11266,13 +11269,13 @@
         <v>177</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D178" s="5" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E178" s="5">
         <v>5</v>
@@ -11281,10 +11284,10 @@
         <v>24</v>
       </c>
       <c r="G178" s="5" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H178" s="5" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="I178" s="5" t="s">
         <v>18</v>
@@ -11296,7 +11299,7 @@
         <v>9</v>
       </c>
       <c r="L178" s="6" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M178" s="6" t="s">
         <v>84</v>
@@ -11310,13 +11313,13 @@
         <v>178</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D179" s="5" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E179" s="5">
         <v>6</v>
@@ -11325,10 +11328,10 @@
         <v>24</v>
       </c>
       <c r="G179" s="5" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H179" s="5" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="I179" s="5" t="s">
         <v>18</v>
@@ -11340,7 +11343,7 @@
         <v>9</v>
       </c>
       <c r="L179" s="6" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M179" s="6" t="s">
         <v>84</v>
@@ -11354,13 +11357,13 @@
         <v>179</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D180" s="5" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E180" s="5">
         <v>7</v>
@@ -11369,10 +11372,10 @@
         <v>24</v>
       </c>
       <c r="G180" s="5" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H180" s="5" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="I180" s="5" t="s">
         <v>18</v>
@@ -11384,7 +11387,7 @@
         <v>9</v>
       </c>
       <c r="L180" s="6" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M180" s="6" t="s">
         <v>84</v>
@@ -11398,13 +11401,13 @@
         <v>180</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D181" s="5" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="E181" s="5">
         <v>8</v>
@@ -11413,10 +11416,10 @@
         <v>24</v>
       </c>
       <c r="G181" s="5" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H181" s="5" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="I181" s="5" t="s">
         <v>18</v>
@@ -11428,7 +11431,7 @@
         <v>9</v>
       </c>
       <c r="L181" s="6" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M181" s="6" t="s">
         <v>21</v>
@@ -11442,13 +11445,13 @@
         <v>181</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D182" s="5" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="E182" s="5">
         <v>9</v>
@@ -11457,10 +11460,10 @@
         <v>24</v>
       </c>
       <c r="G182" s="5" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H182" s="5" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="I182" s="5" t="s">
         <v>18</v>
@@ -11472,7 +11475,7 @@
         <v>9</v>
       </c>
       <c r="L182" s="6" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M182" s="6" t="s">
         <v>21</v>
@@ -11486,13 +11489,13 @@
         <v>182</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E183" s="5">
         <v>10</v>
@@ -11501,10 +11504,10 @@
         <v>24</v>
       </c>
       <c r="G183" s="5" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H183" s="5" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="I183" s="5" t="s">
         <v>18</v>
@@ -11516,7 +11519,7 @@
         <v>9</v>
       </c>
       <c r="L183" s="6" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M183" s="6" t="s">
         <v>21</v>
@@ -11530,13 +11533,13 @@
         <v>183</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D184" s="5" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E184" s="5">
         <v>11</v>
@@ -11545,10 +11548,10 @@
         <v>24</v>
       </c>
       <c r="G184" s="5" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H184" s="5" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="I184" s="5" t="s">
         <v>18</v>
@@ -11560,7 +11563,7 @@
         <v>9</v>
       </c>
       <c r="L184" s="6" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M184" s="6" t="s">
         <v>21</v>
@@ -11574,13 +11577,13 @@
         <v>184</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D185" s="5" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E185" s="5">
         <v>12</v>
@@ -11589,10 +11592,10 @@
         <v>24</v>
       </c>
       <c r="G185" s="5" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H185" s="5" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I185" s="5" t="s">
         <v>18</v>
@@ -11604,7 +11607,7 @@
         <v>9</v>
       </c>
       <c r="L185" s="6" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="M185" s="6" t="s">
         <v>40</v>
@@ -11618,13 +11621,13 @@
         <v>185</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D186" s="5" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="E186" s="5">
         <v>13</v>
@@ -11633,10 +11636,10 @@
         <v>24</v>
       </c>
       <c r="G186" s="5" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H186" s="5" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="I186" s="5" t="s">
         <v>18</v>
@@ -11648,7 +11651,7 @@
         <v>9</v>
       </c>
       <c r="L186" s="6" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="M186" s="6" t="s">
         <v>40</v>
@@ -11662,13 +11665,13 @@
         <v>186</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D187" s="5" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E187" s="5">
         <v>14</v>
@@ -11677,10 +11680,10 @@
         <v>24</v>
       </c>
       <c r="G187" s="5" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H187" s="5" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="I187" s="5" t="s">
         <v>18</v>
@@ -11692,7 +11695,7 @@
         <v>9</v>
       </c>
       <c r="L187" s="6" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="M187" s="6" t="s">
         <v>40</v>
@@ -11706,13 +11709,13 @@
         <v>187</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D188" s="5" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E188" s="5">
         <v>15</v>
@@ -11721,10 +11724,10 @@
         <v>24</v>
       </c>
       <c r="G188" s="5" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H188" s="5" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="I188" s="5" t="s">
         <v>18</v>
@@ -11736,7 +11739,7 @@
         <v>9</v>
       </c>
       <c r="L188" s="6" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="M188" s="6" t="s">
         <v>40</v>
@@ -11750,13 +11753,13 @@
         <v>188</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D189" s="5" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="E189" s="5">
         <v>16</v>
@@ -11765,10 +11768,10 @@
         <v>24</v>
       </c>
       <c r="G189" s="5" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H189" s="5" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="I189" s="5" t="s">
         <v>18</v>
@@ -11780,7 +11783,7 @@
         <v>9</v>
       </c>
       <c r="L189" s="6" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M189" s="6" t="s">
         <v>54</v>
@@ -11794,13 +11797,13 @@
         <v>189</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D190" s="5" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="E190" s="5">
         <v>17</v>
@@ -11809,10 +11812,10 @@
         <v>24</v>
       </c>
       <c r="G190" s="5" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H190" s="5" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="I190" s="5" t="s">
         <v>18</v>
@@ -11824,7 +11827,7 @@
         <v>9</v>
       </c>
       <c r="L190" s="6" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M190" s="6" t="s">
         <v>54</v>
@@ -11838,13 +11841,13 @@
         <v>190</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D191" s="5" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="E191" s="5">
         <v>18</v>
@@ -11853,10 +11856,10 @@
         <v>24</v>
       </c>
       <c r="G191" s="5" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H191" s="5" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="I191" s="5" t="s">
         <v>18</v>
@@ -11868,7 +11871,7 @@
         <v>9</v>
       </c>
       <c r="L191" s="6" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M191" s="6" t="s">
         <v>54</v>
@@ -11882,13 +11885,13 @@
         <v>191</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D192" s="5" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E192" s="5">
         <v>19</v>
@@ -11897,10 +11900,10 @@
         <v>24</v>
       </c>
       <c r="G192" s="5" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H192" s="5" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="I192" s="5" t="s">
         <v>18</v>
@@ -11912,7 +11915,7 @@
         <v>9</v>
       </c>
       <c r="L192" s="6" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M192" s="6" t="s">
         <v>54</v>
@@ -11926,13 +11929,13 @@
         <v>192</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D193" s="5" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="E193" s="5">
         <v>20</v>
@@ -11941,10 +11944,10 @@
         <v>24</v>
       </c>
       <c r="G193" s="5" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H193" s="5" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="I193" s="5" t="s">
         <v>18</v>
@@ -11956,7 +11959,7 @@
         <v>9</v>
       </c>
       <c r="L193" s="6" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="M193" s="6" t="s">
         <v>68</v>
@@ -11970,13 +11973,13 @@
         <v>193</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D194" s="5" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="E194" s="5">
         <v>21</v>
@@ -11985,10 +11988,10 @@
         <v>24</v>
       </c>
       <c r="G194" s="5" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H194" s="5" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="I194" s="5" t="s">
         <v>18</v>
@@ -12000,7 +12003,7 @@
         <v>9</v>
       </c>
       <c r="L194" s="6" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="M194" s="6" t="s">
         <v>68</v>
@@ -12014,13 +12017,13 @@
         <v>194</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D195" s="5" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="E195" s="5">
         <v>22</v>
@@ -12029,10 +12032,10 @@
         <v>24</v>
       </c>
       <c r="G195" s="5" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H195" s="5" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="I195" s="5" t="s">
         <v>18</v>
@@ -12044,7 +12047,7 @@
         <v>9</v>
       </c>
       <c r="L195" s="6" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="M195" s="6" t="s">
         <v>68</v>
@@ -12058,13 +12061,13 @@
         <v>195</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D196" s="5" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="E196" s="5">
         <v>23</v>
@@ -12073,10 +12076,10 @@
         <v>24</v>
       </c>
       <c r="G196" s="5" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H196" s="5" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="I196" s="5" t="s">
         <v>18</v>
@@ -12088,7 +12091,7 @@
         <v>9</v>
       </c>
       <c r="L196" s="6" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="M196" s="6" t="s">
         <v>68</v>
@@ -12102,13 +12105,13 @@
         <v>196</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D197" s="5" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="E197" s="5">
         <v>24</v>
@@ -12117,10 +12120,10 @@
         <v>24</v>
       </c>
       <c r="G197" s="5" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H197" s="5" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="I197" s="5" t="s">
         <v>18</v>
@@ -12132,7 +12135,7 @@
         <v>10</v>
       </c>
       <c r="L197" s="6" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="M197" s="6" t="s">
         <v>84</v>
@@ -12146,13 +12149,13 @@
         <v>197</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D198" s="5" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="E198" s="5">
         <v>25</v>
@@ -12161,10 +12164,10 @@
         <v>24</v>
       </c>
       <c r="G198" s="5" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H198" s="5" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="I198" s="5" t="s">
         <v>18</v>
@@ -12176,7 +12179,7 @@
         <v>10</v>
       </c>
       <c r="L198" s="6" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="M198" s="6" t="s">
         <v>84</v>
@@ -12190,13 +12193,13 @@
         <v>198</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D199" s="5" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E199" s="5">
         <v>26</v>
@@ -12205,10 +12208,10 @@
         <v>24</v>
       </c>
       <c r="G199" s="5" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H199" s="5" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="I199" s="5" t="s">
         <v>18</v>
@@ -12220,7 +12223,7 @@
         <v>10</v>
       </c>
       <c r="L199" s="6" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="M199" s="6" t="s">
         <v>84</v>
@@ -12234,13 +12237,13 @@
         <v>199</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D200" s="5" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E200" s="5">
         <v>27</v>
@@ -12249,10 +12252,10 @@
         <v>24</v>
       </c>
       <c r="G200" s="5" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H200" s="5" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="I200" s="5" t="s">
         <v>18</v>
@@ -12264,7 +12267,7 @@
         <v>10</v>
       </c>
       <c r="L200" s="6" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="M200" s="6" t="s">
         <v>84</v>
@@ -12278,13 +12281,13 @@
         <v>200</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D201" s="5" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="E201" s="5">
         <v>28</v>
@@ -12293,10 +12296,10 @@
         <v>24</v>
       </c>
       <c r="G201" s="5" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H201" s="5" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="I201" s="5" t="s">
         <v>18</v>
@@ -12308,7 +12311,7 @@
         <v>10</v>
       </c>
       <c r="L201" s="6" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="M201" s="6" t="s">
         <v>21</v>
@@ -12322,13 +12325,13 @@
         <v>201</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D202" s="5" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E202" s="5">
         <v>29</v>
@@ -12337,10 +12340,10 @@
         <v>24</v>
       </c>
       <c r="G202" s="5" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H202" s="5" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="I202" s="5" t="s">
         <v>18</v>
@@ -12352,7 +12355,7 @@
         <v>10</v>
       </c>
       <c r="L202" s="6" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="M202" s="6" t="s">
         <v>21</v>
@@ -12366,13 +12369,13 @@
         <v>202</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D203" s="5" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="E203" s="5">
         <v>30</v>
@@ -12381,10 +12384,10 @@
         <v>24</v>
       </c>
       <c r="G203" s="5" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H203" s="5" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="I203" s="5" t="s">
         <v>18</v>
@@ -12396,7 +12399,7 @@
         <v>10</v>
       </c>
       <c r="L203" s="6" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="M203" s="6" t="s">
         <v>21</v>
@@ -12410,13 +12413,13 @@
         <v>203</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D204" s="5" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="E204" s="5">
         <v>31</v>
@@ -12428,7 +12431,7 @@
         <v>73</v>
       </c>
       <c r="H204" s="5" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="I204" s="5" t="s">
         <v>18</v>
@@ -12440,7 +12443,7 @@
         <v>10</v>
       </c>
       <c r="L204" s="6" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="M204" s="6" t="s">
         <v>21</v>
@@ -12454,13 +12457,13 @@
         <v>204</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D205" s="5" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="E205" s="5">
         <v>1</v>
@@ -12469,10 +12472,10 @@
         <v>24</v>
       </c>
       <c r="G205" s="5" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H205" s="5" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="I205" s="5" t="s">
         <v>18</v>
@@ -12484,7 +12487,7 @@
         <v>10</v>
       </c>
       <c r="L205" s="6" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="M205" s="6" t="s">
         <v>40</v>
@@ -12498,13 +12501,13 @@
         <v>205</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D206" s="5" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E206" s="5">
         <v>2</v>
@@ -12513,10 +12516,10 @@
         <v>24</v>
       </c>
       <c r="G206" s="5" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H206" s="5" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="I206" s="5" t="s">
         <v>18</v>
@@ -12528,7 +12531,7 @@
         <v>10</v>
       </c>
       <c r="L206" s="6" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="M206" s="6" t="s">
         <v>40</v>
@@ -12542,13 +12545,13 @@
         <v>206</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D207" s="5" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="E207" s="5">
         <v>3</v>
@@ -12557,10 +12560,10 @@
         <v>24</v>
       </c>
       <c r="G207" s="5" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H207" s="5" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="I207" s="5" t="s">
         <v>18</v>
@@ -12572,7 +12575,7 @@
         <v>10</v>
       </c>
       <c r="L207" s="6" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="M207" s="6" t="s">
         <v>40</v>
@@ -12586,13 +12589,13 @@
         <v>207</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D208" s="5" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="E208" s="5">
         <v>4</v>
@@ -12601,10 +12604,10 @@
         <v>24</v>
       </c>
       <c r="G208" s="5" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H208" s="5" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="I208" s="5" t="s">
         <v>18</v>
@@ -12616,7 +12619,7 @@
         <v>10</v>
       </c>
       <c r="L208" s="6" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="M208" s="6" t="s">
         <v>40</v>
@@ -12630,13 +12633,13 @@
         <v>208</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D209" s="5" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="E209" s="5">
         <v>5</v>
@@ -12645,10 +12648,10 @@
         <v>24</v>
       </c>
       <c r="G209" s="5" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H209" s="5" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="I209" s="5" t="s">
         <v>18</v>
@@ -12660,7 +12663,7 @@
         <v>10</v>
       </c>
       <c r="L209" s="6" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="M209" s="6" t="s">
         <v>54</v>
@@ -12674,13 +12677,13 @@
         <v>209</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D210" s="5" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="E210" s="5">
         <v>6</v>
@@ -12689,10 +12692,10 @@
         <v>24</v>
       </c>
       <c r="G210" s="5" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H210" s="5" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="I210" s="5" t="s">
         <v>18</v>
@@ -12704,7 +12707,7 @@
         <v>10</v>
       </c>
       <c r="L210" s="6" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="M210" s="6" t="s">
         <v>54</v>
@@ -12718,13 +12721,13 @@
         <v>210</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D211" s="5" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="E211" s="5">
         <v>7</v>
@@ -12733,10 +12736,10 @@
         <v>24</v>
       </c>
       <c r="G211" s="5" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H211" s="5" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="I211" s="5" t="s">
         <v>18</v>
@@ -12748,7 +12751,7 @@
         <v>10</v>
       </c>
       <c r="L211" s="6" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="M211" s="6" t="s">
         <v>54</v>
@@ -12762,13 +12765,13 @@
         <v>211</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D212" s="5" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E212" s="5">
         <v>8</v>
@@ -12777,10 +12780,10 @@
         <v>24</v>
       </c>
       <c r="G212" s="5" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H212" s="5" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="I212" s="5" t="s">
         <v>18</v>
@@ -12792,7 +12795,7 @@
         <v>10</v>
       </c>
       <c r="L212" s="6" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="M212" s="6" t="s">
         <v>54</v>
@@ -12806,13 +12809,13 @@
         <v>212</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D213" s="5" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E213" s="5">
         <v>9</v>
@@ -12821,10 +12824,10 @@
         <v>24</v>
       </c>
       <c r="G213" s="5" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H213" s="5" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="I213" s="5" t="s">
         <v>18</v>
@@ -12836,7 +12839,7 @@
         <v>10</v>
       </c>
       <c r="L213" s="6" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="M213" s="6" t="s">
         <v>68</v>
@@ -12850,13 +12853,13 @@
         <v>213</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D214" s="5" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="E214" s="5">
         <v>10</v>
@@ -12865,10 +12868,10 @@
         <v>24</v>
       </c>
       <c r="G214" s="5" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H214" s="5" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="I214" s="5" t="s">
         <v>18</v>
@@ -12880,7 +12883,7 @@
         <v>10</v>
       </c>
       <c r="L214" s="6" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="M214" s="6" t="s">
         <v>68</v>
@@ -12894,13 +12897,13 @@
         <v>214</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D215" s="5" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="E215" s="5">
         <v>11</v>
@@ -12909,10 +12912,10 @@
         <v>24</v>
       </c>
       <c r="G215" s="5" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H215" s="5" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="I215" s="5" t="s">
         <v>18</v>
@@ -12924,7 +12927,7 @@
         <v>10</v>
       </c>
       <c r="L215" s="6" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="M215" s="6" t="s">
         <v>68</v>
@@ -12938,13 +12941,13 @@
         <v>215</v>
       </c>
       <c r="B216" s="5" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D216" s="5" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="E216" s="5">
         <v>12</v>
@@ -12953,10 +12956,10 @@
         <v>24</v>
       </c>
       <c r="G216" s="5" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H216" s="5" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="I216" s="5" t="s">
         <v>18</v>
@@ -12968,7 +12971,7 @@
         <v>10</v>
       </c>
       <c r="L216" s="6" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="M216" s="6" t="s">
         <v>68</v>
@@ -12982,13 +12985,13 @@
         <v>216</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D217" s="5" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E217" s="5">
         <v>13</v>
@@ -12997,10 +13000,10 @@
         <v>24</v>
       </c>
       <c r="G217" s="5" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H217" s="5" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="I217" s="5" t="s">
         <v>18</v>
@@ -13012,7 +13015,7 @@
         <v>11</v>
       </c>
       <c r="L217" s="6" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="M217" s="6" t="s">
         <v>84</v>
@@ -13026,13 +13029,13 @@
         <v>217</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D218" s="5" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="E218" s="5">
         <v>14</v>
@@ -13041,10 +13044,10 @@
         <v>24</v>
       </c>
       <c r="G218" s="5" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H218" s="5" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="I218" s="5" t="s">
         <v>18</v>
@@ -13056,7 +13059,7 @@
         <v>11</v>
       </c>
       <c r="L218" s="6" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="M218" s="6" t="s">
         <v>84</v>
@@ -13070,13 +13073,13 @@
         <v>218</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D219" s="5" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="E219" s="5">
         <v>15</v>
@@ -13085,10 +13088,10 @@
         <v>24</v>
       </c>
       <c r="G219" s="5" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H219" s="5" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="I219" s="5" t="s">
         <v>18</v>
@@ -13100,7 +13103,7 @@
         <v>11</v>
       </c>
       <c r="L219" s="6" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="M219" s="6" t="s">
         <v>84</v>
@@ -13114,13 +13117,13 @@
         <v>219</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D220" s="5" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="E220" s="5">
         <v>16</v>
@@ -13129,10 +13132,10 @@
         <v>24</v>
       </c>
       <c r="G220" s="5" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H220" s="5" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="I220" s="5" t="s">
         <v>18</v>
@@ -13144,7 +13147,7 @@
         <v>11</v>
       </c>
       <c r="L220" s="6" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="M220" s="6" t="s">
         <v>84</v>
@@ -13158,13 +13161,13 @@
         <v>220</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D221" s="5" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="E221" s="5">
         <v>17</v>
@@ -13173,10 +13176,10 @@
         <v>24</v>
       </c>
       <c r="G221" s="5" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H221" s="5" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="I221" s="5" t="s">
         <v>18</v>
@@ -13188,7 +13191,7 @@
         <v>11</v>
       </c>
       <c r="L221" s="6" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="M221" s="6" t="s">
         <v>21</v>
@@ -13202,13 +13205,13 @@
         <v>221</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D222" s="5" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="E222" s="5">
         <v>18</v>
@@ -13217,10 +13220,10 @@
         <v>24</v>
       </c>
       <c r="G222" s="5" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H222" s="5" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="I222" s="5" t="s">
         <v>18</v>
@@ -13232,7 +13235,7 @@
         <v>11</v>
       </c>
       <c r="L222" s="6" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="M222" s="6" t="s">
         <v>21</v>
@@ -13246,13 +13249,13 @@
         <v>222</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D223" s="5" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E223" s="5">
         <v>19</v>
@@ -13261,10 +13264,10 @@
         <v>24</v>
       </c>
       <c r="G223" s="5" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H223" s="5" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="I223" s="5" t="s">
         <v>18</v>
@@ -13276,7 +13279,7 @@
         <v>11</v>
       </c>
       <c r="L223" s="6" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="M223" s="6" t="s">
         <v>21</v>
@@ -13290,13 +13293,13 @@
         <v>223</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D224" s="5" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="E224" s="5">
         <v>20</v>
@@ -13308,7 +13311,7 @@
         <v>73</v>
       </c>
       <c r="H224" s="9" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="I224" s="5" t="s">
         <v>18</v>
@@ -13320,7 +13323,7 @@
         <v>11</v>
       </c>
       <c r="L224" s="6" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="M224" s="6" t="s">
         <v>21</v>
@@ -13332,13 +13335,13 @@
         <v>224</v>
       </c>
       <c r="B225" s="5" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C225" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="D225" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="E225">
         <v>21</v>
@@ -13347,7 +13350,7 @@
         <v>16</v>
       </c>
       <c r="G225" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="I225" s="5" t="s">
         <v>172</v>
@@ -13359,7 +13362,7 @@
         <v>11</v>
       </c>
       <c r="L225" s="6" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="M225" s="6" t="s">
         <v>40</v>
@@ -13370,7 +13373,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="F173 F2:F172 F174:F225">
+    <dataValidation type="list" sqref="F2:F225">
       <formula1>"Video,Resource"</formula1>
     </dataValidation>
   </dataValidations>
@@ -13399,24 +13402,24 @@
   <sheetData>
     <row r="1" ht="27.6" spans="1:4">
       <c r="A1" s="3" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C2" s="2">
         <v>15</v>
@@ -13427,7 +13430,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B3" s="2">
         <v>223</v>
@@ -13441,7 +13444,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B4" s="2">
         <v>204</v>
@@ -13455,7 +13458,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B5" s="2">
         <v>19</v>
@@ -13469,10 +13472,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C6" s="2">
         <v>28</v>
@@ -13483,10 +13486,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C7" s="2">
         <v>20</v>
@@ -13497,15 +13500,15 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B9" s="2">
         <v>51</v>
@@ -13513,18 +13516,18 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -13584,50 +13587,50 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="3" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="2" ht="27.6" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="6" ht="27.6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -13635,15 +13638,15 @@
         <v>9</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
   </sheetData>
@@ -13668,7 +13671,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
@@ -13680,35 +13683,35 @@
         <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="2" ht="27.6" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>73</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>23</v>
@@ -13723,12 +13726,12 @@
         <v>26</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>72</v>
@@ -13743,12 +13746,12 @@
         <v>74</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>88</v>
@@ -13763,12 +13766,12 @@
         <v>90</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>91</v>
@@ -13783,47 +13786,47 @@
         <v>92</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>75</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>75</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
     <row r="9" spans="1:6">
